--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ehigh\claude\Golf League\Scores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61E8F04C-39C8-452D-804A-56479D2B85EE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -23,13 +23,115 @@
     <sheet name="R8 Scores" sheetId="8" r:id="rId8"/>
     <sheet name="R9 Scores" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="27">
+  <si>
+    <t>Skybrook</t>
+  </si>
+  <si>
+    <t>First 3</t>
+  </si>
+  <si>
+    <t>Middle 3</t>
+  </si>
+  <si>
+    <t>Final 3</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>Net Score</t>
+  </si>
+  <si>
+    <t>Holes Won</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>Brian Wojcio</t>
+  </si>
+  <si>
+    <t>Handicap:</t>
+  </si>
+  <si>
+    <t>Tees:</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Holes:</t>
+  </si>
+  <si>
+    <t>Front 9</t>
+  </si>
+  <si>
+    <t>HOLE</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>HC</t>
+  </si>
+  <si>
+    <t>GROSS</t>
+  </si>
+  <si>
+    <t>Strokes</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>Wins Hole</t>
+  </si>
+  <si>
+    <t>Ethan High</t>
+  </si>
+  <si>
+    <t>Rob Bass</t>
+  </si>
+  <si>
+    <t>Carson Bass</t>
+  </si>
+  <si>
+    <t>Highland Creek</t>
+  </si>
+  <si>
+    <t>Jerome Martin</t>
+  </si>
+  <si>
+    <t>Kaylan Adams</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="\+0;\-0;0"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -43,20 +145,218 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="15">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -65,14 +365,171 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -402,30 +859,2218 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:M74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="34"/>
+      <c r="L2" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="34"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6">
+        <v>43</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="38">
+        <v>2</v>
+      </c>
+      <c r="K3" s="39"/>
+      <c r="L3" s="43">
+        <v>6</v>
+      </c>
+      <c r="M3" s="39"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="37"/>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="41"/>
+    </row>
+    <row r="5" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10">
+        <v>39</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="42"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="37"/>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="2"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="2:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11">
+        <v>12</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+      <c r="D9" s="18">
+        <v>2</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3</v>
+      </c>
+      <c r="F9" s="17">
+        <v>4</v>
+      </c>
+      <c r="G9" s="18">
+        <v>5</v>
+      </c>
+      <c r="H9" s="19">
+        <v>6</v>
+      </c>
+      <c r="I9" s="17">
+        <v>7</v>
+      </c>
+      <c r="J9" s="18">
+        <v>8</v>
+      </c>
+      <c r="K9" s="19">
+        <v>9</v>
+      </c>
+      <c r="L9" s="11"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="11">
+        <v>4</v>
+      </c>
+      <c r="D10" s="11">
+        <v>3</v>
+      </c>
+      <c r="E10" s="21">
+        <v>4</v>
+      </c>
+      <c r="F10" s="22">
+        <v>5</v>
+      </c>
+      <c r="G10" s="11">
+        <v>4</v>
+      </c>
+      <c r="H10" s="21">
+        <v>4</v>
+      </c>
+      <c r="I10" s="22">
+        <v>3</v>
+      </c>
+      <c r="J10" s="11">
+        <v>5</v>
+      </c>
+      <c r="K10" s="21">
+        <v>4</v>
+      </c>
+      <c r="L10" s="11">
+        <v>36</v>
+      </c>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="11">
+        <v>7</v>
+      </c>
+      <c r="D11" s="11">
+        <v>15</v>
+      </c>
+      <c r="E11" s="21">
+        <v>5</v>
+      </c>
+      <c r="F11" s="22">
+        <v>13</v>
+      </c>
+      <c r="G11" s="11">
+        <v>3</v>
+      </c>
+      <c r="H11" s="21">
+        <v>11</v>
+      </c>
+      <c r="I11" s="22">
+        <v>17</v>
+      </c>
+      <c r="J11" s="11">
+        <v>9</v>
+      </c>
+      <c r="K11" s="21">
+        <v>1</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="24">
+        <v>5</v>
+      </c>
+      <c r="D12" s="25">
+        <v>5</v>
+      </c>
+      <c r="E12" s="26">
+        <v>5</v>
+      </c>
+      <c r="F12" s="24">
+        <v>5</v>
+      </c>
+      <c r="G12" s="25">
+        <v>6</v>
+      </c>
+      <c r="H12" s="26">
+        <v>5</v>
+      </c>
+      <c r="I12" s="24">
+        <v>4</v>
+      </c>
+      <c r="J12" s="25">
+        <v>8</v>
+      </c>
+      <c r="K12" s="26">
+        <v>6</v>
+      </c>
+      <c r="L12" s="11">
+        <v>49</v>
+      </c>
+      <c r="M12" s="27">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="22">
+        <v>1</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0</v>
+      </c>
+      <c r="E13" s="21">
+        <v>1</v>
+      </c>
+      <c r="F13" s="22">
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
+        <v>1</v>
+      </c>
+      <c r="H13" s="21">
+        <v>1</v>
+      </c>
+      <c r="I13" s="22">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11">
+        <v>1</v>
+      </c>
+      <c r="K13" s="21">
+        <v>1</v>
+      </c>
+      <c r="L13" s="27"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="22">
+        <v>4</v>
+      </c>
+      <c r="D14" s="11">
+        <v>5</v>
+      </c>
+      <c r="E14" s="21">
+        <v>4</v>
+      </c>
+      <c r="F14" s="22">
+        <v>5</v>
+      </c>
+      <c r="G14" s="11">
+        <v>5</v>
+      </c>
+      <c r="H14" s="21">
+        <v>4</v>
+      </c>
+      <c r="I14" s="22">
+        <v>4</v>
+      </c>
+      <c r="J14" s="11">
+        <v>7</v>
+      </c>
+      <c r="K14" s="21">
+        <v>5</v>
+      </c>
+      <c r="L14" s="28">
+        <v>43</v>
+      </c>
+      <c r="M14" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="30">
+        <v>1</v>
+      </c>
+      <c r="D15" s="31">
+        <v>0</v>
+      </c>
+      <c r="E15" s="32">
+        <v>1</v>
+      </c>
+      <c r="F15" s="30">
+        <v>0</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0</v>
+      </c>
+      <c r="H15" s="32">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30">
+        <v>0</v>
+      </c>
+      <c r="J15" s="31">
+        <v>0</v>
+      </c>
+      <c r="K15" s="32">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="2:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="11">
+        <v>12</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="17">
+        <v>1</v>
+      </c>
+      <c r="D18" s="18">
+        <v>2</v>
+      </c>
+      <c r="E18" s="19">
+        <v>3</v>
+      </c>
+      <c r="F18" s="17">
+        <v>4</v>
+      </c>
+      <c r="G18" s="18">
+        <v>5</v>
+      </c>
+      <c r="H18" s="19">
+        <v>6</v>
+      </c>
+      <c r="I18" s="17">
+        <v>7</v>
+      </c>
+      <c r="J18" s="18">
+        <v>8</v>
+      </c>
+      <c r="K18" s="19">
+        <v>9</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" s="27"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="11">
+        <v>4</v>
+      </c>
+      <c r="D19" s="11">
+        <v>3</v>
+      </c>
+      <c r="E19" s="21">
+        <v>4</v>
+      </c>
+      <c r="F19" s="22">
+        <v>5</v>
+      </c>
+      <c r="G19" s="11">
+        <v>4</v>
+      </c>
+      <c r="H19" s="21">
+        <v>4</v>
+      </c>
+      <c r="I19" s="22">
+        <v>3</v>
+      </c>
+      <c r="J19" s="11">
+        <v>5</v>
+      </c>
+      <c r="K19" s="21">
+        <v>4</v>
+      </c>
+      <c r="L19" s="11">
+        <v>36</v>
+      </c>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="11">
+        <v>7</v>
+      </c>
+      <c r="D20" s="11">
+        <v>15</v>
+      </c>
+      <c r="E20" s="21">
+        <v>5</v>
+      </c>
+      <c r="F20" s="22">
+        <v>13</v>
+      </c>
+      <c r="G20" s="11">
+        <v>3</v>
+      </c>
+      <c r="H20" s="21">
+        <v>11</v>
+      </c>
+      <c r="I20" s="22">
+        <v>17</v>
+      </c>
+      <c r="J20" s="11">
+        <v>9</v>
+      </c>
+      <c r="K20" s="21">
+        <v>1</v>
+      </c>
+      <c r="L20" s="11"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="24">
+        <v>6</v>
+      </c>
+      <c r="D21" s="25">
+        <v>4</v>
+      </c>
+      <c r="E21" s="26">
+        <v>7</v>
+      </c>
+      <c r="F21" s="24">
+        <v>5</v>
+      </c>
+      <c r="G21" s="25">
+        <v>5</v>
+      </c>
+      <c r="H21" s="26">
+        <v>5</v>
+      </c>
+      <c r="I21" s="24">
+        <v>4</v>
+      </c>
+      <c r="J21" s="25">
+        <v>5</v>
+      </c>
+      <c r="K21" s="26">
+        <v>4</v>
+      </c>
+      <c r="L21" s="11">
+        <v>45</v>
+      </c>
+      <c r="M21" s="27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="11">
+        <v>0</v>
+      </c>
+      <c r="E22" s="21">
+        <v>1</v>
+      </c>
+      <c r="F22" s="22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11">
+        <v>1</v>
+      </c>
+      <c r="H22" s="21">
+        <v>1</v>
+      </c>
+      <c r="I22" s="22">
+        <v>0</v>
+      </c>
+      <c r="J22" s="11">
+        <v>1</v>
+      </c>
+      <c r="K22" s="21">
+        <v>1</v>
+      </c>
+      <c r="L22" s="27"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="22">
+        <v>5</v>
+      </c>
+      <c r="D23" s="11">
+        <v>4</v>
+      </c>
+      <c r="E23" s="21">
+        <v>6</v>
+      </c>
+      <c r="F23" s="22">
+        <v>5</v>
+      </c>
+      <c r="G23" s="11">
+        <v>4</v>
+      </c>
+      <c r="H23" s="21">
+        <v>4</v>
+      </c>
+      <c r="I23" s="22">
+        <v>4</v>
+      </c>
+      <c r="J23" s="11">
+        <v>4</v>
+      </c>
+      <c r="K23" s="21">
+        <v>3</v>
+      </c>
+      <c r="L23" s="28">
+        <v>39</v>
+      </c>
+      <c r="M23" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="30">
+        <v>0</v>
+      </c>
+      <c r="D24" s="31">
+        <v>1</v>
+      </c>
+      <c r="E24" s="32">
+        <v>0</v>
+      </c>
+      <c r="F24" s="30">
+        <v>0</v>
+      </c>
+      <c r="G24" s="31">
+        <v>1</v>
+      </c>
+      <c r="H24" s="32">
+        <v>0</v>
+      </c>
+      <c r="I24" s="30">
+        <v>0</v>
+      </c>
+      <c r="J24" s="31">
+        <v>1</v>
+      </c>
+      <c r="K24" s="32">
+        <v>1</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="26" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:13" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="34"/>
+      <c r="L27" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="34"/>
+    </row>
+    <row r="28" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="6">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6">
+        <v>1</v>
+      </c>
+      <c r="G28" s="6">
+        <v>3</v>
+      </c>
+      <c r="H28" s="6">
+        <v>43</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="38">
+        <v>1</v>
+      </c>
+      <c r="K28" s="39"/>
+      <c r="L28" s="43">
+        <v>7</v>
+      </c>
+      <c r="M28" s="39"/>
+    </row>
+    <row r="29" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="37"/>
+      <c r="C29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="41"/>
+    </row>
+    <row r="30" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="10">
+        <v>2</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10">
+        <v>2</v>
+      </c>
+      <c r="G30" s="10">
+        <v>5</v>
+      </c>
+      <c r="H30" s="10">
+        <v>38</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="42"/>
+    </row>
+    <row r="31" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="37"/>
+      <c r="C31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="8">
+        <v>2</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8">
+        <v>2</v>
+      </c>
+      <c r="G31" s="8">
+        <v>1</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="2:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="11">
+        <v>15</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B34" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="17">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18">
+        <v>2</v>
+      </c>
+      <c r="E34" s="19">
+        <v>3</v>
+      </c>
+      <c r="F34" s="17">
+        <v>4</v>
+      </c>
+      <c r="G34" s="18">
+        <v>5</v>
+      </c>
+      <c r="H34" s="19">
+        <v>6</v>
+      </c>
+      <c r="I34" s="17">
+        <v>7</v>
+      </c>
+      <c r="J34" s="18">
+        <v>8</v>
+      </c>
+      <c r="K34" s="19">
+        <v>9</v>
+      </c>
+      <c r="L34" s="11"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="11">
+        <v>4</v>
+      </c>
+      <c r="D35" s="11">
+        <v>3</v>
+      </c>
+      <c r="E35" s="21">
+        <v>4</v>
+      </c>
+      <c r="F35" s="22">
+        <v>5</v>
+      </c>
+      <c r="G35" s="11">
+        <v>4</v>
+      </c>
+      <c r="H35" s="21">
+        <v>4</v>
+      </c>
+      <c r="I35" s="22">
+        <v>3</v>
+      </c>
+      <c r="J35" s="11">
+        <v>5</v>
+      </c>
+      <c r="K35" s="21">
+        <v>4</v>
+      </c>
+      <c r="L35" s="11">
+        <v>36</v>
+      </c>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B36" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="11">
+        <v>7</v>
+      </c>
+      <c r="D36" s="11">
+        <v>15</v>
+      </c>
+      <c r="E36" s="21">
+        <v>5</v>
+      </c>
+      <c r="F36" s="22">
+        <v>13</v>
+      </c>
+      <c r="G36" s="11">
+        <v>3</v>
+      </c>
+      <c r="H36" s="21">
+        <v>11</v>
+      </c>
+      <c r="I36" s="22">
+        <v>17</v>
+      </c>
+      <c r="J36" s="11">
+        <v>9</v>
+      </c>
+      <c r="K36" s="21">
+        <v>1</v>
+      </c>
+      <c r="L36" s="11"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B37" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="24">
+        <v>5</v>
+      </c>
+      <c r="D37" s="25">
+        <v>4</v>
+      </c>
+      <c r="E37" s="26">
+        <v>6</v>
+      </c>
+      <c r="F37" s="24">
+        <v>7</v>
+      </c>
+      <c r="G37" s="25">
+        <v>7</v>
+      </c>
+      <c r="H37" s="26">
+        <v>6</v>
+      </c>
+      <c r="I37" s="24">
+        <v>4</v>
+      </c>
+      <c r="J37" s="25">
+        <v>5</v>
+      </c>
+      <c r="K37" s="26">
+        <v>7</v>
+      </c>
+      <c r="L37" s="11">
+        <v>51</v>
+      </c>
+      <c r="M37" s="27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="22">
+        <v>1</v>
+      </c>
+      <c r="D38" s="11">
+        <v>1</v>
+      </c>
+      <c r="E38" s="21">
+        <v>1</v>
+      </c>
+      <c r="F38" s="22">
+        <v>1</v>
+      </c>
+      <c r="G38" s="11">
+        <v>1</v>
+      </c>
+      <c r="H38" s="21">
+        <v>1</v>
+      </c>
+      <c r="I38" s="22">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11">
+        <v>1</v>
+      </c>
+      <c r="K38" s="21">
+        <v>1</v>
+      </c>
+      <c r="L38" s="27"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="22">
+        <v>4</v>
+      </c>
+      <c r="D39" s="11">
+        <v>3</v>
+      </c>
+      <c r="E39" s="21">
+        <v>5</v>
+      </c>
+      <c r="F39" s="22">
+        <v>6</v>
+      </c>
+      <c r="G39" s="11">
+        <v>6</v>
+      </c>
+      <c r="H39" s="21">
+        <v>5</v>
+      </c>
+      <c r="I39" s="22">
+        <v>4</v>
+      </c>
+      <c r="J39" s="11">
+        <v>4</v>
+      </c>
+      <c r="K39" s="21">
+        <v>6</v>
+      </c>
+      <c r="L39" s="28">
+        <v>43</v>
+      </c>
+      <c r="M39" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="30">
+        <v>0</v>
+      </c>
+      <c r="D40" s="31">
+        <v>1</v>
+      </c>
+      <c r="E40" s="32">
+        <v>0</v>
+      </c>
+      <c r="F40" s="30">
+        <v>0</v>
+      </c>
+      <c r="G40" s="31">
+        <v>0</v>
+      </c>
+      <c r="H40" s="32">
+        <v>1</v>
+      </c>
+      <c r="I40" s="30">
+        <v>0</v>
+      </c>
+      <c r="J40" s="31">
+        <v>1</v>
+      </c>
+      <c r="K40" s="32">
+        <v>0</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B41" s="2"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="2:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="11">
+        <v>20</v>
+      </c>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="18">
+        <v>2</v>
+      </c>
+      <c r="E43" s="19">
+        <v>3</v>
+      </c>
+      <c r="F43" s="17">
+        <v>4</v>
+      </c>
+      <c r="G43" s="18">
+        <v>5</v>
+      </c>
+      <c r="H43" s="19">
+        <v>6</v>
+      </c>
+      <c r="I43" s="17">
+        <v>7</v>
+      </c>
+      <c r="J43" s="18">
+        <v>8</v>
+      </c>
+      <c r="K43" s="19">
+        <v>9</v>
+      </c>
+      <c r="L43" s="11"/>
+      <c r="M43" s="27"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B44" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="11">
+        <v>4</v>
+      </c>
+      <c r="D44" s="11">
+        <v>3</v>
+      </c>
+      <c r="E44" s="21">
+        <v>4</v>
+      </c>
+      <c r="F44" s="22">
+        <v>5</v>
+      </c>
+      <c r="G44" s="11">
+        <v>4</v>
+      </c>
+      <c r="H44" s="21">
+        <v>4</v>
+      </c>
+      <c r="I44" s="22">
+        <v>3</v>
+      </c>
+      <c r="J44" s="11">
+        <v>5</v>
+      </c>
+      <c r="K44" s="21">
+        <v>4</v>
+      </c>
+      <c r="L44" s="11">
+        <v>36</v>
+      </c>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B45" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="11">
+        <v>7</v>
+      </c>
+      <c r="D45" s="11">
+        <v>15</v>
+      </c>
+      <c r="E45" s="21">
+        <v>5</v>
+      </c>
+      <c r="F45" s="22">
+        <v>13</v>
+      </c>
+      <c r="G45" s="11">
+        <v>3</v>
+      </c>
+      <c r="H45" s="21">
+        <v>11</v>
+      </c>
+      <c r="I45" s="22">
+        <v>17</v>
+      </c>
+      <c r="J45" s="11">
+        <v>9</v>
+      </c>
+      <c r="K45" s="21">
+        <v>1</v>
+      </c>
+      <c r="L45" s="11"/>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B46" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="24">
+        <v>4</v>
+      </c>
+      <c r="D46" s="25">
+        <v>5</v>
+      </c>
+      <c r="E46" s="26">
+        <v>4</v>
+      </c>
+      <c r="F46" s="24">
+        <v>6</v>
+      </c>
+      <c r="G46" s="25">
+        <v>7</v>
+      </c>
+      <c r="H46" s="26">
+        <v>7</v>
+      </c>
+      <c r="I46" s="24">
+        <v>4</v>
+      </c>
+      <c r="J46" s="25">
+        <v>6</v>
+      </c>
+      <c r="K46" s="26">
+        <v>5</v>
+      </c>
+      <c r="L46" s="11">
+        <v>48</v>
+      </c>
+      <c r="M46" s="27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B47" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="22">
+        <v>1</v>
+      </c>
+      <c r="D47" s="11">
+        <v>1</v>
+      </c>
+      <c r="E47" s="21">
+        <v>1</v>
+      </c>
+      <c r="F47" s="22">
+        <v>1</v>
+      </c>
+      <c r="G47" s="11">
+        <v>1</v>
+      </c>
+      <c r="H47" s="21">
+        <v>1</v>
+      </c>
+      <c r="I47" s="22">
+        <v>1</v>
+      </c>
+      <c r="J47" s="11">
+        <v>1</v>
+      </c>
+      <c r="K47" s="21">
+        <v>2</v>
+      </c>
+      <c r="L47" s="27"/>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B48" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="22">
+        <v>3</v>
+      </c>
+      <c r="D48" s="11">
+        <v>4</v>
+      </c>
+      <c r="E48" s="21">
+        <v>3</v>
+      </c>
+      <c r="F48" s="22">
+        <v>5</v>
+      </c>
+      <c r="G48" s="11">
+        <v>6</v>
+      </c>
+      <c r="H48" s="21">
+        <v>6</v>
+      </c>
+      <c r="I48" s="22">
+        <v>3</v>
+      </c>
+      <c r="J48" s="11">
+        <v>5</v>
+      </c>
+      <c r="K48" s="21">
+        <v>3</v>
+      </c>
+      <c r="L48" s="28">
+        <v>38</v>
+      </c>
+      <c r="M48" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="30">
+        <v>1</v>
+      </c>
+      <c r="D49" s="31">
+        <v>0</v>
+      </c>
+      <c r="E49" s="32">
+        <v>1</v>
+      </c>
+      <c r="F49" s="30">
+        <v>1</v>
+      </c>
+      <c r="G49" s="31">
+        <v>0</v>
+      </c>
+      <c r="H49" s="32">
+        <v>0</v>
+      </c>
+      <c r="I49" s="30">
+        <v>1</v>
+      </c>
+      <c r="J49" s="31">
+        <v>0</v>
+      </c>
+      <c r="K49" s="32">
+        <v>1</v>
+      </c>
+      <c r="L49" s="11"/>
+      <c r="M49" s="2"/>
+    </row>
+    <row r="51" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" s="34"/>
+      <c r="L52" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="34"/>
+    </row>
+    <row r="53" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="6">
+        <v>0</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0</v>
+      </c>
+      <c r="F53" s="6">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6">
+        <v>54</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="38">
+        <v>4</v>
+      </c>
+      <c r="K53" s="39"/>
+      <c r="L53" s="43">
+        <v>4</v>
+      </c>
+      <c r="M53" s="39"/>
+    </row>
+    <row r="54" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="37"/>
+      <c r="C54" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="8">
+        <v>1</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8">
+        <v>1</v>
+      </c>
+      <c r="G54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="44"/>
+      <c r="M54" s="41"/>
+    </row>
+    <row r="55" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="10">
+        <v>0</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0</v>
+      </c>
+      <c r="F55" s="10">
+        <v>0</v>
+      </c>
+      <c r="G55" s="10">
+        <v>0</v>
+      </c>
+      <c r="H55" s="10">
+        <v>54</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="45"/>
+      <c r="M55" s="42"/>
+    </row>
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="37"/>
+      <c r="C56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="8">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>1</v>
+      </c>
+      <c r="F56" s="8">
+        <v>1</v>
+      </c>
+      <c r="G56" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B57" s="2"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="11">
+        <v>36</v>
+      </c>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B59" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="17">
+        <v>1</v>
+      </c>
+      <c r="D59" s="18">
+        <v>2</v>
+      </c>
+      <c r="E59" s="19">
+        <v>3</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4</v>
+      </c>
+      <c r="G59" s="18">
+        <v>5</v>
+      </c>
+      <c r="H59" s="19">
+        <v>6</v>
+      </c>
+      <c r="I59" s="17">
+        <v>7</v>
+      </c>
+      <c r="J59" s="18">
+        <v>8</v>
+      </c>
+      <c r="K59" s="19">
+        <v>9</v>
+      </c>
+      <c r="L59" s="11"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="11">
+        <v>4</v>
+      </c>
+      <c r="D60" s="11">
+        <v>5</v>
+      </c>
+      <c r="E60" s="21">
+        <v>3</v>
+      </c>
+      <c r="F60" s="22">
+        <v>4</v>
+      </c>
+      <c r="G60" s="11">
+        <v>4</v>
+      </c>
+      <c r="H60" s="21">
+        <v>3</v>
+      </c>
+      <c r="I60" s="22">
+        <v>5</v>
+      </c>
+      <c r="J60" s="11">
+        <v>4</v>
+      </c>
+      <c r="K60" s="21">
+        <v>4</v>
+      </c>
+      <c r="L60" s="11">
+        <v>36</v>
+      </c>
+      <c r="M60" s="2"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="11">
+        <v>7</v>
+      </c>
+      <c r="D61" s="11">
+        <v>17</v>
+      </c>
+      <c r="E61" s="21">
+        <v>15</v>
+      </c>
+      <c r="F61" s="22">
+        <v>1</v>
+      </c>
+      <c r="G61" s="11">
+        <v>11</v>
+      </c>
+      <c r="H61" s="21">
+        <v>9</v>
+      </c>
+      <c r="I61" s="22">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11">
+        <v>5</v>
+      </c>
+      <c r="K61" s="21">
+        <v>3</v>
+      </c>
+      <c r="L61" s="11"/>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="24">
+        <v>8</v>
+      </c>
+      <c r="D62" s="25">
+        <v>6</v>
+      </c>
+      <c r="E62" s="26">
+        <v>8</v>
+      </c>
+      <c r="F62" s="24">
+        <v>10</v>
+      </c>
+      <c r="G62" s="25">
+        <v>8</v>
+      </c>
+      <c r="H62" s="26">
+        <v>8</v>
+      </c>
+      <c r="I62" s="24">
+        <v>6</v>
+      </c>
+      <c r="J62" s="25">
+        <v>10</v>
+      </c>
+      <c r="K62" s="26">
+        <v>8</v>
+      </c>
+      <c r="L62" s="11">
+        <v>72</v>
+      </c>
+      <c r="M62" s="27">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B63" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="22">
+        <v>2</v>
+      </c>
+      <c r="D63" s="11">
+        <v>2</v>
+      </c>
+      <c r="E63" s="21">
+        <v>2</v>
+      </c>
+      <c r="F63" s="22">
+        <v>2</v>
+      </c>
+      <c r="G63" s="11">
+        <v>2</v>
+      </c>
+      <c r="H63" s="21">
+        <v>2</v>
+      </c>
+      <c r="I63" s="22">
+        <v>2</v>
+      </c>
+      <c r="J63" s="11">
+        <v>2</v>
+      </c>
+      <c r="K63" s="21">
+        <v>2</v>
+      </c>
+      <c r="L63" s="27"/>
+      <c r="M63" s="2"/>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B64" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="22">
+        <v>6</v>
+      </c>
+      <c r="D64" s="11">
+        <v>4</v>
+      </c>
+      <c r="E64" s="21">
+        <v>6</v>
+      </c>
+      <c r="F64" s="22">
+        <v>8</v>
+      </c>
+      <c r="G64" s="11">
+        <v>6</v>
+      </c>
+      <c r="H64" s="21">
+        <v>6</v>
+      </c>
+      <c r="I64" s="22">
+        <v>4</v>
+      </c>
+      <c r="J64" s="11">
+        <v>8</v>
+      </c>
+      <c r="K64" s="21">
+        <v>6</v>
+      </c>
+      <c r="L64" s="28">
+        <v>54</v>
+      </c>
+      <c r="M64" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="30">
+        <v>0</v>
+      </c>
+      <c r="D65" s="31">
+        <v>0</v>
+      </c>
+      <c r="E65" s="32">
+        <v>0</v>
+      </c>
+      <c r="F65" s="30">
+        <v>0</v>
+      </c>
+      <c r="G65" s="31">
+        <v>0</v>
+      </c>
+      <c r="H65" s="32">
+        <v>0</v>
+      </c>
+      <c r="I65" s="30">
+        <v>0</v>
+      </c>
+      <c r="J65" s="31">
+        <v>0</v>
+      </c>
+      <c r="K65" s="32">
+        <v>0</v>
+      </c>
+      <c r="L65" s="11"/>
+      <c r="M65" s="2"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B66" s="2"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="2"/>
+    </row>
+    <row r="67" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="11">
+        <v>36</v>
+      </c>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="2"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B68" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="17">
+        <v>1</v>
+      </c>
+      <c r="D68" s="18">
+        <v>2</v>
+      </c>
+      <c r="E68" s="19">
+        <v>3</v>
+      </c>
+      <c r="F68" s="17">
+        <v>4</v>
+      </c>
+      <c r="G68" s="18">
+        <v>5</v>
+      </c>
+      <c r="H68" s="19">
+        <v>6</v>
+      </c>
+      <c r="I68" s="17">
+        <v>7</v>
+      </c>
+      <c r="J68" s="18">
+        <v>8</v>
+      </c>
+      <c r="K68" s="19">
+        <v>9</v>
+      </c>
+      <c r="L68" s="11"/>
+      <c r="M68" s="27"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B69" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="11">
+        <v>4</v>
+      </c>
+      <c r="D69" s="11">
+        <v>5</v>
+      </c>
+      <c r="E69" s="21">
+        <v>3</v>
+      </c>
+      <c r="F69" s="22">
+        <v>4</v>
+      </c>
+      <c r="G69" s="11">
+        <v>4</v>
+      </c>
+      <c r="H69" s="21">
+        <v>3</v>
+      </c>
+      <c r="I69" s="22">
+        <v>5</v>
+      </c>
+      <c r="J69" s="11">
+        <v>4</v>
+      </c>
+      <c r="K69" s="21">
+        <v>4</v>
+      </c>
+      <c r="L69" s="11">
+        <v>36</v>
+      </c>
+      <c r="M69" s="2"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B70" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="11">
+        <v>7</v>
+      </c>
+      <c r="D70" s="11">
+        <v>17</v>
+      </c>
+      <c r="E70" s="21">
+        <v>15</v>
+      </c>
+      <c r="F70" s="22">
+        <v>1</v>
+      </c>
+      <c r="G70" s="11">
+        <v>11</v>
+      </c>
+      <c r="H70" s="21">
+        <v>9</v>
+      </c>
+      <c r="I70" s="22">
+        <v>13</v>
+      </c>
+      <c r="J70" s="11">
+        <v>5</v>
+      </c>
+      <c r="K70" s="21">
+        <v>3</v>
+      </c>
+      <c r="L70" s="11"/>
+      <c r="M70" s="2"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="24">
+        <v>8</v>
+      </c>
+      <c r="D71" s="25">
+        <v>6</v>
+      </c>
+      <c r="E71" s="26">
+        <v>8</v>
+      </c>
+      <c r="F71" s="24">
+        <v>10</v>
+      </c>
+      <c r="G71" s="25">
+        <v>8</v>
+      </c>
+      <c r="H71" s="26">
+        <v>8</v>
+      </c>
+      <c r="I71" s="24">
+        <v>6</v>
+      </c>
+      <c r="J71" s="25">
+        <v>10</v>
+      </c>
+      <c r="K71" s="26">
+        <v>8</v>
+      </c>
+      <c r="L71" s="11">
+        <v>72</v>
+      </c>
+      <c r="M71" s="27">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B72" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="22">
+        <v>2</v>
+      </c>
+      <c r="D72" s="11">
+        <v>2</v>
+      </c>
+      <c r="E72" s="21">
+        <v>2</v>
+      </c>
+      <c r="F72" s="22">
+        <v>2</v>
+      </c>
+      <c r="G72" s="11">
+        <v>2</v>
+      </c>
+      <c r="H72" s="21">
+        <v>2</v>
+      </c>
+      <c r="I72" s="22">
+        <v>2</v>
+      </c>
+      <c r="J72" s="11">
+        <v>2</v>
+      </c>
+      <c r="K72" s="21">
+        <v>2</v>
+      </c>
+      <c r="L72" s="27"/>
+      <c r="M72" s="2"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B73" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="22">
+        <v>6</v>
+      </c>
+      <c r="D73" s="11">
+        <v>4</v>
+      </c>
+      <c r="E73" s="21">
+        <v>6</v>
+      </c>
+      <c r="F73" s="22">
+        <v>8</v>
+      </c>
+      <c r="G73" s="11">
+        <v>6</v>
+      </c>
+      <c r="H73" s="21">
+        <v>6</v>
+      </c>
+      <c r="I73" s="22">
+        <v>4</v>
+      </c>
+      <c r="J73" s="11">
+        <v>8</v>
+      </c>
+      <c r="K73" s="21">
+        <v>6</v>
+      </c>
+      <c r="L73" s="28">
+        <v>54</v>
+      </c>
+      <c r="M73" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="30">
+        <v>0</v>
+      </c>
+      <c r="D74" s="31">
+        <v>0</v>
+      </c>
+      <c r="E74" s="32">
+        <v>0</v>
+      </c>
+      <c r="F74" s="30">
+        <v>0</v>
+      </c>
+      <c r="G74" s="31">
+        <v>0</v>
+      </c>
+      <c r="H74" s="32">
+        <v>0</v>
+      </c>
+      <c r="I74" s="30">
+        <v>0</v>
+      </c>
+      <c r="J74" s="31">
+        <v>0</v>
+      </c>
+      <c r="K74" s="32">
+        <v>0</v>
+      </c>
+      <c r="L74" s="11"/>
+      <c r="M74" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C15:K15 C24:K24">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:K40 C49:K49">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C65:K65 C74:K74">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -433,7 +3078,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -442,18 +3087,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -462,7 +3107,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -471,18 +3116,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -491,7 +3136,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -500,18 +3145,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -520,7 +3165,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -529,7 +3174,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61E8F04C-39C8-452D-804A-56479D2B85EE}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F961387-F1C3-4D87-AD2E-43D66A516BAF}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="38">
   <si>
     <t>Skybrook</t>
   </si>
@@ -122,6 +122,39 @@
   </si>
   <si>
     <t>Kaylan Adams</t>
+  </si>
+  <si>
+    <t>Bruce Atkins</t>
+  </si>
+  <si>
+    <t>Michael McHugh</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Ben Linck</t>
+  </si>
+  <si>
+    <t>Charlotte Hayes</t>
+  </si>
+  <si>
+    <t>Curtis Lynn</t>
+  </si>
+  <si>
+    <t>Alex Palmer</t>
+  </si>
+  <si>
+    <t>Back 9</t>
+  </si>
+  <si>
+    <t>Megan Serian</t>
+  </si>
+  <si>
+    <t>Nick Coglianese</t>
+  </si>
+  <si>
+    <t>Red</t>
   </si>
 </sst>
 </file>
@@ -498,7 +531,47 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -859,15 +932,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:M74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:AA99"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:13" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:27" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -896,8 +970,36 @@
         <v>21</v>
       </c>
       <c r="M2" s="34"/>
-    </row>
-    <row r="3" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="4"/>
+      <c r="X2" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA2" s="34"/>
+    </row>
+    <row r="3" spans="2:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="36" t="s">
         <v>8</v>
       </c>
@@ -928,8 +1030,38 @@
         <v>6</v>
       </c>
       <c r="M3" s="39"/>
-    </row>
-    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P3" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" s="6">
+        <v>3</v>
+      </c>
+      <c r="S3" s="6">
+        <v>3</v>
+      </c>
+      <c r="T3" s="6">
+        <v>2</v>
+      </c>
+      <c r="U3" s="6">
+        <v>8</v>
+      </c>
+      <c r="V3" s="6">
+        <v>33</v>
+      </c>
+      <c r="W3" s="2"/>
+      <c r="X3" s="38">
+        <v>8</v>
+      </c>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="43">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="39"/>
+    </row>
+    <row r="4" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="37"/>
       <c r="C4" s="7" t="s">
         <v>7</v>
@@ -954,8 +1086,32 @@
       <c r="K4" s="41"/>
       <c r="L4" s="44"/>
       <c r="M4" s="41"/>
-    </row>
-    <row r="5" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P4" s="37"/>
+      <c r="Q4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" s="8">
+        <v>2</v>
+      </c>
+      <c r="S4" s="8">
+        <v>2</v>
+      </c>
+      <c r="T4" s="8">
+        <v>2</v>
+      </c>
+      <c r="U4" s="8">
+        <v>1</v>
+      </c>
+      <c r="V4" s="8">
+        <v>1</v>
+      </c>
+      <c r="W4" s="2"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="41"/>
+    </row>
+    <row r="5" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="36" t="s">
         <v>21</v>
       </c>
@@ -982,8 +1138,34 @@
       <c r="K5" s="42"/>
       <c r="L5" s="45"/>
       <c r="M5" s="42"/>
-    </row>
-    <row r="6" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="10">
+        <v>0</v>
+      </c>
+      <c r="S5" s="10">
+        <v>0</v>
+      </c>
+      <c r="T5" s="10">
+        <v>0</v>
+      </c>
+      <c r="U5" s="10">
+        <v>0</v>
+      </c>
+      <c r="V5" s="10">
+        <v>46</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="37"/>
+      <c r="Y5" s="42"/>
+      <c r="Z5" s="45"/>
+      <c r="AA5" s="42"/>
+    </row>
+    <row r="6" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="37"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
@@ -1008,8 +1190,32 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P6" s="37"/>
+      <c r="Q6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
+      </c>
+      <c r="S6" s="8">
+        <v>0</v>
+      </c>
+      <c r="T6" s="8">
+        <v>0</v>
+      </c>
+      <c r="U6" s="8">
+        <v>0</v>
+      </c>
+      <c r="V6" s="8">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11"/>
+    </row>
+    <row r="7" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -1022,8 +1228,20 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="2:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P7" s="2"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="2"/>
+    </row>
+    <row r="8" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="12" t="s">
         <v>8</v>
       </c>
@@ -1050,8 +1268,34 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" s="11">
+        <v>24</v>
+      </c>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="X8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="2"/>
+    </row>
+    <row r="9" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
@@ -1084,8 +1328,40 @@
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>1</v>
+      </c>
+      <c r="R9" s="18">
+        <v>2</v>
+      </c>
+      <c r="S9" s="19">
+        <v>3</v>
+      </c>
+      <c r="T9" s="17">
+        <v>4</v>
+      </c>
+      <c r="U9" s="18">
+        <v>5</v>
+      </c>
+      <c r="V9" s="19">
+        <v>6</v>
+      </c>
+      <c r="W9" s="17">
+        <v>7</v>
+      </c>
+      <c r="X9" s="18">
+        <v>8</v>
+      </c>
+      <c r="Y9" s="19">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="2"/>
+    </row>
+    <row r="10" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
@@ -1120,8 +1396,42 @@
         <v>36</v>
       </c>
       <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>4</v>
+      </c>
+      <c r="R10" s="11">
+        <v>5</v>
+      </c>
+      <c r="S10" s="21">
+        <v>3</v>
+      </c>
+      <c r="T10" s="22">
+        <v>4</v>
+      </c>
+      <c r="U10" s="11">
+        <v>4</v>
+      </c>
+      <c r="V10" s="21">
+        <v>3</v>
+      </c>
+      <c r="W10" s="22">
+        <v>5</v>
+      </c>
+      <c r="X10" s="11">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="21">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="11">
+        <v>36</v>
+      </c>
+      <c r="AA10" s="2"/>
+    </row>
+    <row r="11" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
@@ -1154,8 +1464,40 @@
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>7</v>
+      </c>
+      <c r="R11" s="11">
+        <v>17</v>
+      </c>
+      <c r="S11" s="21">
+        <v>15</v>
+      </c>
+      <c r="T11" s="22">
+        <v>1</v>
+      </c>
+      <c r="U11" s="11">
+        <v>11</v>
+      </c>
+      <c r="V11" s="21">
+        <v>9</v>
+      </c>
+      <c r="W11" s="22">
+        <v>13</v>
+      </c>
+      <c r="X11" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="21">
+        <v>3</v>
+      </c>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="2"/>
+    </row>
+    <row r="12" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B12" s="23" t="s">
         <v>17</v>
       </c>
@@ -1192,8 +1534,44 @@
       <c r="M12" s="27">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P12" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="24">
+        <v>5</v>
+      </c>
+      <c r="R12" s="25">
+        <v>5</v>
+      </c>
+      <c r="S12" s="26">
+        <v>4</v>
+      </c>
+      <c r="T12" s="24">
+        <v>5</v>
+      </c>
+      <c r="U12" s="25">
+        <v>4</v>
+      </c>
+      <c r="V12" s="26">
+        <v>4</v>
+      </c>
+      <c r="W12" s="24">
+        <v>6</v>
+      </c>
+      <c r="X12" s="25">
+        <v>7</v>
+      </c>
+      <c r="Y12" s="26">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="11">
+        <v>45</v>
+      </c>
+      <c r="AA12" s="27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
@@ -1226,8 +1604,40 @@
       </c>
       <c r="L13" s="27"/>
       <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1</v>
+      </c>
+      <c r="S13" s="21">
+        <v>1</v>
+      </c>
+      <c r="T13" s="22">
+        <v>2</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1</v>
+      </c>
+      <c r="V13" s="21">
+        <v>1</v>
+      </c>
+      <c r="W13" s="22">
+        <v>1</v>
+      </c>
+      <c r="X13" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="21">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="2"/>
+    </row>
+    <row r="14" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B14" s="20" t="s">
         <v>19</v>
       </c>
@@ -1264,8 +1674,44 @@
       <c r="M14" s="27">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>4</v>
+      </c>
+      <c r="R14" s="11">
+        <v>4</v>
+      </c>
+      <c r="S14" s="21">
+        <v>3</v>
+      </c>
+      <c r="T14" s="22">
+        <v>3</v>
+      </c>
+      <c r="U14" s="11">
+        <v>3</v>
+      </c>
+      <c r="V14" s="21">
+        <v>3</v>
+      </c>
+      <c r="W14" s="22">
+        <v>5</v>
+      </c>
+      <c r="X14" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="21">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="28">
+        <v>33</v>
+      </c>
+      <c r="AA14" s="27">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="29" t="s">
         <v>20</v>
       </c>
@@ -1298,8 +1744,40 @@
       </c>
       <c r="L15" s="11"/>
       <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P15" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="30">
+        <v>1</v>
+      </c>
+      <c r="R15" s="31">
+        <v>1</v>
+      </c>
+      <c r="S15" s="32">
+        <v>1</v>
+      </c>
+      <c r="T15" s="30">
+        <v>1</v>
+      </c>
+      <c r="U15" s="31">
+        <v>1</v>
+      </c>
+      <c r="V15" s="32">
+        <v>1</v>
+      </c>
+      <c r="W15" s="30">
+        <v>0</v>
+      </c>
+      <c r="X15" s="31">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="32">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="2"/>
+    </row>
+    <row r="16" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -1312,8 +1790,20 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="2:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P16" s="2"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="2"/>
+    </row>
+    <row r="17" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="12" t="s">
         <v>21</v>
       </c>
@@ -1340,8 +1830,34 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P17" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R17" s="11">
+        <v>22</v>
+      </c>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="U17" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
@@ -1374,8 +1890,40 @@
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="27"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>1</v>
+      </c>
+      <c r="R18" s="18">
+        <v>2</v>
+      </c>
+      <c r="S18" s="19">
+        <v>3</v>
+      </c>
+      <c r="T18" s="17">
+        <v>4</v>
+      </c>
+      <c r="U18" s="18">
+        <v>5</v>
+      </c>
+      <c r="V18" s="19">
+        <v>6</v>
+      </c>
+      <c r="W18" s="17">
+        <v>7</v>
+      </c>
+      <c r="X18" s="18">
+        <v>8</v>
+      </c>
+      <c r="Y18" s="19">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="27"/>
+    </row>
+    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B19" s="20" t="s">
         <v>15</v>
       </c>
@@ -1410,8 +1958,42 @@
         <v>36</v>
       </c>
       <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>4</v>
+      </c>
+      <c r="R19" s="11">
+        <v>5</v>
+      </c>
+      <c r="S19" s="21">
+        <v>3</v>
+      </c>
+      <c r="T19" s="22">
+        <v>4</v>
+      </c>
+      <c r="U19" s="11">
+        <v>4</v>
+      </c>
+      <c r="V19" s="21">
+        <v>3</v>
+      </c>
+      <c r="W19" s="22">
+        <v>5</v>
+      </c>
+      <c r="X19" s="11">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="21">
+        <v>4</v>
+      </c>
+      <c r="Z19" s="11">
+        <v>36</v>
+      </c>
+      <c r="AA19" s="2"/>
+    </row>
+    <row r="20" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B20" s="20" t="s">
         <v>16</v>
       </c>
@@ -1444,8 +2026,40 @@
       </c>
       <c r="L20" s="11"/>
       <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>7</v>
+      </c>
+      <c r="R20" s="11">
+        <v>17</v>
+      </c>
+      <c r="S20" s="21">
+        <v>15</v>
+      </c>
+      <c r="T20" s="22">
+        <v>1</v>
+      </c>
+      <c r="U20" s="11">
+        <v>11</v>
+      </c>
+      <c r="V20" s="21">
+        <v>9</v>
+      </c>
+      <c r="W20" s="22">
+        <v>13</v>
+      </c>
+      <c r="X20" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="21">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="2"/>
+    </row>
+    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
@@ -1482,8 +2096,44 @@
       <c r="M21" s="27">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P21" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q21" s="24">
+        <v>7</v>
+      </c>
+      <c r="R21" s="25">
+        <v>7</v>
+      </c>
+      <c r="S21" s="26">
+        <v>5</v>
+      </c>
+      <c r="T21" s="24">
+        <v>6</v>
+      </c>
+      <c r="U21" s="25">
+        <v>6</v>
+      </c>
+      <c r="V21" s="26">
+        <v>5</v>
+      </c>
+      <c r="W21" s="24">
+        <v>6</v>
+      </c>
+      <c r="X21" s="25">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="26">
+        <v>7</v>
+      </c>
+      <c r="Z21" s="11">
+        <v>57</v>
+      </c>
+      <c r="AA21" s="27">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B22" s="20" t="s">
         <v>18</v>
       </c>
@@ -1516,8 +2166,40 @@
       </c>
       <c r="L22" s="27"/>
       <c r="M22" s="2"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="11">
+        <v>1</v>
+      </c>
+      <c r="S22" s="21">
+        <v>1</v>
+      </c>
+      <c r="T22" s="22">
+        <v>2</v>
+      </c>
+      <c r="U22" s="11">
+        <v>1</v>
+      </c>
+      <c r="V22" s="21">
+        <v>1</v>
+      </c>
+      <c r="W22" s="22">
+        <v>1</v>
+      </c>
+      <c r="X22" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="21">
+        <v>2</v>
+      </c>
+      <c r="Z22" s="27"/>
+      <c r="AA22" s="2"/>
+    </row>
+    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B23" s="20" t="s">
         <v>19</v>
       </c>
@@ -1554,8 +2236,44 @@
       <c r="M23" s="27">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P23" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="22">
+        <v>6</v>
+      </c>
+      <c r="R23" s="11">
+        <v>6</v>
+      </c>
+      <c r="S23" s="21">
+        <v>4</v>
+      </c>
+      <c r="T23" s="22">
+        <v>4</v>
+      </c>
+      <c r="U23" s="11">
+        <v>5</v>
+      </c>
+      <c r="V23" s="21">
+        <v>4</v>
+      </c>
+      <c r="W23" s="22">
+        <v>5</v>
+      </c>
+      <c r="X23" s="11">
+        <v>7</v>
+      </c>
+      <c r="Y23" s="21">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="28">
+        <v>46</v>
+      </c>
+      <c r="AA23" s="27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="29" t="s">
         <v>20</v>
       </c>
@@ -1588,9 +2306,41 @@
       </c>
       <c r="L24" s="11"/>
       <c r="M24" s="2"/>
-    </row>
-    <row r="26" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="2:13" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P24" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q24" s="30">
+        <v>0</v>
+      </c>
+      <c r="R24" s="31">
+        <v>0</v>
+      </c>
+      <c r="S24" s="32">
+        <v>0</v>
+      </c>
+      <c r="T24" s="30">
+        <v>0</v>
+      </c>
+      <c r="U24" s="31">
+        <v>0</v>
+      </c>
+      <c r="V24" s="32">
+        <v>0</v>
+      </c>
+      <c r="W24" s="30">
+        <v>0</v>
+      </c>
+      <c r="X24" s="31">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="32">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="2"/>
+    </row>
+    <row r="26" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="2:27" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
@@ -1619,8 +2369,36 @@
         <v>23</v>
       </c>
       <c r="M27" s="34"/>
-    </row>
-    <row r="28" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="4"/>
+      <c r="X27" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y27" s="34"/>
+      <c r="Z27" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA27" s="34"/>
+    </row>
+    <row r="28" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="36" t="s">
         <v>22</v>
       </c>
@@ -1651,8 +2429,38 @@
         <v>7</v>
       </c>
       <c r="M28" s="39"/>
-    </row>
-    <row r="29" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P28" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="R28" s="6">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6">
+        <v>1</v>
+      </c>
+      <c r="T28" s="6">
+        <v>1</v>
+      </c>
+      <c r="U28" s="6">
+        <v>2</v>
+      </c>
+      <c r="V28" s="6">
+        <v>39</v>
+      </c>
+      <c r="W28" s="2"/>
+      <c r="X28" s="38">
+        <v>2</v>
+      </c>
+      <c r="Y28" s="39"/>
+      <c r="Z28" s="43">
+        <v>6</v>
+      </c>
+      <c r="AA28" s="39"/>
+    </row>
+    <row r="29" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="37"/>
       <c r="C29" s="7" t="s">
         <v>7</v>
@@ -1677,8 +2485,32 @@
       <c r="K29" s="41"/>
       <c r="L29" s="44"/>
       <c r="M29" s="41"/>
-    </row>
-    <row r="30" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P29" s="37"/>
+      <c r="Q29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="R29" s="8">
+        <v>0</v>
+      </c>
+      <c r="S29" s="8">
+        <v>1</v>
+      </c>
+      <c r="T29" s="8">
+        <v>1</v>
+      </c>
+      <c r="U29" s="8">
+        <v>0</v>
+      </c>
+      <c r="V29" s="8">
+        <v>0</v>
+      </c>
+      <c r="W29" s="2"/>
+      <c r="X29" s="40"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="44"/>
+      <c r="AA29" s="41"/>
+    </row>
+    <row r="30" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="36" t="s">
         <v>23</v>
       </c>
@@ -1705,8 +2537,34 @@
       <c r="K30" s="42"/>
       <c r="L30" s="45"/>
       <c r="M30" s="42"/>
-    </row>
-    <row r="31" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P30" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="R30" s="10">
+        <v>3</v>
+      </c>
+      <c r="S30" s="10">
+        <v>1</v>
+      </c>
+      <c r="T30" s="10">
+        <v>1</v>
+      </c>
+      <c r="U30" s="10">
+        <v>5</v>
+      </c>
+      <c r="V30" s="10">
+        <v>35</v>
+      </c>
+      <c r="W30" s="2"/>
+      <c r="X30" s="37"/>
+      <c r="Y30" s="42"/>
+      <c r="Z30" s="45"/>
+      <c r="AA30" s="42"/>
+    </row>
+    <row r="31" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="37"/>
       <c r="C31" s="7" t="s">
         <v>7</v>
@@ -1731,8 +2589,32 @@
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P31" s="37"/>
+      <c r="Q31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="R31" s="8">
+        <v>2</v>
+      </c>
+      <c r="S31" s="8">
+        <v>1</v>
+      </c>
+      <c r="T31" s="8">
+        <v>1</v>
+      </c>
+      <c r="U31" s="8">
+        <v>1</v>
+      </c>
+      <c r="V31" s="8">
+        <v>1</v>
+      </c>
+      <c r="W31" s="2"/>
+      <c r="X31" s="11"/>
+      <c r="Y31" s="11"/>
+      <c r="Z31" s="11"/>
+      <c r="AA31" s="11"/>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B32" s="2"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -1745,8 +2627,20 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="2"/>
-    </row>
-    <row r="33" spans="2:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P32" s="2"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="2"/>
+    </row>
+    <row r="33" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="12" t="s">
         <v>22</v>
       </c>
@@ -1773,8 +2667,34 @@
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
       <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P33" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q33" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R33" s="11">
+        <v>30</v>
+      </c>
+      <c r="S33" s="11"/>
+      <c r="T33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="U33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="V33" s="11"/>
+      <c r="W33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="X33" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y33" s="11"/>
+      <c r="Z33" s="11"/>
+      <c r="AA33" s="2"/>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B34" s="16" t="s">
         <v>14</v>
       </c>
@@ -1807,8 +2727,40 @@
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="2"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P34" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q34" s="17">
+        <v>1</v>
+      </c>
+      <c r="R34" s="18">
+        <v>2</v>
+      </c>
+      <c r="S34" s="19">
+        <v>3</v>
+      </c>
+      <c r="T34" s="17">
+        <v>4</v>
+      </c>
+      <c r="U34" s="18">
+        <v>5</v>
+      </c>
+      <c r="V34" s="19">
+        <v>6</v>
+      </c>
+      <c r="W34" s="17">
+        <v>7</v>
+      </c>
+      <c r="X34" s="18">
+        <v>8</v>
+      </c>
+      <c r="Y34" s="19">
+        <v>9</v>
+      </c>
+      <c r="Z34" s="11"/>
+      <c r="AA34" s="2"/>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B35" s="20" t="s">
         <v>15</v>
       </c>
@@ -1843,8 +2795,42 @@
         <v>36</v>
       </c>
       <c r="M35" s="2"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P35" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>4</v>
+      </c>
+      <c r="R35" s="11">
+        <v>5</v>
+      </c>
+      <c r="S35" s="21">
+        <v>4</v>
+      </c>
+      <c r="T35" s="22">
+        <v>4</v>
+      </c>
+      <c r="U35" s="11">
+        <v>3</v>
+      </c>
+      <c r="V35" s="21">
+        <v>4</v>
+      </c>
+      <c r="W35" s="22">
+        <v>3</v>
+      </c>
+      <c r="X35" s="11">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="21">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="11">
+        <v>36</v>
+      </c>
+      <c r="AA35" s="2"/>
+    </row>
+    <row r="36" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B36" s="20" t="s">
         <v>16</v>
       </c>
@@ -1877,8 +2863,40 @@
       </c>
       <c r="L36" s="11"/>
       <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P36" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q36" s="11">
+        <v>4</v>
+      </c>
+      <c r="R36" s="11">
+        <v>12</v>
+      </c>
+      <c r="S36" s="21">
+        <v>14</v>
+      </c>
+      <c r="T36" s="22">
+        <v>6</v>
+      </c>
+      <c r="U36" s="11">
+        <v>16</v>
+      </c>
+      <c r="V36" s="21">
+        <v>8</v>
+      </c>
+      <c r="W36" s="22">
+        <v>18</v>
+      </c>
+      <c r="X36" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y36" s="21">
+        <v>10</v>
+      </c>
+      <c r="Z36" s="11"/>
+      <c r="AA36" s="2"/>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B37" s="23" t="s">
         <v>17</v>
       </c>
@@ -1915,8 +2933,44 @@
       <c r="M37" s="27">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P37" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q37" s="24">
+        <v>7</v>
+      </c>
+      <c r="R37" s="25">
+        <v>8</v>
+      </c>
+      <c r="S37" s="26">
+        <v>5</v>
+      </c>
+      <c r="T37" s="24">
+        <v>5</v>
+      </c>
+      <c r="U37" s="25">
+        <v>6</v>
+      </c>
+      <c r="V37" s="26">
+        <v>6</v>
+      </c>
+      <c r="W37" s="24">
+        <v>6</v>
+      </c>
+      <c r="X37" s="25">
+        <v>5</v>
+      </c>
+      <c r="Y37" s="26">
+        <v>6</v>
+      </c>
+      <c r="Z37" s="11">
+        <v>54</v>
+      </c>
+      <c r="AA37" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B38" s="20" t="s">
         <v>18</v>
       </c>
@@ -1949,8 +3003,40 @@
       </c>
       <c r="L38" s="27"/>
       <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P38" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q38" s="22">
+        <v>2</v>
+      </c>
+      <c r="R38" s="11">
+        <v>2</v>
+      </c>
+      <c r="S38" s="21">
+        <v>1</v>
+      </c>
+      <c r="T38" s="22">
+        <v>2</v>
+      </c>
+      <c r="U38" s="11">
+        <v>1</v>
+      </c>
+      <c r="V38" s="21">
+        <v>2</v>
+      </c>
+      <c r="W38" s="22">
+        <v>1</v>
+      </c>
+      <c r="X38" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y38" s="21">
+        <v>2</v>
+      </c>
+      <c r="Z38" s="27"/>
+      <c r="AA38" s="2"/>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B39" s="20" t="s">
         <v>19</v>
       </c>
@@ -1987,8 +3073,44 @@
       <c r="M39" s="27">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q39" s="22">
+        <v>5</v>
+      </c>
+      <c r="R39" s="11">
+        <v>6</v>
+      </c>
+      <c r="S39" s="21">
+        <v>4</v>
+      </c>
+      <c r="T39" s="22">
+        <v>3</v>
+      </c>
+      <c r="U39" s="11">
+        <v>5</v>
+      </c>
+      <c r="V39" s="21">
+        <v>4</v>
+      </c>
+      <c r="W39" s="22">
+        <v>5</v>
+      </c>
+      <c r="X39" s="11">
+        <v>3</v>
+      </c>
+      <c r="Y39" s="21">
+        <v>4</v>
+      </c>
+      <c r="Z39" s="28">
+        <v>39</v>
+      </c>
+      <c r="AA39" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="29" t="s">
         <v>20</v>
       </c>
@@ -2021,8 +3143,40 @@
       </c>
       <c r="L40" s="11"/>
       <c r="M40" s="2"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P40" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="30">
+        <v>0</v>
+      </c>
+      <c r="R40" s="31">
+        <v>0</v>
+      </c>
+      <c r="S40" s="32">
+        <v>0</v>
+      </c>
+      <c r="T40" s="30">
+        <v>1</v>
+      </c>
+      <c r="U40" s="31">
+        <v>0</v>
+      </c>
+      <c r="V40" s="32">
+        <v>0</v>
+      </c>
+      <c r="W40" s="30">
+        <v>0</v>
+      </c>
+      <c r="X40" s="31">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="32">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="11"/>
+      <c r="AA40" s="2"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B41" s="2"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -2035,8 +3189,20 @@
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="2"/>
-    </row>
-    <row r="42" spans="2:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P41" s="2"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="11"/>
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="11"/>
+      <c r="Z41" s="11"/>
+      <c r="AA41" s="2"/>
+    </row>
+    <row r="42" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="12" t="s">
         <v>23</v>
       </c>
@@ -2063,8 +3229,34 @@
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
       <c r="M42" s="2"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P42" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q42" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R42" s="11">
+        <v>20</v>
+      </c>
+      <c r="S42" s="11"/>
+      <c r="T42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="U42" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="V42" s="11"/>
+      <c r="W42" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="X42" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y42" s="11"/>
+      <c r="Z42" s="11"/>
+      <c r="AA42" s="2"/>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B43" s="16" t="s">
         <v>14</v>
       </c>
@@ -2097,8 +3289,40 @@
       </c>
       <c r="L43" s="11"/>
       <c r="M43" s="27"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q43" s="17">
+        <v>1</v>
+      </c>
+      <c r="R43" s="18">
+        <v>2</v>
+      </c>
+      <c r="S43" s="19">
+        <v>3</v>
+      </c>
+      <c r="T43" s="17">
+        <v>4</v>
+      </c>
+      <c r="U43" s="18">
+        <v>5</v>
+      </c>
+      <c r="V43" s="19">
+        <v>6</v>
+      </c>
+      <c r="W43" s="17">
+        <v>7</v>
+      </c>
+      <c r="X43" s="18">
+        <v>8</v>
+      </c>
+      <c r="Y43" s="19">
+        <v>9</v>
+      </c>
+      <c r="Z43" s="11"/>
+      <c r="AA43" s="27"/>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B44" s="20" t="s">
         <v>15</v>
       </c>
@@ -2133,8 +3357,42 @@
         <v>36</v>
       </c>
       <c r="M44" s="2"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P44" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q44" s="11">
+        <v>4</v>
+      </c>
+      <c r="R44" s="11">
+        <v>5</v>
+      </c>
+      <c r="S44" s="21">
+        <v>4</v>
+      </c>
+      <c r="T44" s="22">
+        <v>4</v>
+      </c>
+      <c r="U44" s="11">
+        <v>3</v>
+      </c>
+      <c r="V44" s="21">
+        <v>4</v>
+      </c>
+      <c r="W44" s="22">
+        <v>3</v>
+      </c>
+      <c r="X44" s="11">
+        <v>4</v>
+      </c>
+      <c r="Y44" s="21">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="11">
+        <v>36</v>
+      </c>
+      <c r="AA44" s="2"/>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B45" s="20" t="s">
         <v>16</v>
       </c>
@@ -2167,8 +3425,40 @@
       </c>
       <c r="L45" s="11"/>
       <c r="M45" s="2"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P45" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q45" s="11">
+        <v>4</v>
+      </c>
+      <c r="R45" s="11">
+        <v>12</v>
+      </c>
+      <c r="S45" s="21">
+        <v>14</v>
+      </c>
+      <c r="T45" s="22">
+        <v>6</v>
+      </c>
+      <c r="U45" s="11">
+        <v>16</v>
+      </c>
+      <c r="V45" s="21">
+        <v>8</v>
+      </c>
+      <c r="W45" s="22">
+        <v>18</v>
+      </c>
+      <c r="X45" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y45" s="21">
+        <v>10</v>
+      </c>
+      <c r="Z45" s="11"/>
+      <c r="AA45" s="2"/>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B46" s="23" t="s">
         <v>17</v>
       </c>
@@ -2205,8 +3495,44 @@
       <c r="M46" s="27">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P46" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q46" s="24">
+        <v>5</v>
+      </c>
+      <c r="R46" s="25">
+        <v>6</v>
+      </c>
+      <c r="S46" s="26">
+        <v>4</v>
+      </c>
+      <c r="T46" s="24">
+        <v>6</v>
+      </c>
+      <c r="U46" s="25">
+        <v>4</v>
+      </c>
+      <c r="V46" s="26">
+        <v>5</v>
+      </c>
+      <c r="W46" s="24">
+        <v>3</v>
+      </c>
+      <c r="X46" s="25">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="26">
+        <v>7</v>
+      </c>
+      <c r="Z46" s="11">
+        <v>45</v>
+      </c>
+      <c r="AA46" s="27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B47" s="20" t="s">
         <v>18</v>
       </c>
@@ -2239,8 +3565,40 @@
       </c>
       <c r="L47" s="27"/>
       <c r="M47" s="2"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P47" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q47" s="22">
+        <v>1</v>
+      </c>
+      <c r="R47" s="11">
+        <v>1</v>
+      </c>
+      <c r="S47" s="21">
+        <v>1</v>
+      </c>
+      <c r="T47" s="22">
+        <v>1</v>
+      </c>
+      <c r="U47" s="11">
+        <v>1</v>
+      </c>
+      <c r="V47" s="21">
+        <v>1</v>
+      </c>
+      <c r="W47" s="22">
+        <v>1</v>
+      </c>
+      <c r="X47" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="27"/>
+      <c r="AA47" s="2"/>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B48" s="20" t="s">
         <v>19</v>
       </c>
@@ -2277,8 +3635,44 @@
       <c r="M48" s="27">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P48" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q48" s="22">
+        <v>4</v>
+      </c>
+      <c r="R48" s="11">
+        <v>5</v>
+      </c>
+      <c r="S48" s="21">
+        <v>3</v>
+      </c>
+      <c r="T48" s="22">
+        <v>5</v>
+      </c>
+      <c r="U48" s="11">
+        <v>3</v>
+      </c>
+      <c r="V48" s="21">
+        <v>4</v>
+      </c>
+      <c r="W48" s="22">
+        <v>2</v>
+      </c>
+      <c r="X48" s="11">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="21">
+        <v>6</v>
+      </c>
+      <c r="Z48" s="28">
+        <v>35</v>
+      </c>
+      <c r="AA48" s="27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="29" t="s">
         <v>20</v>
       </c>
@@ -2311,9 +3705,41 @@
       </c>
       <c r="L49" s="11"/>
       <c r="M49" s="2"/>
-    </row>
-    <row r="51" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P49" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="30">
+        <v>1</v>
+      </c>
+      <c r="R49" s="31">
+        <v>1</v>
+      </c>
+      <c r="S49" s="32">
+        <v>1</v>
+      </c>
+      <c r="T49" s="30">
+        <v>0</v>
+      </c>
+      <c r="U49" s="31">
+        <v>1</v>
+      </c>
+      <c r="V49" s="32">
+        <v>0</v>
+      </c>
+      <c r="W49" s="30">
+        <v>1</v>
+      </c>
+      <c r="X49" s="31">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="32">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="2"/>
+    </row>
+    <row r="51" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="2:27" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
         <v>24</v>
       </c>
@@ -2342,8 +3768,36 @@
         <v>26</v>
       </c>
       <c r="M52" s="34"/>
-    </row>
-    <row r="53" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="4"/>
+      <c r="X52" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y52" s="34"/>
+      <c r="Z52" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA52" s="34"/>
+    </row>
+    <row r="53" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>25</v>
       </c>
@@ -2374,8 +3828,38 @@
         <v>4</v>
       </c>
       <c r="M53" s="39"/>
-    </row>
-    <row r="54" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P53" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="R53" s="6">
+        <v>1</v>
+      </c>
+      <c r="S53" s="6">
+        <v>3</v>
+      </c>
+      <c r="T53" s="6">
+        <v>2</v>
+      </c>
+      <c r="U53" s="6">
+        <v>6</v>
+      </c>
+      <c r="V53" s="6">
+        <v>37</v>
+      </c>
+      <c r="W53" s="2"/>
+      <c r="X53" s="38">
+        <v>7</v>
+      </c>
+      <c r="Y53" s="39"/>
+      <c r="Z53" s="43">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="39"/>
+    </row>
+    <row r="54" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="37"/>
       <c r="C54" s="7" t="s">
         <v>7</v>
@@ -2400,8 +3884,32 @@
       <c r="K54" s="41"/>
       <c r="L54" s="44"/>
       <c r="M54" s="41"/>
-    </row>
-    <row r="55" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P54" s="37"/>
+      <c r="Q54" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="R54" s="8">
+        <v>1</v>
+      </c>
+      <c r="S54" s="8">
+        <v>2</v>
+      </c>
+      <c r="T54" s="8">
+        <v>2</v>
+      </c>
+      <c r="U54" s="8">
+        <v>1</v>
+      </c>
+      <c r="V54" s="8">
+        <v>1</v>
+      </c>
+      <c r="W54" s="2"/>
+      <c r="X54" s="40"/>
+      <c r="Y54" s="41"/>
+      <c r="Z54" s="44"/>
+      <c r="AA54" s="41"/>
+    </row>
+    <row r="55" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="36" t="s">
         <v>26</v>
       </c>
@@ -2428,8 +3936,34 @@
       <c r="K55" s="42"/>
       <c r="L55" s="45"/>
       <c r="M55" s="42"/>
-    </row>
-    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P55" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q55" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="R55" s="10">
+        <v>1</v>
+      </c>
+      <c r="S55" s="10">
+        <v>0</v>
+      </c>
+      <c r="T55" s="10">
+        <v>0</v>
+      </c>
+      <c r="U55" s="10">
+        <v>1</v>
+      </c>
+      <c r="V55" s="10">
+        <v>48</v>
+      </c>
+      <c r="W55" s="2"/>
+      <c r="X55" s="37"/>
+      <c r="Y55" s="42"/>
+      <c r="Z55" s="45"/>
+      <c r="AA55" s="42"/>
+    </row>
+    <row r="56" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="37"/>
       <c r="C56" s="7" t="s">
         <v>7</v>
@@ -2454,8 +3988,32 @@
       <c r="K56" s="11"/>
       <c r="L56" s="11"/>
       <c r="M56" s="11"/>
-    </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P56" s="37"/>
+      <c r="Q56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="R56" s="8">
+        <v>1</v>
+      </c>
+      <c r="S56" s="8">
+        <v>0</v>
+      </c>
+      <c r="T56" s="8">
+        <v>0</v>
+      </c>
+      <c r="U56" s="8">
+        <v>0</v>
+      </c>
+      <c r="V56" s="8">
+        <v>0</v>
+      </c>
+      <c r="W56" s="2"/>
+      <c r="X56" s="11"/>
+      <c r="Y56" s="11"/>
+      <c r="Z56" s="11"/>
+      <c r="AA56" s="11"/>
+    </row>
+    <row r="57" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B57" s="2"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
@@ -2468,8 +4026,20 @@
       <c r="K57" s="11"/>
       <c r="L57" s="11"/>
       <c r="M57" s="2"/>
-    </row>
-    <row r="58" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P57" s="2"/>
+      <c r="Q57" s="11"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="11"/>
+      <c r="T57" s="11"/>
+      <c r="U57" s="11"/>
+      <c r="V57" s="11"/>
+      <c r="W57" s="11"/>
+      <c r="X57" s="11"/>
+      <c r="Y57" s="11"/>
+      <c r="Z57" s="11"/>
+      <c r="AA57" s="2"/>
+    </row>
+    <row r="58" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="12" t="s">
         <v>25</v>
       </c>
@@ -2496,8 +4066,34 @@
       <c r="K58" s="11"/>
       <c r="L58" s="11"/>
       <c r="M58" s="2"/>
-    </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P58" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q58" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R58" s="11">
+        <v>28</v>
+      </c>
+      <c r="S58" s="11"/>
+      <c r="T58" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="U58" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="V58" s="11"/>
+      <c r="W58" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="X58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y58" s="11"/>
+      <c r="Z58" s="11"/>
+      <c r="AA58" s="2"/>
+    </row>
+    <row r="59" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B59" s="16" t="s">
         <v>14</v>
       </c>
@@ -2530,8 +4126,40 @@
       </c>
       <c r="L59" s="11"/>
       <c r="M59" s="2"/>
-    </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P59" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q59" s="17">
+        <v>1</v>
+      </c>
+      <c r="R59" s="18">
+        <v>2</v>
+      </c>
+      <c r="S59" s="19">
+        <v>3</v>
+      </c>
+      <c r="T59" s="17">
+        <v>4</v>
+      </c>
+      <c r="U59" s="18">
+        <v>5</v>
+      </c>
+      <c r="V59" s="19">
+        <v>6</v>
+      </c>
+      <c r="W59" s="17">
+        <v>7</v>
+      </c>
+      <c r="X59" s="18">
+        <v>8</v>
+      </c>
+      <c r="Y59" s="19">
+        <v>9</v>
+      </c>
+      <c r="Z59" s="11"/>
+      <c r="AA59" s="2"/>
+    </row>
+    <row r="60" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B60" s="20" t="s">
         <v>15</v>
       </c>
@@ -2566,8 +4194,42 @@
         <v>36</v>
       </c>
       <c r="M60" s="2"/>
-    </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P60" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q60" s="11">
+        <v>4</v>
+      </c>
+      <c r="R60" s="11">
+        <v>3</v>
+      </c>
+      <c r="S60" s="21">
+        <v>4</v>
+      </c>
+      <c r="T60" s="22">
+        <v>5</v>
+      </c>
+      <c r="U60" s="11">
+        <v>4</v>
+      </c>
+      <c r="V60" s="21">
+        <v>4</v>
+      </c>
+      <c r="W60" s="22">
+        <v>3</v>
+      </c>
+      <c r="X60" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="21">
+        <v>4</v>
+      </c>
+      <c r="Z60" s="11">
+        <v>36</v>
+      </c>
+      <c r="AA60" s="2"/>
+    </row>
+    <row r="61" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B61" s="20" t="s">
         <v>16</v>
       </c>
@@ -2600,8 +4262,40 @@
       </c>
       <c r="L61" s="11"/>
       <c r="M61" s="2"/>
-    </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P61" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q61" s="11">
+        <v>7</v>
+      </c>
+      <c r="R61" s="11">
+        <v>15</v>
+      </c>
+      <c r="S61" s="21">
+        <v>5</v>
+      </c>
+      <c r="T61" s="22">
+        <v>13</v>
+      </c>
+      <c r="U61" s="11">
+        <v>3</v>
+      </c>
+      <c r="V61" s="21">
+        <v>11</v>
+      </c>
+      <c r="W61" s="22">
+        <v>17</v>
+      </c>
+      <c r="X61" s="11">
+        <v>9</v>
+      </c>
+      <c r="Y61" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z61" s="11"/>
+      <c r="AA61" s="2"/>
+    </row>
+    <row r="62" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B62" s="23" t="s">
         <v>17</v>
       </c>
@@ -2609,25 +4303,25 @@
         <v>8</v>
       </c>
       <c r="D62" s="25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E62" s="26">
+        <v>6</v>
+      </c>
+      <c r="F62" s="24">
         <v>8</v>
-      </c>
-      <c r="F62" s="24">
-        <v>10</v>
       </c>
       <c r="G62" s="25">
         <v>8</v>
       </c>
       <c r="H62" s="26">
+        <v>6</v>
+      </c>
+      <c r="I62" s="24">
+        <v>10</v>
+      </c>
+      <c r="J62" s="25">
         <v>8</v>
-      </c>
-      <c r="I62" s="24">
-        <v>6</v>
-      </c>
-      <c r="J62" s="25">
-        <v>10</v>
       </c>
       <c r="K62" s="26">
         <v>8</v>
@@ -2638,8 +4332,44 @@
       <c r="M62" s="27">
         <v>36</v>
       </c>
-    </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P62" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q62" s="24">
+        <v>6</v>
+      </c>
+      <c r="R62" s="25">
+        <v>4</v>
+      </c>
+      <c r="S62" s="26">
+        <v>7</v>
+      </c>
+      <c r="T62" s="24">
+        <v>7</v>
+      </c>
+      <c r="U62" s="25">
+        <v>4</v>
+      </c>
+      <c r="V62" s="26">
+        <v>5</v>
+      </c>
+      <c r="W62" s="24">
+        <v>4</v>
+      </c>
+      <c r="X62" s="25">
+        <v>6</v>
+      </c>
+      <c r="Y62" s="26">
+        <v>8</v>
+      </c>
+      <c r="Z62" s="11">
+        <v>51</v>
+      </c>
+      <c r="AA62" s="27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B63" s="20" t="s">
         <v>18</v>
       </c>
@@ -2672,8 +4402,40 @@
       </c>
       <c r="L63" s="27"/>
       <c r="M63" s="2"/>
-    </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P63" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q63" s="22">
+        <v>2</v>
+      </c>
+      <c r="R63" s="11">
+        <v>1</v>
+      </c>
+      <c r="S63" s="21">
+        <v>2</v>
+      </c>
+      <c r="T63" s="22">
+        <v>1</v>
+      </c>
+      <c r="U63" s="11">
+        <v>2</v>
+      </c>
+      <c r="V63" s="21">
+        <v>1</v>
+      </c>
+      <c r="W63" s="22">
+        <v>1</v>
+      </c>
+      <c r="X63" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y63" s="21">
+        <v>2</v>
+      </c>
+      <c r="Z63" s="27"/>
+      <c r="AA63" s="2"/>
+    </row>
+    <row r="64" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B64" s="20" t="s">
         <v>19</v>
       </c>
@@ -2681,25 +4443,25 @@
         <v>6</v>
       </c>
       <c r="D64" s="11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E64" s="21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F64" s="22">
+        <v>6</v>
+      </c>
+      <c r="G64" s="11">
+        <v>6</v>
+      </c>
+      <c r="H64" s="21">
+        <v>4</v>
+      </c>
+      <c r="I64" s="22">
         <v>8</v>
       </c>
-      <c r="G64" s="11">
-        <v>6</v>
-      </c>
-      <c r="H64" s="21">
-        <v>6</v>
-      </c>
-      <c r="I64" s="22">
-        <v>4</v>
-      </c>
       <c r="J64" s="11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K64" s="21">
         <v>6</v>
@@ -2710,8 +4472,44 @@
       <c r="M64" s="27">
         <v>18</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P64" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q64" s="22">
+        <v>4</v>
+      </c>
+      <c r="R64" s="11">
+        <v>3</v>
+      </c>
+      <c r="S64" s="21">
+        <v>5</v>
+      </c>
+      <c r="T64" s="22">
+        <v>6</v>
+      </c>
+      <c r="U64" s="11">
+        <v>2</v>
+      </c>
+      <c r="V64" s="21">
+        <v>4</v>
+      </c>
+      <c r="W64" s="22">
+        <v>3</v>
+      </c>
+      <c r="X64" s="11">
+        <v>4</v>
+      </c>
+      <c r="Y64" s="21">
+        <v>6</v>
+      </c>
+      <c r="Z64" s="28">
+        <v>37</v>
+      </c>
+      <c r="AA64" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="29" t="s">
         <v>20</v>
       </c>
@@ -2744,8 +4542,40 @@
       </c>
       <c r="L65" s="11"/>
       <c r="M65" s="2"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P65" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q65" s="30">
+        <v>0</v>
+      </c>
+      <c r="R65" s="31">
+        <v>1</v>
+      </c>
+      <c r="S65" s="32">
+        <v>0</v>
+      </c>
+      <c r="T65" s="30">
+        <v>1</v>
+      </c>
+      <c r="U65" s="31">
+        <v>1</v>
+      </c>
+      <c r="V65" s="32">
+        <v>1</v>
+      </c>
+      <c r="W65" s="30">
+        <v>1</v>
+      </c>
+      <c r="X65" s="31">
+        <v>1</v>
+      </c>
+      <c r="Y65" s="32">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="11"/>
+      <c r="AA65" s="2"/>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B66" s="2"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -2758,8 +4588,20 @@
       <c r="K66" s="11"/>
       <c r="L66" s="11"/>
       <c r="M66" s="2"/>
-    </row>
-    <row r="67" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P66" s="2"/>
+      <c r="Q66" s="11"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="11"/>
+      <c r="T66" s="11"/>
+      <c r="U66" s="11"/>
+      <c r="V66" s="11"/>
+      <c r="W66" s="11"/>
+      <c r="X66" s="11"/>
+      <c r="Y66" s="11"/>
+      <c r="Z66" s="11"/>
+      <c r="AA66" s="2"/>
+    </row>
+    <row r="67" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="12" t="s">
         <v>26</v>
       </c>
@@ -2786,8 +4628,34 @@
       <c r="K67" s="11"/>
       <c r="L67" s="11"/>
       <c r="M67" s="2"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P67" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q67" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R67" s="11">
+        <v>27</v>
+      </c>
+      <c r="S67" s="11"/>
+      <c r="T67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="U67" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="V67" s="11"/>
+      <c r="W67" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="X67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y67" s="11"/>
+      <c r="Z67" s="11"/>
+      <c r="AA67" s="2"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B68" s="16" t="s">
         <v>14</v>
       </c>
@@ -2820,8 +4688,40 @@
       </c>
       <c r="L68" s="11"/>
       <c r="M68" s="27"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P68" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q68" s="17">
+        <v>1</v>
+      </c>
+      <c r="R68" s="18">
+        <v>2</v>
+      </c>
+      <c r="S68" s="19">
+        <v>3</v>
+      </c>
+      <c r="T68" s="17">
+        <v>4</v>
+      </c>
+      <c r="U68" s="18">
+        <v>5</v>
+      </c>
+      <c r="V68" s="19">
+        <v>6</v>
+      </c>
+      <c r="W68" s="17">
+        <v>7</v>
+      </c>
+      <c r="X68" s="18">
+        <v>8</v>
+      </c>
+      <c r="Y68" s="19">
+        <v>9</v>
+      </c>
+      <c r="Z68" s="11"/>
+      <c r="AA68" s="27"/>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B69" s="20" t="s">
         <v>15</v>
       </c>
@@ -2856,8 +4756,42 @@
         <v>36</v>
       </c>
       <c r="M69" s="2"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P69" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q69" s="11">
+        <v>4</v>
+      </c>
+      <c r="R69" s="11">
+        <v>3</v>
+      </c>
+      <c r="S69" s="21">
+        <v>4</v>
+      </c>
+      <c r="T69" s="22">
+        <v>5</v>
+      </c>
+      <c r="U69" s="11">
+        <v>4</v>
+      </c>
+      <c r="V69" s="21">
+        <v>4</v>
+      </c>
+      <c r="W69" s="22">
+        <v>3</v>
+      </c>
+      <c r="X69" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y69" s="21">
+        <v>4</v>
+      </c>
+      <c r="Z69" s="11">
+        <v>36</v>
+      </c>
+      <c r="AA69" s="2"/>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B70" s="20" t="s">
         <v>16</v>
       </c>
@@ -2890,8 +4824,40 @@
       </c>
       <c r="L70" s="11"/>
       <c r="M70" s="2"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P70" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q70" s="11">
+        <v>7</v>
+      </c>
+      <c r="R70" s="11">
+        <v>15</v>
+      </c>
+      <c r="S70" s="21">
+        <v>5</v>
+      </c>
+      <c r="T70" s="22">
+        <v>13</v>
+      </c>
+      <c r="U70" s="11">
+        <v>3</v>
+      </c>
+      <c r="V70" s="21">
+        <v>11</v>
+      </c>
+      <c r="W70" s="22">
+        <v>17</v>
+      </c>
+      <c r="X70" s="11">
+        <v>9</v>
+      </c>
+      <c r="Y70" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="11"/>
+      <c r="AA70" s="2"/>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B71" s="23" t="s">
         <v>17</v>
       </c>
@@ -2899,25 +4865,25 @@
         <v>8</v>
       </c>
       <c r="D71" s="25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E71" s="26">
+        <v>6</v>
+      </c>
+      <c r="F71" s="24">
         <v>8</v>
-      </c>
-      <c r="F71" s="24">
-        <v>10</v>
       </c>
       <c r="G71" s="25">
         <v>8</v>
       </c>
       <c r="H71" s="26">
+        <v>6</v>
+      </c>
+      <c r="I71" s="24">
+        <v>10</v>
+      </c>
+      <c r="J71" s="25">
         <v>8</v>
-      </c>
-      <c r="I71" s="24">
-        <v>6</v>
-      </c>
-      <c r="J71" s="25">
-        <v>10</v>
       </c>
       <c r="K71" s="26">
         <v>8</v>
@@ -2928,8 +4894,44 @@
       <c r="M71" s="27">
         <v>36</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q71" s="24">
+        <v>6</v>
+      </c>
+      <c r="R71" s="25">
+        <v>6</v>
+      </c>
+      <c r="S71" s="26">
+        <v>6</v>
+      </c>
+      <c r="T71" s="24">
+        <v>8</v>
+      </c>
+      <c r="U71" s="25">
+        <v>5</v>
+      </c>
+      <c r="V71" s="26">
+        <v>8</v>
+      </c>
+      <c r="W71" s="24">
+        <v>6</v>
+      </c>
+      <c r="X71" s="25">
+        <v>9</v>
+      </c>
+      <c r="Y71" s="26">
+        <v>8</v>
+      </c>
+      <c r="Z71" s="11">
+        <v>62</v>
+      </c>
+      <c r="AA71" s="27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B72" s="20" t="s">
         <v>18</v>
       </c>
@@ -2962,8 +4964,40 @@
       </c>
       <c r="L72" s="27"/>
       <c r="M72" s="2"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="P72" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q72" s="22">
+        <v>2</v>
+      </c>
+      <c r="R72" s="11">
+        <v>1</v>
+      </c>
+      <c r="S72" s="21">
+        <v>2</v>
+      </c>
+      <c r="T72" s="22">
+        <v>1</v>
+      </c>
+      <c r="U72" s="11">
+        <v>2</v>
+      </c>
+      <c r="V72" s="21">
+        <v>1</v>
+      </c>
+      <c r="W72" s="22">
+        <v>1</v>
+      </c>
+      <c r="X72" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y72" s="21">
+        <v>2</v>
+      </c>
+      <c r="Z72" s="27"/>
+      <c r="AA72" s="2"/>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B73" s="20" t="s">
         <v>19</v>
       </c>
@@ -2971,25 +5005,25 @@
         <v>6</v>
       </c>
       <c r="D73" s="11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E73" s="21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F73" s="22">
+        <v>6</v>
+      </c>
+      <c r="G73" s="11">
+        <v>6</v>
+      </c>
+      <c r="H73" s="21">
+        <v>4</v>
+      </c>
+      <c r="I73" s="22">
         <v>8</v>
       </c>
-      <c r="G73" s="11">
-        <v>6</v>
-      </c>
-      <c r="H73" s="21">
-        <v>6</v>
-      </c>
-      <c r="I73" s="22">
-        <v>4</v>
-      </c>
       <c r="J73" s="11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K73" s="21">
         <v>6</v>
@@ -3000,8 +5034,44 @@
       <c r="M73" s="27">
         <v>18</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P73" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q73" s="22">
+        <v>4</v>
+      </c>
+      <c r="R73" s="11">
+        <v>5</v>
+      </c>
+      <c r="S73" s="21">
+        <v>4</v>
+      </c>
+      <c r="T73" s="22">
+        <v>7</v>
+      </c>
+      <c r="U73" s="11">
+        <v>3</v>
+      </c>
+      <c r="V73" s="21">
+        <v>7</v>
+      </c>
+      <c r="W73" s="22">
+        <v>5</v>
+      </c>
+      <c r="X73" s="11">
+        <v>7</v>
+      </c>
+      <c r="Y73" s="21">
+        <v>6</v>
+      </c>
+      <c r="Z73" s="28">
+        <v>48</v>
+      </c>
+      <c r="AA73" s="27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="29" t="s">
         <v>20</v>
       </c>
@@ -3034,9 +5104,776 @@
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="2"/>
+      <c r="P74" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="30">
+        <v>0</v>
+      </c>
+      <c r="R74" s="31">
+        <v>0</v>
+      </c>
+      <c r="S74" s="32">
+        <v>1</v>
+      </c>
+      <c r="T74" s="30">
+        <v>0</v>
+      </c>
+      <c r="U74" s="31">
+        <v>0</v>
+      </c>
+      <c r="V74" s="32">
+        <v>0</v>
+      </c>
+      <c r="W74" s="30">
+        <v>0</v>
+      </c>
+      <c r="X74" s="31">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="32">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="11"/>
+      <c r="AA74" s="2"/>
+    </row>
+    <row r="76" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="2:27" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="K77" s="34"/>
+      <c r="L77" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="M77" s="34"/>
+    </row>
+    <row r="78" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="6">
+        <v>1</v>
+      </c>
+      <c r="E78" s="6">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6">
+        <v>0</v>
+      </c>
+      <c r="G78" s="6">
+        <v>2</v>
+      </c>
+      <c r="H78" s="6">
+        <v>50</v>
+      </c>
+      <c r="I78" s="2"/>
+      <c r="J78" s="38">
+        <v>7</v>
+      </c>
+      <c r="K78" s="39"/>
+      <c r="L78" s="43">
+        <v>1</v>
+      </c>
+      <c r="M78" s="39"/>
+    </row>
+    <row r="79" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="37"/>
+      <c r="C79" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="8">
+        <v>2</v>
+      </c>
+      <c r="E79" s="8">
+        <v>2</v>
+      </c>
+      <c r="F79" s="8">
+        <v>1</v>
+      </c>
+      <c r="G79" s="8">
+        <v>1</v>
+      </c>
+      <c r="H79" s="8">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2"/>
+      <c r="J79" s="40"/>
+      <c r="K79" s="41"/>
+      <c r="L79" s="44"/>
+      <c r="M79" s="41"/>
+    </row>
+    <row r="80" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="10">
+        <v>0</v>
+      </c>
+      <c r="E80" s="10">
+        <v>0</v>
+      </c>
+      <c r="F80" s="10">
+        <v>0</v>
+      </c>
+      <c r="G80" s="10">
+        <v>0</v>
+      </c>
+      <c r="H80" s="10">
+        <v>53</v>
+      </c>
+      <c r="I80" s="2"/>
+      <c r="J80" s="37"/>
+      <c r="K80" s="42"/>
+      <c r="L80" s="45"/>
+      <c r="M80" s="42"/>
+    </row>
+    <row r="81" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="37"/>
+      <c r="C81" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="8">
+        <v>0</v>
+      </c>
+      <c r="E81" s="8">
+        <v>0</v>
+      </c>
+      <c r="F81" s="8">
+        <v>1</v>
+      </c>
+      <c r="G81" s="8">
+        <v>0</v>
+      </c>
+      <c r="H81" s="8">
+        <v>0</v>
+      </c>
+      <c r="I81" s="2"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+    </row>
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B82" s="2"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="2"/>
+    </row>
+    <row r="83" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B83" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="11">
+        <v>36</v>
+      </c>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="2"/>
+    </row>
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B84" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="17">
+        <v>1</v>
+      </c>
+      <c r="D84" s="18">
+        <v>2</v>
+      </c>
+      <c r="E84" s="19">
+        <v>3</v>
+      </c>
+      <c r="F84" s="17">
+        <v>4</v>
+      </c>
+      <c r="G84" s="18">
+        <v>5</v>
+      </c>
+      <c r="H84" s="19">
+        <v>6</v>
+      </c>
+      <c r="I84" s="17">
+        <v>7</v>
+      </c>
+      <c r="J84" s="18">
+        <v>8</v>
+      </c>
+      <c r="K84" s="19">
+        <v>9</v>
+      </c>
+      <c r="L84" s="11"/>
+      <c r="M84" s="2"/>
+    </row>
+    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B85" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="11">
+        <v>4</v>
+      </c>
+      <c r="D85" s="11">
+        <v>3</v>
+      </c>
+      <c r="E85" s="21">
+        <v>4</v>
+      </c>
+      <c r="F85" s="22">
+        <v>5</v>
+      </c>
+      <c r="G85" s="11">
+        <v>4</v>
+      </c>
+      <c r="H85" s="21">
+        <v>4</v>
+      </c>
+      <c r="I85" s="22">
+        <v>3</v>
+      </c>
+      <c r="J85" s="11">
+        <v>5</v>
+      </c>
+      <c r="K85" s="21">
+        <v>4</v>
+      </c>
+      <c r="L85" s="11">
+        <v>36</v>
+      </c>
+      <c r="M85" s="2"/>
+    </row>
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B86" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="11">
+        <v>17</v>
+      </c>
+      <c r="D86" s="11">
+        <v>9</v>
+      </c>
+      <c r="E86" s="21">
+        <v>5</v>
+      </c>
+      <c r="F86" s="22">
+        <v>7</v>
+      </c>
+      <c r="G86" s="11">
+        <v>3</v>
+      </c>
+      <c r="H86" s="21">
+        <v>15</v>
+      </c>
+      <c r="I86" s="22">
+        <v>11</v>
+      </c>
+      <c r="J86" s="11">
+        <v>13</v>
+      </c>
+      <c r="K86" s="21">
+        <v>1</v>
+      </c>
+      <c r="L86" s="11"/>
+      <c r="M86" s="2"/>
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B87" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="24">
+        <v>6</v>
+      </c>
+      <c r="D87" s="25">
+        <v>6</v>
+      </c>
+      <c r="E87" s="26">
+        <v>8</v>
+      </c>
+      <c r="F87" s="24">
+        <v>9</v>
+      </c>
+      <c r="G87" s="25">
+        <v>8</v>
+      </c>
+      <c r="H87" s="26">
+        <v>8</v>
+      </c>
+      <c r="I87" s="24">
+        <v>6</v>
+      </c>
+      <c r="J87" s="25">
+        <v>9</v>
+      </c>
+      <c r="K87" s="26">
+        <v>8</v>
+      </c>
+      <c r="L87" s="11">
+        <v>68</v>
+      </c>
+      <c r="M87" s="27">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B88" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="22">
+        <v>2</v>
+      </c>
+      <c r="D88" s="11">
+        <v>2</v>
+      </c>
+      <c r="E88" s="21">
+        <v>2</v>
+      </c>
+      <c r="F88" s="22">
+        <v>2</v>
+      </c>
+      <c r="G88" s="11">
+        <v>2</v>
+      </c>
+      <c r="H88" s="21">
+        <v>2</v>
+      </c>
+      <c r="I88" s="22">
+        <v>2</v>
+      </c>
+      <c r="J88" s="11">
+        <v>2</v>
+      </c>
+      <c r="K88" s="21">
+        <v>2</v>
+      </c>
+      <c r="L88" s="27"/>
+      <c r="M88" s="2"/>
+    </row>
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B89" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" s="22">
+        <v>4</v>
+      </c>
+      <c r="D89" s="11">
+        <v>4</v>
+      </c>
+      <c r="E89" s="21">
+        <v>6</v>
+      </c>
+      <c r="F89" s="22">
+        <v>7</v>
+      </c>
+      <c r="G89" s="11">
+        <v>6</v>
+      </c>
+      <c r="H89" s="21">
+        <v>6</v>
+      </c>
+      <c r="I89" s="22">
+        <v>4</v>
+      </c>
+      <c r="J89" s="11">
+        <v>7</v>
+      </c>
+      <c r="K89" s="21">
+        <v>6</v>
+      </c>
+      <c r="L89" s="28">
+        <v>50</v>
+      </c>
+      <c r="M89" s="27">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B90" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" s="30">
+        <v>1</v>
+      </c>
+      <c r="D90" s="31">
+        <v>0</v>
+      </c>
+      <c r="E90" s="32">
+        <v>0</v>
+      </c>
+      <c r="F90" s="30">
+        <v>1</v>
+      </c>
+      <c r="G90" s="31">
+        <v>0</v>
+      </c>
+      <c r="H90" s="32">
+        <v>0</v>
+      </c>
+      <c r="I90" s="30">
+        <v>0</v>
+      </c>
+      <c r="J90" s="31">
+        <v>0</v>
+      </c>
+      <c r="K90" s="32">
+        <v>0</v>
+      </c>
+      <c r="L90" s="11"/>
+      <c r="M90" s="2"/>
+    </row>
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B91" s="2"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="11"/>
+      <c r="M91" s="2"/>
+    </row>
+    <row r="92" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="11">
+        <v>36</v>
+      </c>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="2"/>
+    </row>
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B93" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" s="17">
+        <v>1</v>
+      </c>
+      <c r="D93" s="18">
+        <v>2</v>
+      </c>
+      <c r="E93" s="19">
+        <v>3</v>
+      </c>
+      <c r="F93" s="17">
+        <v>4</v>
+      </c>
+      <c r="G93" s="18">
+        <v>5</v>
+      </c>
+      <c r="H93" s="19">
+        <v>6</v>
+      </c>
+      <c r="I93" s="17">
+        <v>7</v>
+      </c>
+      <c r="J93" s="18">
+        <v>8</v>
+      </c>
+      <c r="K93" s="19">
+        <v>9</v>
+      </c>
+      <c r="L93" s="11"/>
+      <c r="M93" s="27"/>
+    </row>
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B94" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="11">
+        <v>4</v>
+      </c>
+      <c r="D94" s="11">
+        <v>3</v>
+      </c>
+      <c r="E94" s="21">
+        <v>4</v>
+      </c>
+      <c r="F94" s="22">
+        <v>5</v>
+      </c>
+      <c r="G94" s="11">
+        <v>4</v>
+      </c>
+      <c r="H94" s="21">
+        <v>4</v>
+      </c>
+      <c r="I94" s="22">
+        <v>3</v>
+      </c>
+      <c r="J94" s="11">
+        <v>5</v>
+      </c>
+      <c r="K94" s="21">
+        <v>4</v>
+      </c>
+      <c r="L94" s="11">
+        <v>36</v>
+      </c>
+      <c r="M94" s="2"/>
+    </row>
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B95" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="11">
+        <v>7</v>
+      </c>
+      <c r="D95" s="11">
+        <v>15</v>
+      </c>
+      <c r="E95" s="21">
+        <v>5</v>
+      </c>
+      <c r="F95" s="22">
+        <v>13</v>
+      </c>
+      <c r="G95" s="11">
+        <v>3</v>
+      </c>
+      <c r="H95" s="21">
+        <v>11</v>
+      </c>
+      <c r="I95" s="22">
+        <v>17</v>
+      </c>
+      <c r="J95" s="11">
+        <v>9</v>
+      </c>
+      <c r="K95" s="21">
+        <v>1</v>
+      </c>
+      <c r="L95" s="11"/>
+      <c r="M95" s="2"/>
+    </row>
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B96" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="24">
+        <v>8</v>
+      </c>
+      <c r="D96" s="25">
+        <v>6</v>
+      </c>
+      <c r="E96" s="26">
+        <v>8</v>
+      </c>
+      <c r="F96" s="24">
+        <v>10</v>
+      </c>
+      <c r="G96" s="25">
+        <v>8</v>
+      </c>
+      <c r="H96" s="26">
+        <v>8</v>
+      </c>
+      <c r="I96" s="24">
+        <v>6</v>
+      </c>
+      <c r="J96" s="25">
+        <v>9</v>
+      </c>
+      <c r="K96" s="26">
+        <v>8</v>
+      </c>
+      <c r="L96" s="11">
+        <v>71</v>
+      </c>
+      <c r="M96" s="27">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B97" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="22">
+        <v>2</v>
+      </c>
+      <c r="D97" s="11">
+        <v>2</v>
+      </c>
+      <c r="E97" s="21">
+        <v>2</v>
+      </c>
+      <c r="F97" s="22">
+        <v>2</v>
+      </c>
+      <c r="G97" s="11">
+        <v>2</v>
+      </c>
+      <c r="H97" s="21">
+        <v>2</v>
+      </c>
+      <c r="I97" s="22">
+        <v>2</v>
+      </c>
+      <c r="J97" s="11">
+        <v>2</v>
+      </c>
+      <c r="K97" s="21">
+        <v>2</v>
+      </c>
+      <c r="L97" s="27"/>
+      <c r="M97" s="2"/>
+    </row>
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B98" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" s="22">
+        <v>6</v>
+      </c>
+      <c r="D98" s="11">
+        <v>4</v>
+      </c>
+      <c r="E98" s="21">
+        <v>6</v>
+      </c>
+      <c r="F98" s="22">
+        <v>8</v>
+      </c>
+      <c r="G98" s="11">
+        <v>6</v>
+      </c>
+      <c r="H98" s="21">
+        <v>6</v>
+      </c>
+      <c r="I98" s="22">
+        <v>4</v>
+      </c>
+      <c r="J98" s="11">
+        <v>7</v>
+      </c>
+      <c r="K98" s="21">
+        <v>6</v>
+      </c>
+      <c r="L98" s="28">
+        <v>53</v>
+      </c>
+      <c r="M98" s="27">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" s="30">
+        <v>0</v>
+      </c>
+      <c r="D99" s="31">
+        <v>0</v>
+      </c>
+      <c r="E99" s="32">
+        <v>0</v>
+      </c>
+      <c r="F99" s="30">
+        <v>0</v>
+      </c>
+      <c r="G99" s="31">
+        <v>0</v>
+      </c>
+      <c r="H99" s="32">
+        <v>0</v>
+      </c>
+      <c r="I99" s="30">
+        <v>0</v>
+      </c>
+      <c r="J99" s="31">
+        <v>0</v>
+      </c>
+      <c r="K99" s="32">
+        <v>0</v>
+      </c>
+      <c r="L99" s="11"/>
+      <c r="M99" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="42">
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="L52:M52"/>
     <mergeCell ref="B53:B54"/>
@@ -3055,18 +5892,50 @@
     <mergeCell ref="J28:K30"/>
     <mergeCell ref="L28:M30"/>
     <mergeCell ref="B30:B31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="P28:P29"/>
+    <mergeCell ref="X28:Y30"/>
+    <mergeCell ref="Z28:AA30"/>
+    <mergeCell ref="P30:P31"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C90:K90 C99:K99">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -3078,7 +5947,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3087,18 +5956,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3107,7 +5976,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3116,18 +5985,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3136,7 +6005,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3145,18 +6014,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3165,7 +6034,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3174,7 +6043,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F961387-F1C3-4D87-AD2E-43D66A516BAF}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B03FA299-A009-4C43-93DB-8668810D817A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="38">
   <si>
     <t>Skybrook</t>
   </si>
@@ -531,7 +531,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -933,15 +953,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA99"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:27" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:27" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -999,7 +1019,7 @@
       </c>
       <c r="AA2" s="34"/>
     </row>
-    <row r="3" spans="2:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="36" t="s">
         <v>8</v>
       </c>
@@ -1061,7 +1081,7 @@
       </c>
       <c r="AA3" s="39"/>
     </row>
-    <row r="4" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="37"/>
       <c r="C4" s="7" t="s">
         <v>7</v>
@@ -1111,7 +1131,7 @@
       <c r="Z4" s="44"/>
       <c r="AA4" s="41"/>
     </row>
-    <row r="5" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="36" t="s">
         <v>21</v>
       </c>
@@ -1165,7 +1185,7 @@
       <c r="Z5" s="45"/>
       <c r="AA5" s="42"/>
     </row>
-    <row r="6" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="37"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
@@ -1215,7 +1235,7 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -1241,7 +1261,7 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="2"/>
     </row>
-    <row r="8" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
         <v>8</v>
       </c>
@@ -1295,7 +1315,7 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
@@ -1361,7 +1381,7 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
@@ -1431,7 +1451,7 @@
       </c>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
@@ -1497,7 +1517,7 @@
       <c r="Z11" s="11"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" s="23" t="s">
         <v>17</v>
       </c>
@@ -1571,7 +1591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
@@ -1637,7 +1657,7 @@
       <c r="Z13" s="27"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
         <v>19</v>
       </c>
@@ -1711,7 +1731,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="15" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>20</v>
       </c>
@@ -1777,7 +1797,7 @@
       <c r="Z15" s="11"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -1803,7 +1823,7 @@
       <c r="Z16" s="11"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="12" t="s">
         <v>21</v>
       </c>
@@ -1857,7 +1877,7 @@
       <c r="Z17" s="11"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
@@ -1923,7 +1943,7 @@
       <c r="Z18" s="11"/>
       <c r="AA18" s="27"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B19" s="20" t="s">
         <v>15</v>
       </c>
@@ -1993,7 +2013,7 @@
       </c>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
         <v>16</v>
       </c>
@@ -2059,7 +2079,7 @@
       <c r="Z20" s="11"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
@@ -2133,7 +2153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B22" s="20" t="s">
         <v>18</v>
       </c>
@@ -2199,7 +2219,7 @@
       <c r="Z22" s="27"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B23" s="20" t="s">
         <v>19</v>
       </c>
@@ -2273,7 +2293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="29" t="s">
         <v>20</v>
       </c>
@@ -2339,8 +2359,8 @@
       <c r="Z24" s="11"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="26" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:27" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:27" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
@@ -2398,7 +2418,7 @@
       </c>
       <c r="AA27" s="34"/>
     </row>
-    <row r="28" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="36" t="s">
         <v>22</v>
       </c>
@@ -2460,7 +2480,7 @@
       </c>
       <c r="AA28" s="39"/>
     </row>
-    <row r="29" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="37"/>
       <c r="C29" s="7" t="s">
         <v>7</v>
@@ -2510,7 +2530,7 @@
       <c r="Z29" s="44"/>
       <c r="AA29" s="41"/>
     </row>
-    <row r="30" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="36" t="s">
         <v>23</v>
       </c>
@@ -2564,7 +2584,7 @@
       <c r="Z30" s="45"/>
       <c r="AA30" s="42"/>
     </row>
-    <row r="31" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="37"/>
       <c r="C31" s="7" t="s">
         <v>7</v>
@@ -2614,7 +2634,7 @@
       <c r="Z31" s="11"/>
       <c r="AA31" s="11"/>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -2640,7 +2660,7 @@
       <c r="Z32" s="11"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
         <v>22</v>
       </c>
@@ -2694,7 +2714,7 @@
       <c r="Z33" s="11"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" s="16" t="s">
         <v>14</v>
       </c>
@@ -2760,7 +2780,7 @@
       <c r="Z34" s="11"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" s="20" t="s">
         <v>15</v>
       </c>
@@ -2830,7 +2850,7 @@
       </c>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
         <v>16</v>
       </c>
@@ -2896,7 +2916,7 @@
       <c r="Z36" s="11"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B37" s="23" t="s">
         <v>17</v>
       </c>
@@ -2970,7 +2990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
         <v>18</v>
       </c>
@@ -3036,7 +3056,7 @@
       <c r="Z38" s="27"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
         <v>19</v>
       </c>
@@ -3110,7 +3130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="29" t="s">
         <v>20</v>
       </c>
@@ -3176,7 +3196,7 @@
       <c r="Z40" s="11"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -3202,7 +3222,7 @@
       <c r="Z41" s="11"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="12" t="s">
         <v>23</v>
       </c>
@@ -3256,7 +3276,7 @@
       <c r="Z42" s="11"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
         <v>14</v>
       </c>
@@ -3322,7 +3342,7 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="27"/>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" s="20" t="s">
         <v>15</v>
       </c>
@@ -3392,7 +3412,7 @@
       </c>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="20" t="s">
         <v>16</v>
       </c>
@@ -3458,7 +3478,7 @@
       <c r="Z45" s="11"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="23" t="s">
         <v>17</v>
       </c>
@@ -3532,7 +3552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="20" t="s">
         <v>18</v>
       </c>
@@ -3598,7 +3618,7 @@
       <c r="Z47" s="27"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
         <v>19</v>
       </c>
@@ -3672,7 +3692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="49" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="29" t="s">
         <v>20</v>
       </c>
@@ -3738,8 +3758,8 @@
       <c r="Z49" s="11"/>
       <c r="AA49" s="2"/>
     </row>
-    <row r="51" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="2:27" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:27" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>24</v>
       </c>
@@ -3797,7 +3817,7 @@
       </c>
       <c r="AA52" s="34"/>
     </row>
-    <row r="53" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>25</v>
       </c>
@@ -3859,7 +3879,7 @@
       </c>
       <c r="AA53" s="39"/>
     </row>
-    <row r="54" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="37"/>
       <c r="C54" s="7" t="s">
         <v>7</v>
@@ -3909,7 +3929,7 @@
       <c r="Z54" s="44"/>
       <c r="AA54" s="41"/>
     </row>
-    <row r="55" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="36" t="s">
         <v>26</v>
       </c>
@@ -3963,7 +3983,7 @@
       <c r="Z55" s="45"/>
       <c r="AA55" s="42"/>
     </row>
-    <row r="56" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="37"/>
       <c r="C56" s="7" t="s">
         <v>7</v>
@@ -4013,7 +4033,7 @@
       <c r="Z56" s="11"/>
       <c r="AA56" s="11"/>
     </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
@@ -4039,7 +4059,7 @@
       <c r="Z57" s="11"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="12" t="s">
         <v>25</v>
       </c>
@@ -4093,7 +4113,7 @@
       <c r="Z58" s="11"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B59" s="16" t="s">
         <v>14</v>
       </c>
@@ -4159,7 +4179,7 @@
       <c r="Z59" s="11"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
         <v>15</v>
       </c>
@@ -4229,7 +4249,7 @@
       </c>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
         <v>16</v>
       </c>
@@ -4295,7 +4315,7 @@
       <c r="Z61" s="11"/>
       <c r="AA61" s="2"/>
     </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B62" s="23" t="s">
         <v>17</v>
       </c>
@@ -4369,7 +4389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
         <v>18</v>
       </c>
@@ -4435,7 +4455,7 @@
       <c r="Z63" s="27"/>
       <c r="AA63" s="2"/>
     </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B64" s="20" t="s">
         <v>19</v>
       </c>
@@ -4509,7 +4529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="29" t="s">
         <v>20</v>
       </c>
@@ -4575,7 +4595,7 @@
       <c r="Z65" s="11"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -4601,7 +4621,7 @@
       <c r="Z66" s="11"/>
       <c r="AA66" s="2"/>
     </row>
-    <row r="67" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="12" t="s">
         <v>26</v>
       </c>
@@ -4655,7 +4675,7 @@
       <c r="Z67" s="11"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B68" s="16" t="s">
         <v>14</v>
       </c>
@@ -4721,7 +4741,7 @@
       <c r="Z68" s="11"/>
       <c r="AA68" s="27"/>
     </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B69" s="20" t="s">
         <v>15</v>
       </c>
@@ -4791,7 +4811,7 @@
       </c>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
         <v>16</v>
       </c>
@@ -4857,7 +4877,7 @@
       <c r="Z70" s="11"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B71" s="23" t="s">
         <v>17</v>
       </c>
@@ -4931,7 +4951,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B72" s="20" t="s">
         <v>18</v>
       </c>
@@ -4997,7 +5017,7 @@
       <c r="Z72" s="27"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
         <v>19</v>
       </c>
@@ -5071,7 +5091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="29" t="s">
         <v>20</v>
       </c>
@@ -5137,8 +5157,8 @@
       <c r="Z74" s="11"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="76" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="2:27" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:27" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
         <v>0</v>
       </c>
@@ -5168,7 +5188,7 @@
       </c>
       <c r="M77" s="34"/>
     </row>
-    <row r="78" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="36" t="s">
         <v>35</v>
       </c>
@@ -5200,7 +5220,7 @@
       </c>
       <c r="M78" s="39"/>
     </row>
-    <row r="79" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="37"/>
       <c r="C79" s="7" t="s">
         <v>7</v>
@@ -5226,7 +5246,7 @@
       <c r="L79" s="44"/>
       <c r="M79" s="41"/>
     </row>
-    <row r="80" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="36" t="s">
         <v>36</v>
       </c>
@@ -5254,7 +5274,7 @@
       <c r="L80" s="45"/>
       <c r="M80" s="42"/>
     </row>
-    <row r="81" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="37"/>
       <c r="C81" s="7" t="s">
         <v>7</v>
@@ -5280,7 +5300,7 @@
       <c r="L81" s="11"/>
       <c r="M81" s="11"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
@@ -5294,7 +5314,7 @@
       <c r="L82" s="11"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="12" t="s">
         <v>35</v>
       </c>
@@ -5322,7 +5342,7 @@
       <c r="L83" s="11"/>
       <c r="M83" s="2"/>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B84" s="16" t="s">
         <v>14</v>
       </c>
@@ -5356,7 +5376,7 @@
       <c r="L84" s="11"/>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B85" s="20" t="s">
         <v>15</v>
       </c>
@@ -5392,7 +5412,7 @@
       </c>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B86" s="20" t="s">
         <v>16</v>
       </c>
@@ -5426,7 +5446,7 @@
       <c r="L86" s="11"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B87" s="23" t="s">
         <v>17</v>
       </c>
@@ -5464,7 +5484,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B88" s="20" t="s">
         <v>18</v>
       </c>
@@ -5498,7 +5518,7 @@
       <c r="L88" s="27"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
         <v>19</v>
       </c>
@@ -5536,7 +5556,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="29" t="s">
         <v>20</v>
       </c>
@@ -5570,7 +5590,7 @@
       <c r="L90" s="11"/>
       <c r="M90" s="2"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
@@ -5584,7 +5604,7 @@
       <c r="L91" s="11"/>
       <c r="M91" s="2"/>
     </row>
-    <row r="92" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="12" t="s">
         <v>36</v>
       </c>
@@ -5612,7 +5632,7 @@
       <c r="L92" s="11"/>
       <c r="M92" s="2"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B93" s="16" t="s">
         <v>14</v>
       </c>
@@ -5646,7 +5666,7 @@
       <c r="L93" s="11"/>
       <c r="M93" s="27"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B94" s="20" t="s">
         <v>15</v>
       </c>
@@ -5682,7 +5702,7 @@
       </c>
       <c r="M94" s="2"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B95" s="20" t="s">
         <v>16</v>
       </c>
@@ -5716,7 +5736,7 @@
       <c r="L95" s="11"/>
       <c r="M95" s="2"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B96" s="23" t="s">
         <v>17</v>
       </c>
@@ -5754,7 +5774,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B97" s="20" t="s">
         <v>18</v>
       </c>
@@ -5788,7 +5808,7 @@
       <c r="L97" s="27"/>
       <c r="M97" s="2"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B98" s="20" t="s">
         <v>19</v>
       </c>
@@ -5826,7 +5846,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="29" t="s">
         <v>20</v>
       </c>
@@ -5862,81 +5882,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="P28:P29"/>
+    <mergeCell ref="X28:Y30"/>
+    <mergeCell ref="Z28:AA30"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="J77:K77"/>
     <mergeCell ref="L77:M77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="J78:K80"/>
     <mergeCell ref="L78:M80"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="P28:P29"/>
-    <mergeCell ref="X28:Y30"/>
-    <mergeCell ref="Z28:AA30"/>
-    <mergeCell ref="P30:P31"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C90:K90 C99:K99">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
-      <formula>0.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5946,9 +5966,1483 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="B1:M49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="34"/>
+      <c r="L2" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="34"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6">
+        <v>3</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6">
+        <v>6</v>
+      </c>
+      <c r="H3" s="6">
+        <v>36</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="38">
+        <v>7</v>
+      </c>
+      <c r="K3" s="39"/>
+      <c r="L3" s="43">
+        <v>1</v>
+      </c>
+      <c r="M3" s="39"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="37"/>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="41"/>
+    </row>
+    <row r="5" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>2</v>
+      </c>
+      <c r="H5" s="10">
+        <v>47</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="42"/>
+    </row>
+    <row r="6" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="37"/>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="2"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11">
+        <v>12</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+      <c r="D9" s="18">
+        <v>2</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3</v>
+      </c>
+      <c r="F9" s="17">
+        <v>4</v>
+      </c>
+      <c r="G9" s="18">
+        <v>5</v>
+      </c>
+      <c r="H9" s="19">
+        <v>6</v>
+      </c>
+      <c r="I9" s="17">
+        <v>7</v>
+      </c>
+      <c r="J9" s="18">
+        <v>8</v>
+      </c>
+      <c r="K9" s="19">
+        <v>9</v>
+      </c>
+      <c r="L9" s="11"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="11">
+        <v>4</v>
+      </c>
+      <c r="D10" s="11">
+        <v>3</v>
+      </c>
+      <c r="E10" s="21">
+        <v>4</v>
+      </c>
+      <c r="F10" s="22">
+        <v>5</v>
+      </c>
+      <c r="G10" s="11">
+        <v>4</v>
+      </c>
+      <c r="H10" s="21">
+        <v>4</v>
+      </c>
+      <c r="I10" s="22">
+        <v>3</v>
+      </c>
+      <c r="J10" s="11">
+        <v>5</v>
+      </c>
+      <c r="K10" s="21">
+        <v>4</v>
+      </c>
+      <c r="L10" s="11">
+        <v>36</v>
+      </c>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="11">
+        <v>7</v>
+      </c>
+      <c r="D11" s="11">
+        <v>15</v>
+      </c>
+      <c r="E11" s="21">
+        <v>5</v>
+      </c>
+      <c r="F11" s="22">
+        <v>13</v>
+      </c>
+      <c r="G11" s="11">
+        <v>3</v>
+      </c>
+      <c r="H11" s="21">
+        <v>11</v>
+      </c>
+      <c r="I11" s="22">
+        <v>17</v>
+      </c>
+      <c r="J11" s="11">
+        <v>9</v>
+      </c>
+      <c r="K11" s="21">
+        <v>1</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="24">
+        <v>6</v>
+      </c>
+      <c r="D12" s="25">
+        <v>3</v>
+      </c>
+      <c r="E12" s="26">
+        <v>3</v>
+      </c>
+      <c r="F12" s="24">
+        <v>5</v>
+      </c>
+      <c r="G12" s="25">
+        <v>7</v>
+      </c>
+      <c r="H12" s="26">
+        <v>4</v>
+      </c>
+      <c r="I12" s="24">
+        <v>2</v>
+      </c>
+      <c r="J12" s="25">
+        <v>5</v>
+      </c>
+      <c r="K12" s="26">
+        <v>7</v>
+      </c>
+      <c r="L12" s="11">
+        <v>42</v>
+      </c>
+      <c r="M12" s="27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="22">
+        <v>1</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0</v>
+      </c>
+      <c r="E13" s="21">
+        <v>1</v>
+      </c>
+      <c r="F13" s="22">
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
+        <v>1</v>
+      </c>
+      <c r="H13" s="21">
+        <v>1</v>
+      </c>
+      <c r="I13" s="22">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11">
+        <v>1</v>
+      </c>
+      <c r="K13" s="21">
+        <v>1</v>
+      </c>
+      <c r="L13" s="27"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="22">
+        <v>5</v>
+      </c>
+      <c r="D14" s="11">
+        <v>3</v>
+      </c>
+      <c r="E14" s="21">
+        <v>2</v>
+      </c>
+      <c r="F14" s="22">
+        <v>5</v>
+      </c>
+      <c r="G14" s="11">
+        <v>6</v>
+      </c>
+      <c r="H14" s="21">
+        <v>3</v>
+      </c>
+      <c r="I14" s="22">
+        <v>2</v>
+      </c>
+      <c r="J14" s="11">
+        <v>4</v>
+      </c>
+      <c r="K14" s="21">
+        <v>6</v>
+      </c>
+      <c r="L14" s="28">
+        <v>36</v>
+      </c>
+      <c r="M14" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="30">
+        <v>1</v>
+      </c>
+      <c r="D15" s="31">
+        <v>1</v>
+      </c>
+      <c r="E15" s="32">
+        <v>1</v>
+      </c>
+      <c r="F15" s="30">
+        <v>1</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0</v>
+      </c>
+      <c r="H15" s="32">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30">
+        <v>1</v>
+      </c>
+      <c r="J15" s="31">
+        <v>1</v>
+      </c>
+      <c r="K15" s="32">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="11">
+        <v>20</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="17">
+        <v>1</v>
+      </c>
+      <c r="D18" s="18">
+        <v>2</v>
+      </c>
+      <c r="E18" s="19">
+        <v>3</v>
+      </c>
+      <c r="F18" s="17">
+        <v>4</v>
+      </c>
+      <c r="G18" s="18">
+        <v>5</v>
+      </c>
+      <c r="H18" s="19">
+        <v>6</v>
+      </c>
+      <c r="I18" s="17">
+        <v>7</v>
+      </c>
+      <c r="J18" s="18">
+        <v>8</v>
+      </c>
+      <c r="K18" s="19">
+        <v>9</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" s="27"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="11">
+        <v>4</v>
+      </c>
+      <c r="D19" s="11">
+        <v>3</v>
+      </c>
+      <c r="E19" s="21">
+        <v>4</v>
+      </c>
+      <c r="F19" s="22">
+        <v>5</v>
+      </c>
+      <c r="G19" s="11">
+        <v>4</v>
+      </c>
+      <c r="H19" s="21">
+        <v>4</v>
+      </c>
+      <c r="I19" s="22">
+        <v>3</v>
+      </c>
+      <c r="J19" s="11">
+        <v>5</v>
+      </c>
+      <c r="K19" s="21">
+        <v>4</v>
+      </c>
+      <c r="L19" s="11">
+        <v>36</v>
+      </c>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="11">
+        <v>7</v>
+      </c>
+      <c r="D20" s="11">
+        <v>15</v>
+      </c>
+      <c r="E20" s="21">
+        <v>5</v>
+      </c>
+      <c r="F20" s="22">
+        <v>13</v>
+      </c>
+      <c r="G20" s="11">
+        <v>3</v>
+      </c>
+      <c r="H20" s="21">
+        <v>11</v>
+      </c>
+      <c r="I20" s="22">
+        <v>17</v>
+      </c>
+      <c r="J20" s="11">
+        <v>9</v>
+      </c>
+      <c r="K20" s="21">
+        <v>1</v>
+      </c>
+      <c r="L20" s="11"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="24">
+        <v>7</v>
+      </c>
+      <c r="D21" s="25">
+        <v>6</v>
+      </c>
+      <c r="E21" s="26">
+        <v>5</v>
+      </c>
+      <c r="F21" s="24">
+        <v>7</v>
+      </c>
+      <c r="G21" s="25">
+        <v>6</v>
+      </c>
+      <c r="H21" s="26">
+        <v>4</v>
+      </c>
+      <c r="I21" s="24">
+        <v>6</v>
+      </c>
+      <c r="J21" s="25">
+        <v>10</v>
+      </c>
+      <c r="K21" s="26">
+        <v>6</v>
+      </c>
+      <c r="L21" s="11">
+        <v>57</v>
+      </c>
+      <c r="M21" s="27">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1</v>
+      </c>
+      <c r="E22" s="21">
+        <v>1</v>
+      </c>
+      <c r="F22" s="22">
+        <v>1</v>
+      </c>
+      <c r="G22" s="11">
+        <v>1</v>
+      </c>
+      <c r="H22" s="21">
+        <v>1</v>
+      </c>
+      <c r="I22" s="22">
+        <v>1</v>
+      </c>
+      <c r="J22" s="11">
+        <v>1</v>
+      </c>
+      <c r="K22" s="21">
+        <v>2</v>
+      </c>
+      <c r="L22" s="27"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="22">
+        <v>6</v>
+      </c>
+      <c r="D23" s="11">
+        <v>5</v>
+      </c>
+      <c r="E23" s="21">
+        <v>4</v>
+      </c>
+      <c r="F23" s="22">
+        <v>6</v>
+      </c>
+      <c r="G23" s="11">
+        <v>5</v>
+      </c>
+      <c r="H23" s="21">
+        <v>3</v>
+      </c>
+      <c r="I23" s="22">
+        <v>5</v>
+      </c>
+      <c r="J23" s="11">
+        <v>9</v>
+      </c>
+      <c r="K23" s="21">
+        <v>4</v>
+      </c>
+      <c r="L23" s="28">
+        <v>47</v>
+      </c>
+      <c r="M23" s="27">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="30">
+        <v>0</v>
+      </c>
+      <c r="D24" s="31">
+        <v>0</v>
+      </c>
+      <c r="E24" s="32">
+        <v>0</v>
+      </c>
+      <c r="F24" s="30">
+        <v>0</v>
+      </c>
+      <c r="G24" s="31">
+        <v>1</v>
+      </c>
+      <c r="H24" s="32">
+        <v>0</v>
+      </c>
+      <c r="I24" s="30">
+        <v>0</v>
+      </c>
+      <c r="J24" s="31">
+        <v>0</v>
+      </c>
+      <c r="K24" s="32">
+        <v>1</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="26" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="34"/>
+      <c r="L27" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="34"/>
+    </row>
+    <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6">
+        <v>3</v>
+      </c>
+      <c r="G28" s="6">
+        <v>4</v>
+      </c>
+      <c r="H28" s="6">
+        <v>40</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="38">
+        <v>4</v>
+      </c>
+      <c r="K28" s="39"/>
+      <c r="L28" s="43">
+        <v>4</v>
+      </c>
+      <c r="M28" s="39"/>
+    </row>
+    <row r="29" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="37"/>
+      <c r="C29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2</v>
+      </c>
+      <c r="G29" s="8">
+        <v>1</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="41"/>
+    </row>
+    <row r="30" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="10">
+        <v>2</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10">
+        <v>0</v>
+      </c>
+      <c r="G30" s="10">
+        <v>3</v>
+      </c>
+      <c r="H30" s="10">
+        <v>39</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="42"/>
+    </row>
+    <row r="31" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="37"/>
+      <c r="C31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="8">
+        <v>2</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="11">
+        <v>12</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B34" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="17">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18">
+        <v>2</v>
+      </c>
+      <c r="E34" s="19">
+        <v>3</v>
+      </c>
+      <c r="F34" s="17">
+        <v>4</v>
+      </c>
+      <c r="G34" s="18">
+        <v>5</v>
+      </c>
+      <c r="H34" s="19">
+        <v>6</v>
+      </c>
+      <c r="I34" s="17">
+        <v>7</v>
+      </c>
+      <c r="J34" s="18">
+        <v>8</v>
+      </c>
+      <c r="K34" s="19">
+        <v>9</v>
+      </c>
+      <c r="L34" s="11"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="11">
+        <v>4</v>
+      </c>
+      <c r="D35" s="11">
+        <v>3</v>
+      </c>
+      <c r="E35" s="21">
+        <v>4</v>
+      </c>
+      <c r="F35" s="22">
+        <v>5</v>
+      </c>
+      <c r="G35" s="11">
+        <v>4</v>
+      </c>
+      <c r="H35" s="21">
+        <v>4</v>
+      </c>
+      <c r="I35" s="22">
+        <v>3</v>
+      </c>
+      <c r="J35" s="11">
+        <v>5</v>
+      </c>
+      <c r="K35" s="21">
+        <v>4</v>
+      </c>
+      <c r="L35" s="11">
+        <v>36</v>
+      </c>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B36" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="11">
+        <v>7</v>
+      </c>
+      <c r="D36" s="11">
+        <v>15</v>
+      </c>
+      <c r="E36" s="21">
+        <v>5</v>
+      </c>
+      <c r="F36" s="22">
+        <v>13</v>
+      </c>
+      <c r="G36" s="11">
+        <v>3</v>
+      </c>
+      <c r="H36" s="21">
+        <v>11</v>
+      </c>
+      <c r="I36" s="22">
+        <v>17</v>
+      </c>
+      <c r="J36" s="11">
+        <v>9</v>
+      </c>
+      <c r="K36" s="21">
+        <v>1</v>
+      </c>
+      <c r="L36" s="11"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B37" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="24">
+        <v>6</v>
+      </c>
+      <c r="D37" s="25">
+        <v>5</v>
+      </c>
+      <c r="E37" s="26">
+        <v>6</v>
+      </c>
+      <c r="F37" s="24">
+        <v>8</v>
+      </c>
+      <c r="G37" s="25">
+        <v>4</v>
+      </c>
+      <c r="H37" s="26">
+        <v>5</v>
+      </c>
+      <c r="I37" s="24">
+        <v>3</v>
+      </c>
+      <c r="J37" s="25">
+        <v>5</v>
+      </c>
+      <c r="K37" s="26">
+        <v>4</v>
+      </c>
+      <c r="L37" s="11">
+        <v>46</v>
+      </c>
+      <c r="M37" s="27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="22">
+        <v>1</v>
+      </c>
+      <c r="D38" s="11">
+        <v>0</v>
+      </c>
+      <c r="E38" s="21">
+        <v>1</v>
+      </c>
+      <c r="F38" s="22">
+        <v>0</v>
+      </c>
+      <c r="G38" s="11">
+        <v>1</v>
+      </c>
+      <c r="H38" s="21">
+        <v>1</v>
+      </c>
+      <c r="I38" s="22">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11">
+        <v>1</v>
+      </c>
+      <c r="K38" s="21">
+        <v>1</v>
+      </c>
+      <c r="L38" s="27"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="22">
+        <v>5</v>
+      </c>
+      <c r="D39" s="11">
+        <v>5</v>
+      </c>
+      <c r="E39" s="21">
+        <v>5</v>
+      </c>
+      <c r="F39" s="22">
+        <v>8</v>
+      </c>
+      <c r="G39" s="11">
+        <v>3</v>
+      </c>
+      <c r="H39" s="21">
+        <v>4</v>
+      </c>
+      <c r="I39" s="22">
+        <v>3</v>
+      </c>
+      <c r="J39" s="11">
+        <v>4</v>
+      </c>
+      <c r="K39" s="21">
+        <v>3</v>
+      </c>
+      <c r="L39" s="28">
+        <v>40</v>
+      </c>
+      <c r="M39" s="27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="30">
+        <v>0</v>
+      </c>
+      <c r="D40" s="31">
+        <v>0</v>
+      </c>
+      <c r="E40" s="32">
+        <v>0</v>
+      </c>
+      <c r="F40" s="30">
+        <v>0</v>
+      </c>
+      <c r="G40" s="31">
+        <v>1</v>
+      </c>
+      <c r="H40" s="32">
+        <v>0</v>
+      </c>
+      <c r="I40" s="30">
+        <v>1</v>
+      </c>
+      <c r="J40" s="31">
+        <v>1</v>
+      </c>
+      <c r="K40" s="32">
+        <v>1</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B41" s="2"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="11">
+        <v>15</v>
+      </c>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="18">
+        <v>2</v>
+      </c>
+      <c r="E43" s="19">
+        <v>3</v>
+      </c>
+      <c r="F43" s="17">
+        <v>4</v>
+      </c>
+      <c r="G43" s="18">
+        <v>5</v>
+      </c>
+      <c r="H43" s="19">
+        <v>6</v>
+      </c>
+      <c r="I43" s="17">
+        <v>7</v>
+      </c>
+      <c r="J43" s="18">
+        <v>8</v>
+      </c>
+      <c r="K43" s="19">
+        <v>9</v>
+      </c>
+      <c r="L43" s="11"/>
+      <c r="M43" s="27"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B44" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="11">
+        <v>4</v>
+      </c>
+      <c r="D44" s="11">
+        <v>3</v>
+      </c>
+      <c r="E44" s="21">
+        <v>4</v>
+      </c>
+      <c r="F44" s="22">
+        <v>5</v>
+      </c>
+      <c r="G44" s="11">
+        <v>4</v>
+      </c>
+      <c r="H44" s="21">
+        <v>4</v>
+      </c>
+      <c r="I44" s="22">
+        <v>3</v>
+      </c>
+      <c r="J44" s="11">
+        <v>5</v>
+      </c>
+      <c r="K44" s="21">
+        <v>4</v>
+      </c>
+      <c r="L44" s="11">
+        <v>36</v>
+      </c>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B45" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="11">
+        <v>7</v>
+      </c>
+      <c r="D45" s="11">
+        <v>15</v>
+      </c>
+      <c r="E45" s="21">
+        <v>5</v>
+      </c>
+      <c r="F45" s="22">
+        <v>13</v>
+      </c>
+      <c r="G45" s="11">
+        <v>3</v>
+      </c>
+      <c r="H45" s="21">
+        <v>11</v>
+      </c>
+      <c r="I45" s="22">
+        <v>17</v>
+      </c>
+      <c r="J45" s="11">
+        <v>9</v>
+      </c>
+      <c r="K45" s="21">
+        <v>1</v>
+      </c>
+      <c r="L45" s="11"/>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B46" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="24">
+        <v>5</v>
+      </c>
+      <c r="D46" s="25">
+        <v>5</v>
+      </c>
+      <c r="E46" s="26">
+        <v>6</v>
+      </c>
+      <c r="F46" s="24">
+        <v>6</v>
+      </c>
+      <c r="G46" s="25">
+        <v>5</v>
+      </c>
+      <c r="H46" s="26">
+        <v>5</v>
+      </c>
+      <c r="I46" s="24">
+        <v>4</v>
+      </c>
+      <c r="J46" s="25">
+        <v>6</v>
+      </c>
+      <c r="K46" s="26">
+        <v>5</v>
+      </c>
+      <c r="L46" s="11">
+        <v>47</v>
+      </c>
+      <c r="M46" s="27">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B47" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="22">
+        <v>1</v>
+      </c>
+      <c r="D47" s="11">
+        <v>1</v>
+      </c>
+      <c r="E47" s="21">
+        <v>1</v>
+      </c>
+      <c r="F47" s="22">
+        <v>1</v>
+      </c>
+      <c r="G47" s="11">
+        <v>1</v>
+      </c>
+      <c r="H47" s="21">
+        <v>1</v>
+      </c>
+      <c r="I47" s="22">
+        <v>0</v>
+      </c>
+      <c r="J47" s="11">
+        <v>1</v>
+      </c>
+      <c r="K47" s="21">
+        <v>1</v>
+      </c>
+      <c r="L47" s="27"/>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B48" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="22">
+        <v>4</v>
+      </c>
+      <c r="D48" s="11">
+        <v>4</v>
+      </c>
+      <c r="E48" s="21">
+        <v>5</v>
+      </c>
+      <c r="F48" s="22">
+        <v>5</v>
+      </c>
+      <c r="G48" s="11">
+        <v>4</v>
+      </c>
+      <c r="H48" s="21">
+        <v>4</v>
+      </c>
+      <c r="I48" s="22">
+        <v>4</v>
+      </c>
+      <c r="J48" s="11">
+        <v>5</v>
+      </c>
+      <c r="K48" s="21">
+        <v>4</v>
+      </c>
+      <c r="L48" s="28">
+        <v>39</v>
+      </c>
+      <c r="M48" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="30">
+        <v>1</v>
+      </c>
+      <c r="D49" s="31">
+        <v>1</v>
+      </c>
+      <c r="E49" s="32">
+        <v>0</v>
+      </c>
+      <c r="F49" s="30">
+        <v>1</v>
+      </c>
+      <c r="G49" s="31">
+        <v>0</v>
+      </c>
+      <c r="H49" s="32">
+        <v>0</v>
+      </c>
+      <c r="I49" s="30">
+        <v>0</v>
+      </c>
+      <c r="J49" s="31">
+        <v>0</v>
+      </c>
+      <c r="K49" s="32">
+        <v>0</v>
+      </c>
+      <c r="L49" s="11"/>
+      <c r="M49" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C15:K15 C24:K24">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:K40 C49:K49">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5956,18 +7450,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5976,7 +7470,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5985,18 +7479,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6005,7 +7499,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6014,18 +7508,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6034,7 +7528,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6043,7 +7537,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B03FA299-A009-4C43-93DB-8668810D817A}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{632CA295-A26E-4010-8748-F90134476D1A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="38">
   <si>
     <t>Skybrook</t>
   </si>
@@ -531,7 +531,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -5882,81 +5892,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="X27:Y27"/>
     <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="P28:P29"/>
     <mergeCell ref="X28:Y30"/>
     <mergeCell ref="Z28:AA30"/>
     <mergeCell ref="P30:P31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5966,10 +5976,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:M49"/>
+  <dimension ref="B1:M74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7418,27 +7428,761 @@
       <c r="L49" s="11"/>
       <c r="M49" s="2"/>
     </row>
+    <row r="51" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" s="34"/>
+      <c r="L52" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="34"/>
+    </row>
+    <row r="53" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6">
+        <v>2</v>
+      </c>
+      <c r="F53" s="6">
+        <v>1</v>
+      </c>
+      <c r="G53" s="6">
+        <v>5</v>
+      </c>
+      <c r="H53" s="6">
+        <v>42</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="38">
+        <v>8</v>
+      </c>
+      <c r="K53" s="39"/>
+      <c r="L53" s="43">
+        <v>0</v>
+      </c>
+      <c r="M53" s="39"/>
+    </row>
+    <row r="54" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="37"/>
+      <c r="C54" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="8">
+        <v>2</v>
+      </c>
+      <c r="E54" s="8">
+        <v>2</v>
+      </c>
+      <c r="F54" s="8">
+        <v>2</v>
+      </c>
+      <c r="G54" s="8">
+        <v>1</v>
+      </c>
+      <c r="H54" s="8">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="44"/>
+      <c r="M54" s="41"/>
+    </row>
+    <row r="55" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="10">
+        <v>0</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0</v>
+      </c>
+      <c r="F55" s="10">
+        <v>0</v>
+      </c>
+      <c r="G55" s="10">
+        <v>0</v>
+      </c>
+      <c r="H55" s="10">
+        <v>51</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="45"/>
+      <c r="M55" s="42"/>
+    </row>
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="37"/>
+      <c r="C56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="8">
+        <v>0</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0</v>
+      </c>
+      <c r="F56" s="8">
+        <v>0</v>
+      </c>
+      <c r="G56" s="8">
+        <v>0</v>
+      </c>
+      <c r="H56" s="8">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B57" s="2"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="11">
+        <v>20</v>
+      </c>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B59" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="17">
+        <v>1</v>
+      </c>
+      <c r="D59" s="18">
+        <v>2</v>
+      </c>
+      <c r="E59" s="19">
+        <v>3</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4</v>
+      </c>
+      <c r="G59" s="18">
+        <v>5</v>
+      </c>
+      <c r="H59" s="19">
+        <v>6</v>
+      </c>
+      <c r="I59" s="17">
+        <v>7</v>
+      </c>
+      <c r="J59" s="18">
+        <v>8</v>
+      </c>
+      <c r="K59" s="19">
+        <v>9</v>
+      </c>
+      <c r="L59" s="11"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="11">
+        <v>4</v>
+      </c>
+      <c r="D60" s="11">
+        <v>5</v>
+      </c>
+      <c r="E60" s="21">
+        <v>3</v>
+      </c>
+      <c r="F60" s="22">
+        <v>4</v>
+      </c>
+      <c r="G60" s="11">
+        <v>4</v>
+      </c>
+      <c r="H60" s="21">
+        <v>3</v>
+      </c>
+      <c r="I60" s="22">
+        <v>5</v>
+      </c>
+      <c r="J60" s="11">
+        <v>4</v>
+      </c>
+      <c r="K60" s="21">
+        <v>4</v>
+      </c>
+      <c r="L60" s="11">
+        <v>36</v>
+      </c>
+      <c r="M60" s="2"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="11">
+        <v>7</v>
+      </c>
+      <c r="D61" s="11">
+        <v>17</v>
+      </c>
+      <c r="E61" s="21">
+        <v>15</v>
+      </c>
+      <c r="F61" s="22">
+        <v>1</v>
+      </c>
+      <c r="G61" s="11">
+        <v>11</v>
+      </c>
+      <c r="H61" s="21">
+        <v>9</v>
+      </c>
+      <c r="I61" s="22">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11">
+        <v>5</v>
+      </c>
+      <c r="K61" s="21">
+        <v>3</v>
+      </c>
+      <c r="L61" s="11"/>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="24">
+        <v>6</v>
+      </c>
+      <c r="D62" s="25">
+        <v>6</v>
+      </c>
+      <c r="E62" s="26">
+        <v>3</v>
+      </c>
+      <c r="F62" s="24">
+        <v>6</v>
+      </c>
+      <c r="G62" s="25">
+        <v>5</v>
+      </c>
+      <c r="H62" s="26">
+        <v>5</v>
+      </c>
+      <c r="I62" s="24">
+        <v>8</v>
+      </c>
+      <c r="J62" s="25">
+        <v>7</v>
+      </c>
+      <c r="K62" s="26">
+        <v>6</v>
+      </c>
+      <c r="L62" s="11">
+        <v>52</v>
+      </c>
+      <c r="M62" s="27">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B63" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="22">
+        <v>1</v>
+      </c>
+      <c r="D63" s="11">
+        <v>1</v>
+      </c>
+      <c r="E63" s="21">
+        <v>1</v>
+      </c>
+      <c r="F63" s="22">
+        <v>2</v>
+      </c>
+      <c r="G63" s="11">
+        <v>1</v>
+      </c>
+      <c r="H63" s="21">
+        <v>1</v>
+      </c>
+      <c r="I63" s="22">
+        <v>1</v>
+      </c>
+      <c r="J63" s="11">
+        <v>1</v>
+      </c>
+      <c r="K63" s="21">
+        <v>1</v>
+      </c>
+      <c r="L63" s="27"/>
+      <c r="M63" s="2"/>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B64" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="22">
+        <v>5</v>
+      </c>
+      <c r="D64" s="11">
+        <v>5</v>
+      </c>
+      <c r="E64" s="21">
+        <v>2</v>
+      </c>
+      <c r="F64" s="22">
+        <v>4</v>
+      </c>
+      <c r="G64" s="11">
+        <v>4</v>
+      </c>
+      <c r="H64" s="21">
+        <v>4</v>
+      </c>
+      <c r="I64" s="22">
+        <v>7</v>
+      </c>
+      <c r="J64" s="11">
+        <v>6</v>
+      </c>
+      <c r="K64" s="21">
+        <v>5</v>
+      </c>
+      <c r="L64" s="28">
+        <v>42</v>
+      </c>
+      <c r="M64" s="27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="30">
+        <v>1</v>
+      </c>
+      <c r="D65" s="31">
+        <v>1</v>
+      </c>
+      <c r="E65" s="32">
+        <v>0</v>
+      </c>
+      <c r="F65" s="30">
+        <v>1</v>
+      </c>
+      <c r="G65" s="31">
+        <v>1</v>
+      </c>
+      <c r="H65" s="32">
+        <v>0</v>
+      </c>
+      <c r="I65" s="30">
+        <v>0</v>
+      </c>
+      <c r="J65" s="31">
+        <v>0</v>
+      </c>
+      <c r="K65" s="32">
+        <v>1</v>
+      </c>
+      <c r="L65" s="11"/>
+      <c r="M65" s="2"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B66" s="2"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="2"/>
+    </row>
+    <row r="67" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="11">
+        <v>36</v>
+      </c>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="2"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B68" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="17">
+        <v>1</v>
+      </c>
+      <c r="D68" s="18">
+        <v>2</v>
+      </c>
+      <c r="E68" s="19">
+        <v>3</v>
+      </c>
+      <c r="F68" s="17">
+        <v>4</v>
+      </c>
+      <c r="G68" s="18">
+        <v>5</v>
+      </c>
+      <c r="H68" s="19">
+        <v>6</v>
+      </c>
+      <c r="I68" s="17">
+        <v>7</v>
+      </c>
+      <c r="J68" s="18">
+        <v>8</v>
+      </c>
+      <c r="K68" s="19">
+        <v>9</v>
+      </c>
+      <c r="L68" s="11"/>
+      <c r="M68" s="27"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B69" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="11">
+        <v>4</v>
+      </c>
+      <c r="D69" s="11">
+        <v>5</v>
+      </c>
+      <c r="E69" s="21">
+        <v>3</v>
+      </c>
+      <c r="F69" s="22">
+        <v>4</v>
+      </c>
+      <c r="G69" s="11">
+        <v>4</v>
+      </c>
+      <c r="H69" s="21">
+        <v>3</v>
+      </c>
+      <c r="I69" s="22">
+        <v>5</v>
+      </c>
+      <c r="J69" s="11">
+        <v>4</v>
+      </c>
+      <c r="K69" s="21">
+        <v>4</v>
+      </c>
+      <c r="L69" s="11">
+        <v>36</v>
+      </c>
+      <c r="M69" s="2"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B70" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="11">
+        <v>7</v>
+      </c>
+      <c r="D70" s="11">
+        <v>17</v>
+      </c>
+      <c r="E70" s="21">
+        <v>15</v>
+      </c>
+      <c r="F70" s="22">
+        <v>1</v>
+      </c>
+      <c r="G70" s="11">
+        <v>11</v>
+      </c>
+      <c r="H70" s="21">
+        <v>9</v>
+      </c>
+      <c r="I70" s="22">
+        <v>13</v>
+      </c>
+      <c r="J70" s="11">
+        <v>5</v>
+      </c>
+      <c r="K70" s="21">
+        <v>3</v>
+      </c>
+      <c r="L70" s="11"/>
+      <c r="M70" s="2"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="24">
+        <v>8</v>
+      </c>
+      <c r="D71" s="25">
+        <v>10</v>
+      </c>
+      <c r="E71" s="26">
+        <v>4</v>
+      </c>
+      <c r="F71" s="24">
+        <v>8</v>
+      </c>
+      <c r="G71" s="25">
+        <v>8</v>
+      </c>
+      <c r="H71" s="26">
+        <v>6</v>
+      </c>
+      <c r="I71" s="24">
+        <v>9</v>
+      </c>
+      <c r="J71" s="25">
+        <v>8</v>
+      </c>
+      <c r="K71" s="26">
+        <v>8</v>
+      </c>
+      <c r="L71" s="11">
+        <v>69</v>
+      </c>
+      <c r="M71" s="27">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B72" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="22">
+        <v>2</v>
+      </c>
+      <c r="D72" s="11">
+        <v>2</v>
+      </c>
+      <c r="E72" s="21">
+        <v>2</v>
+      </c>
+      <c r="F72" s="22">
+        <v>2</v>
+      </c>
+      <c r="G72" s="11">
+        <v>2</v>
+      </c>
+      <c r="H72" s="21">
+        <v>2</v>
+      </c>
+      <c r="I72" s="22">
+        <v>2</v>
+      </c>
+      <c r="J72" s="11">
+        <v>2</v>
+      </c>
+      <c r="K72" s="21">
+        <v>2</v>
+      </c>
+      <c r="L72" s="27"/>
+      <c r="M72" s="2"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B73" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="22">
+        <v>6</v>
+      </c>
+      <c r="D73" s="11">
+        <v>8</v>
+      </c>
+      <c r="E73" s="21">
+        <v>2</v>
+      </c>
+      <c r="F73" s="22">
+        <v>6</v>
+      </c>
+      <c r="G73" s="11">
+        <v>6</v>
+      </c>
+      <c r="H73" s="21">
+        <v>4</v>
+      </c>
+      <c r="I73" s="22">
+        <v>7</v>
+      </c>
+      <c r="J73" s="11">
+        <v>6</v>
+      </c>
+      <c r="K73" s="21">
+        <v>6</v>
+      </c>
+      <c r="L73" s="28">
+        <v>51</v>
+      </c>
+      <c r="M73" s="27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="30">
+        <v>0</v>
+      </c>
+      <c r="D74" s="31">
+        <v>0</v>
+      </c>
+      <c r="E74" s="32">
+        <v>0</v>
+      </c>
+      <c r="F74" s="30">
+        <v>0</v>
+      </c>
+      <c r="G74" s="31">
+        <v>0</v>
+      </c>
+      <c r="H74" s="32">
+        <v>0</v>
+      </c>
+      <c r="I74" s="30">
+        <v>0</v>
+      </c>
+      <c r="J74" s="31">
+        <v>0</v>
+      </c>
+      <c r="K74" s="32">
+        <v>0</v>
+      </c>
+      <c r="L74" s="11"/>
+      <c r="M74" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="J28:K30"/>
     <mergeCell ref="L28:M30"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:K40 C49:K49">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C40:K40 C49:K49">
+  <conditionalFormatting sqref="C65:K65 C74:K74">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{632CA295-A26E-4010-8748-F90134476D1A}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B43AC6E7-5556-427D-8E2A-B0EBF402ECAF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>Red</t>
+  </si>
+  <si>
+    <t>David Maddox</t>
   </si>
 </sst>
 </file>
@@ -531,7 +534,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -963,15 +986,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:27" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:27" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1029,7 +1052,7 @@
       </c>
       <c r="AA2" s="34"/>
     </row>
-    <row r="3" spans="2:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="36" t="s">
         <v>8</v>
       </c>
@@ -1091,7 +1114,7 @@
       </c>
       <c r="AA3" s="39"/>
     </row>
-    <row r="4" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="37"/>
       <c r="C4" s="7" t="s">
         <v>7</v>
@@ -1141,7 +1164,7 @@
       <c r="Z4" s="44"/>
       <c r="AA4" s="41"/>
     </row>
-    <row r="5" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="36" t="s">
         <v>21</v>
       </c>
@@ -1195,7 +1218,7 @@
       <c r="Z5" s="45"/>
       <c r="AA5" s="42"/>
     </row>
-    <row r="6" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="37"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
@@ -1245,7 +1268,7 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -1271,7 +1294,7 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="2"/>
     </row>
-    <row r="8" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="12" t="s">
         <v>8</v>
       </c>
@@ -1325,7 +1348,7 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
@@ -1391,7 +1414,7 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
@@ -1461,7 +1484,7 @@
       </c>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
@@ -1527,7 +1550,7 @@
       <c r="Z11" s="11"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B12" s="23" t="s">
         <v>17</v>
       </c>
@@ -1601,7 +1624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
@@ -1667,7 +1690,7 @@
       <c r="Z13" s="27"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B14" s="20" t="s">
         <v>19</v>
       </c>
@@ -1741,7 +1764,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="15" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="29" t="s">
         <v>20</v>
       </c>
@@ -1807,7 +1830,7 @@
       <c r="Z15" s="11"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -1833,7 +1856,7 @@
       <c r="Z16" s="11"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="12" t="s">
         <v>21</v>
       </c>
@@ -1887,7 +1910,7 @@
       <c r="Z17" s="11"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
@@ -1953,7 +1976,7 @@
       <c r="Z18" s="11"/>
       <c r="AA18" s="27"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B19" s="20" t="s">
         <v>15</v>
       </c>
@@ -2023,7 +2046,7 @@
       </c>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B20" s="20" t="s">
         <v>16</v>
       </c>
@@ -2089,7 +2112,7 @@
       <c r="Z20" s="11"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
@@ -2163,7 +2186,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B22" s="20" t="s">
         <v>18</v>
       </c>
@@ -2229,7 +2252,7 @@
       <c r="Z22" s="27"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B23" s="20" t="s">
         <v>19</v>
       </c>
@@ -2303,7 +2326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="29" t="s">
         <v>20</v>
       </c>
@@ -2369,8 +2392,8 @@
       <c r="Z24" s="11"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="26" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="2:27" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="2:27" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
@@ -2428,7 +2451,7 @@
       </c>
       <c r="AA27" s="34"/>
     </row>
-    <row r="28" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="36" t="s">
         <v>22</v>
       </c>
@@ -2490,7 +2513,7 @@
       </c>
       <c r="AA28" s="39"/>
     </row>
-    <row r="29" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="37"/>
       <c r="C29" s="7" t="s">
         <v>7</v>
@@ -2540,7 +2563,7 @@
       <c r="Z29" s="44"/>
       <c r="AA29" s="41"/>
     </row>
-    <row r="30" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="36" t="s">
         <v>23</v>
       </c>
@@ -2594,7 +2617,7 @@
       <c r="Z30" s="45"/>
       <c r="AA30" s="42"/>
     </row>
-    <row r="31" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="37"/>
       <c r="C31" s="7" t="s">
         <v>7</v>
@@ -2644,7 +2667,7 @@
       <c r="Z31" s="11"/>
       <c r="AA31" s="11"/>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B32" s="2"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -2670,7 +2693,7 @@
       <c r="Z32" s="11"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="12" t="s">
         <v>22</v>
       </c>
@@ -2724,7 +2747,7 @@
       <c r="Z33" s="11"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B34" s="16" t="s">
         <v>14</v>
       </c>
@@ -2790,7 +2813,7 @@
       <c r="Z34" s="11"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B35" s="20" t="s">
         <v>15</v>
       </c>
@@ -2860,7 +2883,7 @@
       </c>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B36" s="20" t="s">
         <v>16</v>
       </c>
@@ -2926,7 +2949,7 @@
       <c r="Z36" s="11"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B37" s="23" t="s">
         <v>17</v>
       </c>
@@ -3000,7 +3023,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B38" s="20" t="s">
         <v>18</v>
       </c>
@@ -3066,7 +3089,7 @@
       <c r="Z38" s="27"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B39" s="20" t="s">
         <v>19</v>
       </c>
@@ -3140,7 +3163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="29" t="s">
         <v>20</v>
       </c>
@@ -3206,7 +3229,7 @@
       <c r="Z40" s="11"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B41" s="2"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -3232,7 +3255,7 @@
       <c r="Z41" s="11"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="12" t="s">
         <v>23</v>
       </c>
@@ -3286,7 +3309,7 @@
       <c r="Z42" s="11"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B43" s="16" t="s">
         <v>14</v>
       </c>
@@ -3352,7 +3375,7 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="27"/>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B44" s="20" t="s">
         <v>15</v>
       </c>
@@ -3422,7 +3445,7 @@
       </c>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B45" s="20" t="s">
         <v>16</v>
       </c>
@@ -3488,7 +3511,7 @@
       <c r="Z45" s="11"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B46" s="23" t="s">
         <v>17</v>
       </c>
@@ -3562,7 +3585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B47" s="20" t="s">
         <v>18</v>
       </c>
@@ -3628,7 +3651,7 @@
       <c r="Z47" s="27"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B48" s="20" t="s">
         <v>19</v>
       </c>
@@ -3702,7 +3725,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="49" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="29" t="s">
         <v>20</v>
       </c>
@@ -3768,8 +3791,8 @@
       <c r="Z49" s="11"/>
       <c r="AA49" s="2"/>
     </row>
-    <row r="51" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="2:27" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="2:27" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
         <v>24</v>
       </c>
@@ -3827,7 +3850,7 @@
       </c>
       <c r="AA52" s="34"/>
     </row>
-    <row r="53" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>25</v>
       </c>
@@ -3889,7 +3912,7 @@
       </c>
       <c r="AA53" s="39"/>
     </row>
-    <row r="54" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="37"/>
       <c r="C54" s="7" t="s">
         <v>7</v>
@@ -3939,7 +3962,7 @@
       <c r="Z54" s="44"/>
       <c r="AA54" s="41"/>
     </row>
-    <row r="55" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="36" t="s">
         <v>26</v>
       </c>
@@ -3993,7 +4016,7 @@
       <c r="Z55" s="45"/>
       <c r="AA55" s="42"/>
     </row>
-    <row r="56" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="37"/>
       <c r="C56" s="7" t="s">
         <v>7</v>
@@ -4043,7 +4066,7 @@
       <c r="Z56" s="11"/>
       <c r="AA56" s="11"/>
     </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B57" s="2"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
@@ -4069,7 +4092,7 @@
       <c r="Z57" s="11"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="12" t="s">
         <v>25</v>
       </c>
@@ -4123,7 +4146,7 @@
       <c r="Z58" s="11"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B59" s="16" t="s">
         <v>14</v>
       </c>
@@ -4189,7 +4212,7 @@
       <c r="Z59" s="11"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B60" s="20" t="s">
         <v>15</v>
       </c>
@@ -4259,7 +4282,7 @@
       </c>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B61" s="20" t="s">
         <v>16</v>
       </c>
@@ -4325,7 +4348,7 @@
       <c r="Z61" s="11"/>
       <c r="AA61" s="2"/>
     </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B62" s="23" t="s">
         <v>17</v>
       </c>
@@ -4399,7 +4422,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B63" s="20" t="s">
         <v>18</v>
       </c>
@@ -4465,7 +4488,7 @@
       <c r="Z63" s="27"/>
       <c r="AA63" s="2"/>
     </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B64" s="20" t="s">
         <v>19</v>
       </c>
@@ -4539,7 +4562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="29" t="s">
         <v>20</v>
       </c>
@@ -4605,7 +4628,7 @@
       <c r="Z65" s="11"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B66" s="2"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -4631,7 +4654,7 @@
       <c r="Z66" s="11"/>
       <c r="AA66" s="2"/>
     </row>
-    <row r="67" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="12" t="s">
         <v>26</v>
       </c>
@@ -4685,7 +4708,7 @@
       <c r="Z67" s="11"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B68" s="16" t="s">
         <v>14</v>
       </c>
@@ -4751,7 +4774,7 @@
       <c r="Z68" s="11"/>
       <c r="AA68" s="27"/>
     </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B69" s="20" t="s">
         <v>15</v>
       </c>
@@ -4821,7 +4844,7 @@
       </c>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B70" s="20" t="s">
         <v>16</v>
       </c>
@@ -4887,7 +4910,7 @@
       <c r="Z70" s="11"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B71" s="23" t="s">
         <v>17</v>
       </c>
@@ -4961,7 +4984,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B72" s="20" t="s">
         <v>18</v>
       </c>
@@ -5027,7 +5050,7 @@
       <c r="Z72" s="27"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B73" s="20" t="s">
         <v>19</v>
       </c>
@@ -5101,7 +5124,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="29" t="s">
         <v>20</v>
       </c>
@@ -5167,8 +5190,8 @@
       <c r="Z74" s="11"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="76" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="2:27" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="2:27" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B77" s="1" t="s">
         <v>0</v>
       </c>
@@ -5198,7 +5221,7 @@
       </c>
       <c r="M77" s="34"/>
     </row>
-    <row r="78" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B78" s="36" t="s">
         <v>35</v>
       </c>
@@ -5230,7 +5253,7 @@
       </c>
       <c r="M78" s="39"/>
     </row>
-    <row r="79" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="37"/>
       <c r="C79" s="7" t="s">
         <v>7</v>
@@ -5256,7 +5279,7 @@
       <c r="L79" s="44"/>
       <c r="M79" s="41"/>
     </row>
-    <row r="80" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="36" t="s">
         <v>36</v>
       </c>
@@ -5284,7 +5307,7 @@
       <c r="L80" s="45"/>
       <c r="M80" s="42"/>
     </row>
-    <row r="81" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="37"/>
       <c r="C81" s="7" t="s">
         <v>7</v>
@@ -5310,7 +5333,7 @@
       <c r="L81" s="11"/>
       <c r="M81" s="11"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
@@ -5324,7 +5347,7 @@
       <c r="L82" s="11"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B83" s="12" t="s">
         <v>35</v>
       </c>
@@ -5352,7 +5375,7 @@
       <c r="L83" s="11"/>
       <c r="M83" s="2"/>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B84" s="16" t="s">
         <v>14</v>
       </c>
@@ -5386,7 +5409,7 @@
       <c r="L84" s="11"/>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B85" s="20" t="s">
         <v>15</v>
       </c>
@@ -5422,7 +5445,7 @@
       </c>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B86" s="20" t="s">
         <v>16</v>
       </c>
@@ -5456,7 +5479,7 @@
       <c r="L86" s="11"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B87" s="23" t="s">
         <v>17</v>
       </c>
@@ -5494,7 +5517,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B88" s="20" t="s">
         <v>18</v>
       </c>
@@ -5528,7 +5551,7 @@
       <c r="L88" s="27"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B89" s="20" t="s">
         <v>19</v>
       </c>
@@ -5566,7 +5589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B90" s="29" t="s">
         <v>20</v>
       </c>
@@ -5600,7 +5623,7 @@
       <c r="L90" s="11"/>
       <c r="M90" s="2"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B91" s="2"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
@@ -5614,7 +5637,7 @@
       <c r="L91" s="11"/>
       <c r="M91" s="2"/>
     </row>
-    <row r="92" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="12" t="s">
         <v>36</v>
       </c>
@@ -5642,7 +5665,7 @@
       <c r="L92" s="11"/>
       <c r="M92" s="2"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B93" s="16" t="s">
         <v>14</v>
       </c>
@@ -5676,7 +5699,7 @@
       <c r="L93" s="11"/>
       <c r="M93" s="27"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B94" s="20" t="s">
         <v>15</v>
       </c>
@@ -5712,7 +5735,7 @@
       </c>
       <c r="M94" s="2"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B95" s="20" t="s">
         <v>16</v>
       </c>
@@ -5746,7 +5769,7 @@
       <c r="L95" s="11"/>
       <c r="M95" s="2"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B96" s="23" t="s">
         <v>17</v>
       </c>
@@ -5784,7 +5807,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B97" s="20" t="s">
         <v>18</v>
       </c>
@@ -5818,7 +5841,7 @@
       <c r="L97" s="27"/>
       <c r="M97" s="2"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B98" s="20" t="s">
         <v>19</v>
       </c>
@@ -5856,7 +5879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B99" s="29" t="s">
         <v>20</v>
       </c>
@@ -5892,81 +5915,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="P28:P29"/>
+    <mergeCell ref="X28:Y30"/>
+    <mergeCell ref="Z28:AA30"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="J77:K77"/>
     <mergeCell ref="L77:M77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="J78:K80"/>
     <mergeCell ref="L78:M80"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="P28:P29"/>
-    <mergeCell ref="X28:Y30"/>
-    <mergeCell ref="Z28:AA30"/>
-    <mergeCell ref="P30:P31"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5976,14 +5999,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:M74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:M124"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -6013,7 +6036,7 @@
       </c>
       <c r="M2" s="34"/>
     </row>
-    <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="36" t="s">
         <v>21</v>
       </c>
@@ -6045,7 +6068,7 @@
       </c>
       <c r="M3" s="39"/>
     </row>
-    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="37"/>
       <c r="C4" s="7" t="s">
         <v>7</v>
@@ -6071,7 +6094,7 @@
       <c r="L4" s="44"/>
       <c r="M4" s="41"/>
     </row>
-    <row r="5" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="36" t="s">
         <v>23</v>
       </c>
@@ -6099,7 +6122,7 @@
       <c r="L5" s="45"/>
       <c r="M5" s="42"/>
     </row>
-    <row r="6" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="37"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
@@ -6125,7 +6148,7 @@
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -6139,7 +6162,7 @@
       <c r="L7" s="11"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="12" t="s">
         <v>21</v>
       </c>
@@ -6167,7 +6190,7 @@
       <c r="L8" s="11"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
@@ -6201,7 +6224,7 @@
       <c r="L9" s="11"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
@@ -6237,7 +6260,7 @@
       </c>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
@@ -6271,7 +6294,7 @@
       <c r="L11" s="11"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="23" t="s">
         <v>17</v>
       </c>
@@ -6309,7 +6332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
@@ -6343,7 +6366,7 @@
       <c r="L13" s="27"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="20" t="s">
         <v>19</v>
       </c>
@@ -6381,7 +6404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="29" t="s">
         <v>20</v>
       </c>
@@ -6415,7 +6438,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -6429,7 +6452,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="12" t="s">
         <v>23</v>
       </c>
@@ -6457,7 +6480,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
@@ -6491,7 +6514,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="27"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="20" t="s">
         <v>15</v>
       </c>
@@ -6527,7 +6550,7 @@
       </c>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="20" t="s">
         <v>16</v>
       </c>
@@ -6561,7 +6584,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
@@ -6599,7 +6622,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="20" t="s">
         <v>18</v>
       </c>
@@ -6633,7 +6656,7 @@
       <c r="L22" s="27"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="20" t="s">
         <v>19</v>
       </c>
@@ -6671,7 +6694,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="29" t="s">
         <v>20</v>
       </c>
@@ -6705,8 +6728,8 @@
       <c r="L24" s="11"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="26" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
@@ -6736,7 +6759,7 @@
       </c>
       <c r="M27" s="34"/>
     </row>
-    <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="36" t="s">
         <v>8</v>
       </c>
@@ -6768,7 +6791,7 @@
       </c>
       <c r="M28" s="39"/>
     </row>
-    <row r="29" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="37"/>
       <c r="C29" s="7" t="s">
         <v>7</v>
@@ -6794,7 +6817,7 @@
       <c r="L29" s="44"/>
       <c r="M29" s="41"/>
     </row>
-    <row r="30" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="36" t="s">
         <v>22</v>
       </c>
@@ -6822,7 +6845,7 @@
       <c r="L30" s="45"/>
       <c r="M30" s="42"/>
     </row>
-    <row r="31" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="37"/>
       <c r="C31" s="7" t="s">
         <v>7</v>
@@ -6848,7 +6871,7 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="2"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -6862,7 +6885,7 @@
       <c r="L32" s="11"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="12" t="s">
         <v>8</v>
       </c>
@@ -6890,7 +6913,7 @@
       <c r="L33" s="11"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="16" t="s">
         <v>14</v>
       </c>
@@ -6924,7 +6947,7 @@
       <c r="L34" s="11"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="20" t="s">
         <v>15</v>
       </c>
@@ -6960,7 +6983,7 @@
       </c>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="20" t="s">
         <v>16</v>
       </c>
@@ -6994,7 +7017,7 @@
       <c r="L36" s="11"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="23" t="s">
         <v>17</v>
       </c>
@@ -7032,7 +7055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="20" t="s">
         <v>18</v>
       </c>
@@ -7066,7 +7089,7 @@
       <c r="L38" s="27"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="20" t="s">
         <v>19</v>
       </c>
@@ -7104,7 +7127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="29" t="s">
         <v>20</v>
       </c>
@@ -7138,7 +7161,7 @@
       <c r="L40" s="11"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="2"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -7152,7 +7175,7 @@
       <c r="L41" s="11"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="12" t="s">
         <v>22</v>
       </c>
@@ -7180,7 +7203,7 @@
       <c r="L42" s="11"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="16" t="s">
         <v>14</v>
       </c>
@@ -7214,7 +7237,7 @@
       <c r="L43" s="11"/>
       <c r="M43" s="27"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="20" t="s">
         <v>15</v>
       </c>
@@ -7250,7 +7273,7 @@
       </c>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="20" t="s">
         <v>16</v>
       </c>
@@ -7284,7 +7307,7 @@
       <c r="L45" s="11"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="23" t="s">
         <v>17</v>
       </c>
@@ -7322,7 +7345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="20" t="s">
         <v>18</v>
       </c>
@@ -7356,7 +7379,7 @@
       <c r="L47" s="27"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B48" s="20" t="s">
         <v>19</v>
       </c>
@@ -7394,7 +7417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="29" t="s">
         <v>20</v>
       </c>
@@ -7428,8 +7451,8 @@
       <c r="L49" s="11"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="51" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
         <v>24</v>
       </c>
@@ -7459,7 +7482,7 @@
       </c>
       <c r="M52" s="34"/>
     </row>
-    <row r="53" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="36" t="s">
         <v>31</v>
       </c>
@@ -7491,7 +7514,7 @@
       </c>
       <c r="M53" s="39"/>
     </row>
-    <row r="54" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="37"/>
       <c r="C54" s="7" t="s">
         <v>7</v>
@@ -7517,7 +7540,7 @@
       <c r="L54" s="44"/>
       <c r="M54" s="41"/>
     </row>
-    <row r="55" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="36" t="s">
         <v>26</v>
       </c>
@@ -7545,7 +7568,7 @@
       <c r="L55" s="45"/>
       <c r="M55" s="42"/>
     </row>
-    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="37"/>
       <c r="C56" s="7" t="s">
         <v>7</v>
@@ -7571,7 +7594,7 @@
       <c r="L56" s="11"/>
       <c r="M56" s="11"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B57" s="2"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
@@ -7585,7 +7608,7 @@
       <c r="L57" s="11"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="12" t="s">
         <v>31</v>
       </c>
@@ -7613,7 +7636,7 @@
       <c r="L58" s="11"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B59" s="16" t="s">
         <v>14</v>
       </c>
@@ -7647,7 +7670,7 @@
       <c r="L59" s="11"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B60" s="20" t="s">
         <v>15</v>
       </c>
@@ -7683,7 +7706,7 @@
       </c>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B61" s="20" t="s">
         <v>16</v>
       </c>
@@ -7717,7 +7740,7 @@
       <c r="L61" s="11"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B62" s="23" t="s">
         <v>17</v>
       </c>
@@ -7755,7 +7778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B63" s="20" t="s">
         <v>18</v>
       </c>
@@ -7789,7 +7812,7 @@
       <c r="L63" s="27"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B64" s="20" t="s">
         <v>19</v>
       </c>
@@ -7827,7 +7850,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="29" t="s">
         <v>20</v>
       </c>
@@ -7861,7 +7884,7 @@
       <c r="L65" s="11"/>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66" s="2"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -7875,7 +7898,7 @@
       <c r="L66" s="11"/>
       <c r="M66" s="2"/>
     </row>
-    <row r="67" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="12" t="s">
         <v>26</v>
       </c>
@@ -7903,7 +7926,7 @@
       <c r="L67" s="11"/>
       <c r="M67" s="2"/>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="16" t="s">
         <v>14</v>
       </c>
@@ -7937,7 +7960,7 @@
       <c r="L68" s="11"/>
       <c r="M68" s="27"/>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="20" t="s">
         <v>15</v>
       </c>
@@ -7973,7 +7996,7 @@
       </c>
       <c r="M69" s="2"/>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70" s="20" t="s">
         <v>16</v>
       </c>
@@ -8007,7 +8030,7 @@
       <c r="L70" s="11"/>
       <c r="M70" s="2"/>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71" s="23" t="s">
         <v>17</v>
       </c>
@@ -8045,7 +8068,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" s="20" t="s">
         <v>18</v>
       </c>
@@ -8079,7 +8102,7 @@
       <c r="L72" s="27"/>
       <c r="M72" s="2"/>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B73" s="20" t="s">
         <v>19</v>
       </c>
@@ -8117,7 +8140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="29" t="s">
         <v>20</v>
       </c>
@@ -8151,38 +8174,1506 @@
       <c r="L74" s="11"/>
       <c r="M74" s="2"/>
     </row>
+    <row r="76" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="K77" s="34"/>
+      <c r="L77" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="M77" s="34"/>
+    </row>
+    <row r="78" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="6">
+        <v>1</v>
+      </c>
+      <c r="E78" s="6">
+        <v>2</v>
+      </c>
+      <c r="F78" s="6">
+        <v>1</v>
+      </c>
+      <c r="G78" s="6">
+        <v>4</v>
+      </c>
+      <c r="H78" s="6">
+        <v>38</v>
+      </c>
+      <c r="I78" s="2"/>
+      <c r="J78" s="38">
+        <v>6</v>
+      </c>
+      <c r="K78" s="39"/>
+      <c r="L78" s="43">
+        <v>2</v>
+      </c>
+      <c r="M78" s="39"/>
+    </row>
+    <row r="79" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="37"/>
+      <c r="C79" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="8">
+        <v>1</v>
+      </c>
+      <c r="E79" s="8">
+        <v>2</v>
+      </c>
+      <c r="F79" s="8">
+        <v>1</v>
+      </c>
+      <c r="G79" s="8">
+        <v>1</v>
+      </c>
+      <c r="H79" s="8">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2"/>
+      <c r="J79" s="40"/>
+      <c r="K79" s="41"/>
+      <c r="L79" s="44"/>
+      <c r="M79" s="41"/>
+    </row>
+    <row r="80" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="10">
+        <v>1</v>
+      </c>
+      <c r="E80" s="10">
+        <v>1</v>
+      </c>
+      <c r="F80" s="10">
+        <v>1</v>
+      </c>
+      <c r="G80" s="10">
+        <v>3</v>
+      </c>
+      <c r="H80" s="10">
+        <v>39</v>
+      </c>
+      <c r="I80" s="2"/>
+      <c r="J80" s="37"/>
+      <c r="K80" s="42"/>
+      <c r="L80" s="45"/>
+      <c r="M80" s="42"/>
+    </row>
+    <row r="81" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="37"/>
+      <c r="C81" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="8">
+        <v>1</v>
+      </c>
+      <c r="E81" s="8">
+        <v>0</v>
+      </c>
+      <c r="F81" s="8">
+        <v>1</v>
+      </c>
+      <c r="G81" s="8">
+        <v>0</v>
+      </c>
+      <c r="H81" s="8">
+        <v>0</v>
+      </c>
+      <c r="I81" s="2"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+    </row>
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B82" s="2"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="2"/>
+    </row>
+    <row r="83" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B83" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="11">
+        <v>28</v>
+      </c>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="2"/>
+    </row>
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B84" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="17">
+        <v>1</v>
+      </c>
+      <c r="D84" s="18">
+        <v>2</v>
+      </c>
+      <c r="E84" s="19">
+        <v>3</v>
+      </c>
+      <c r="F84" s="17">
+        <v>4</v>
+      </c>
+      <c r="G84" s="18">
+        <v>5</v>
+      </c>
+      <c r="H84" s="19">
+        <v>6</v>
+      </c>
+      <c r="I84" s="17">
+        <v>7</v>
+      </c>
+      <c r="J84" s="18">
+        <v>8</v>
+      </c>
+      <c r="K84" s="19">
+        <v>9</v>
+      </c>
+      <c r="L84" s="11"/>
+      <c r="M84" s="2"/>
+    </row>
+    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B85" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="11">
+        <v>4</v>
+      </c>
+      <c r="D85" s="11">
+        <v>3</v>
+      </c>
+      <c r="E85" s="21">
+        <v>4</v>
+      </c>
+      <c r="F85" s="22">
+        <v>5</v>
+      </c>
+      <c r="G85" s="11">
+        <v>4</v>
+      </c>
+      <c r="H85" s="21">
+        <v>4</v>
+      </c>
+      <c r="I85" s="22">
+        <v>3</v>
+      </c>
+      <c r="J85" s="11">
+        <v>5</v>
+      </c>
+      <c r="K85" s="21">
+        <v>4</v>
+      </c>
+      <c r="L85" s="11">
+        <v>36</v>
+      </c>
+      <c r="M85" s="2"/>
+    </row>
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B86" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="11">
+        <v>7</v>
+      </c>
+      <c r="D86" s="11">
+        <v>15</v>
+      </c>
+      <c r="E86" s="21">
+        <v>5</v>
+      </c>
+      <c r="F86" s="22">
+        <v>13</v>
+      </c>
+      <c r="G86" s="11">
+        <v>3</v>
+      </c>
+      <c r="H86" s="21">
+        <v>11</v>
+      </c>
+      <c r="I86" s="22">
+        <v>17</v>
+      </c>
+      <c r="J86" s="11">
+        <v>9</v>
+      </c>
+      <c r="K86" s="21">
+        <v>1</v>
+      </c>
+      <c r="L86" s="11"/>
+      <c r="M86" s="2"/>
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B87" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="24">
+        <v>5</v>
+      </c>
+      <c r="D87" s="25">
+        <v>4</v>
+      </c>
+      <c r="E87" s="26">
+        <v>8</v>
+      </c>
+      <c r="F87" s="24">
+        <v>7</v>
+      </c>
+      <c r="G87" s="25">
+        <v>5</v>
+      </c>
+      <c r="H87" s="26">
+        <v>5</v>
+      </c>
+      <c r="I87" s="24">
+        <v>5</v>
+      </c>
+      <c r="J87" s="25">
+        <v>5</v>
+      </c>
+      <c r="K87" s="26">
+        <v>8</v>
+      </c>
+      <c r="L87" s="11">
+        <v>52</v>
+      </c>
+      <c r="M87" s="27">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B88" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="22">
+        <v>2</v>
+      </c>
+      <c r="D88" s="11">
+        <v>1</v>
+      </c>
+      <c r="E88" s="21">
+        <v>2</v>
+      </c>
+      <c r="F88" s="22">
+        <v>1</v>
+      </c>
+      <c r="G88" s="11">
+        <v>2</v>
+      </c>
+      <c r="H88" s="21">
+        <v>1</v>
+      </c>
+      <c r="I88" s="22">
+        <v>1</v>
+      </c>
+      <c r="J88" s="11">
+        <v>2</v>
+      </c>
+      <c r="K88" s="21">
+        <v>2</v>
+      </c>
+      <c r="L88" s="27"/>
+      <c r="M88" s="2"/>
+    </row>
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B89" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" s="22">
+        <v>3</v>
+      </c>
+      <c r="D89" s="11">
+        <v>3</v>
+      </c>
+      <c r="E89" s="21">
+        <v>6</v>
+      </c>
+      <c r="F89" s="22">
+        <v>6</v>
+      </c>
+      <c r="G89" s="11">
+        <v>3</v>
+      </c>
+      <c r="H89" s="21">
+        <v>4</v>
+      </c>
+      <c r="I89" s="22">
+        <v>4</v>
+      </c>
+      <c r="J89" s="11">
+        <v>3</v>
+      </c>
+      <c r="K89" s="21">
+        <v>6</v>
+      </c>
+      <c r="L89" s="28">
+        <v>38</v>
+      </c>
+      <c r="M89" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B90" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" s="30">
+        <v>1</v>
+      </c>
+      <c r="D90" s="31">
+        <v>0</v>
+      </c>
+      <c r="E90" s="32">
+        <v>0</v>
+      </c>
+      <c r="F90" s="30">
+        <v>0</v>
+      </c>
+      <c r="G90" s="31">
+        <v>1</v>
+      </c>
+      <c r="H90" s="32">
+        <v>1</v>
+      </c>
+      <c r="I90" s="30">
+        <v>0</v>
+      </c>
+      <c r="J90" s="31">
+        <v>1</v>
+      </c>
+      <c r="K90" s="32">
+        <v>0</v>
+      </c>
+      <c r="L90" s="11"/>
+      <c r="M90" s="2"/>
+    </row>
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B91" s="2"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="11"/>
+      <c r="M91" s="2"/>
+    </row>
+    <row r="92" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="11">
+        <v>24</v>
+      </c>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="2"/>
+    </row>
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B93" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" s="17">
+        <v>1</v>
+      </c>
+      <c r="D93" s="18">
+        <v>2</v>
+      </c>
+      <c r="E93" s="19">
+        <v>3</v>
+      </c>
+      <c r="F93" s="17">
+        <v>4</v>
+      </c>
+      <c r="G93" s="18">
+        <v>5</v>
+      </c>
+      <c r="H93" s="19">
+        <v>6</v>
+      </c>
+      <c r="I93" s="17">
+        <v>7</v>
+      </c>
+      <c r="J93" s="18">
+        <v>8</v>
+      </c>
+      <c r="K93" s="19">
+        <v>9</v>
+      </c>
+      <c r="L93" s="11"/>
+      <c r="M93" s="27"/>
+    </row>
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B94" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="11">
+        <v>4</v>
+      </c>
+      <c r="D94" s="11">
+        <v>3</v>
+      </c>
+      <c r="E94" s="21">
+        <v>4</v>
+      </c>
+      <c r="F94" s="22">
+        <v>5</v>
+      </c>
+      <c r="G94" s="11">
+        <v>4</v>
+      </c>
+      <c r="H94" s="21">
+        <v>4</v>
+      </c>
+      <c r="I94" s="22">
+        <v>3</v>
+      </c>
+      <c r="J94" s="11">
+        <v>5</v>
+      </c>
+      <c r="K94" s="21">
+        <v>4</v>
+      </c>
+      <c r="L94" s="11">
+        <v>36</v>
+      </c>
+      <c r="M94" s="2"/>
+    </row>
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B95" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="11">
+        <v>7</v>
+      </c>
+      <c r="D95" s="11">
+        <v>15</v>
+      </c>
+      <c r="E95" s="21">
+        <v>5</v>
+      </c>
+      <c r="F95" s="22">
+        <v>13</v>
+      </c>
+      <c r="G95" s="11">
+        <v>3</v>
+      </c>
+      <c r="H95" s="21">
+        <v>11</v>
+      </c>
+      <c r="I95" s="22">
+        <v>17</v>
+      </c>
+      <c r="J95" s="11">
+        <v>9</v>
+      </c>
+      <c r="K95" s="21">
+        <v>1</v>
+      </c>
+      <c r="L95" s="11"/>
+      <c r="M95" s="2"/>
+    </row>
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B96" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="24">
+        <v>6</v>
+      </c>
+      <c r="D96" s="25">
+        <v>4</v>
+      </c>
+      <c r="E96" s="26">
+        <v>5</v>
+      </c>
+      <c r="F96" s="24">
+        <v>6</v>
+      </c>
+      <c r="G96" s="25">
+        <v>7</v>
+      </c>
+      <c r="H96" s="26">
+        <v>6</v>
+      </c>
+      <c r="I96" s="24">
+        <v>5</v>
+      </c>
+      <c r="J96" s="25">
+        <v>7</v>
+      </c>
+      <c r="K96" s="26">
+        <v>5</v>
+      </c>
+      <c r="L96" s="11">
+        <v>51</v>
+      </c>
+      <c r="M96" s="27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B97" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="22">
+        <v>1</v>
+      </c>
+      <c r="D97" s="11">
+        <v>1</v>
+      </c>
+      <c r="E97" s="21">
+        <v>2</v>
+      </c>
+      <c r="F97" s="22">
+        <v>1</v>
+      </c>
+      <c r="G97" s="11">
+        <v>2</v>
+      </c>
+      <c r="H97" s="21">
+        <v>1</v>
+      </c>
+      <c r="I97" s="22">
+        <v>1</v>
+      </c>
+      <c r="J97" s="11">
+        <v>1</v>
+      </c>
+      <c r="K97" s="21">
+        <v>2</v>
+      </c>
+      <c r="L97" s="27"/>
+      <c r="M97" s="2"/>
+    </row>
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B98" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" s="22">
+        <v>5</v>
+      </c>
+      <c r="D98" s="11">
+        <v>3</v>
+      </c>
+      <c r="E98" s="21">
+        <v>3</v>
+      </c>
+      <c r="F98" s="22">
+        <v>5</v>
+      </c>
+      <c r="G98" s="11">
+        <v>5</v>
+      </c>
+      <c r="H98" s="21">
+        <v>5</v>
+      </c>
+      <c r="I98" s="22">
+        <v>4</v>
+      </c>
+      <c r="J98" s="11">
+        <v>6</v>
+      </c>
+      <c r="K98" s="21">
+        <v>3</v>
+      </c>
+      <c r="L98" s="28">
+        <v>39</v>
+      </c>
+      <c r="M98" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" s="30">
+        <v>0</v>
+      </c>
+      <c r="D99" s="31">
+        <v>0</v>
+      </c>
+      <c r="E99" s="32">
+        <v>1</v>
+      </c>
+      <c r="F99" s="30">
+        <v>1</v>
+      </c>
+      <c r="G99" s="31">
+        <v>0</v>
+      </c>
+      <c r="H99" s="32">
+        <v>0</v>
+      </c>
+      <c r="I99" s="30">
+        <v>0</v>
+      </c>
+      <c r="J99" s="31">
+        <v>0</v>
+      </c>
+      <c r="K99" s="32">
+        <v>1</v>
+      </c>
+      <c r="L99" s="11"/>
+      <c r="M99" s="2"/>
+    </row>
+    <row r="101" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="102" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B102" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="4"/>
+      <c r="J102" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="K102" s="34"/>
+      <c r="L102" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="M102" s="34"/>
+    </row>
+    <row r="103" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B103" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" s="6">
+        <v>2</v>
+      </c>
+      <c r="E103" s="6">
+        <v>3</v>
+      </c>
+      <c r="F103" s="6">
+        <v>1</v>
+      </c>
+      <c r="G103" s="6">
+        <v>6</v>
+      </c>
+      <c r="H103" s="6">
+        <v>43</v>
+      </c>
+      <c r="I103" s="2"/>
+      <c r="J103" s="38">
+        <v>8</v>
+      </c>
+      <c r="K103" s="39"/>
+      <c r="L103" s="43">
+        <v>0</v>
+      </c>
+      <c r="M103" s="39"/>
+    </row>
+    <row r="104" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B104" s="37"/>
+      <c r="C104" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="8">
+        <v>2</v>
+      </c>
+      <c r="E104" s="8">
+        <v>2</v>
+      </c>
+      <c r="F104" s="8">
+        <v>2</v>
+      </c>
+      <c r="G104" s="8">
+        <v>1</v>
+      </c>
+      <c r="H104" s="8">
+        <v>1</v>
+      </c>
+      <c r="I104" s="2"/>
+      <c r="J104" s="40"/>
+      <c r="K104" s="41"/>
+      <c r="L104" s="44"/>
+      <c r="M104" s="41"/>
+    </row>
+    <row r="105" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" s="10">
+        <v>0</v>
+      </c>
+      <c r="E105" s="10">
+        <v>0</v>
+      </c>
+      <c r="F105" s="10">
+        <v>0</v>
+      </c>
+      <c r="G105" s="10">
+        <v>0</v>
+      </c>
+      <c r="H105" s="10">
+        <v>52</v>
+      </c>
+      <c r="I105" s="2"/>
+      <c r="J105" s="37"/>
+      <c r="K105" s="42"/>
+      <c r="L105" s="45"/>
+      <c r="M105" s="42"/>
+    </row>
+    <row r="106" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B106" s="37"/>
+      <c r="C106" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="8">
+        <v>0</v>
+      </c>
+      <c r="E106" s="8">
+        <v>0</v>
+      </c>
+      <c r="F106" s="8">
+        <v>0</v>
+      </c>
+      <c r="G106" s="8">
+        <v>0</v>
+      </c>
+      <c r="H106" s="8">
+        <v>0</v>
+      </c>
+      <c r="I106" s="2"/>
+      <c r="J106" s="11"/>
+      <c r="K106" s="11"/>
+      <c r="L106" s="11"/>
+      <c r="M106" s="11"/>
+    </row>
+    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B107" s="2"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="11"/>
+      <c r="I107" s="11"/>
+      <c r="J107" s="11"/>
+      <c r="K107" s="11"/>
+      <c r="L107" s="11"/>
+      <c r="M107" s="2"/>
+    </row>
+    <row r="108" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="11">
+        <v>36</v>
+      </c>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H108" s="11"/>
+      <c r="I108" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K108" s="11"/>
+      <c r="L108" s="11"/>
+      <c r="M108" s="2"/>
+    </row>
+    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B109" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" s="17">
+        <v>1</v>
+      </c>
+      <c r="D109" s="18">
+        <v>2</v>
+      </c>
+      <c r="E109" s="19">
+        <v>3</v>
+      </c>
+      <c r="F109" s="17">
+        <v>4</v>
+      </c>
+      <c r="G109" s="18">
+        <v>5</v>
+      </c>
+      <c r="H109" s="19">
+        <v>6</v>
+      </c>
+      <c r="I109" s="17">
+        <v>7</v>
+      </c>
+      <c r="J109" s="18">
+        <v>8</v>
+      </c>
+      <c r="K109" s="19">
+        <v>9</v>
+      </c>
+      <c r="L109" s="11"/>
+      <c r="M109" s="2"/>
+    </row>
+    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B110" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" s="11">
+        <v>4</v>
+      </c>
+      <c r="D110" s="11">
+        <v>3</v>
+      </c>
+      <c r="E110" s="21">
+        <v>4</v>
+      </c>
+      <c r="F110" s="22">
+        <v>5</v>
+      </c>
+      <c r="G110" s="11">
+        <v>4</v>
+      </c>
+      <c r="H110" s="21">
+        <v>4</v>
+      </c>
+      <c r="I110" s="22">
+        <v>3</v>
+      </c>
+      <c r="J110" s="11">
+        <v>5</v>
+      </c>
+      <c r="K110" s="21">
+        <v>4</v>
+      </c>
+      <c r="L110" s="11">
+        <v>36</v>
+      </c>
+      <c r="M110" s="2"/>
+    </row>
+    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B111" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" s="11">
+        <v>7</v>
+      </c>
+      <c r="D111" s="11">
+        <v>15</v>
+      </c>
+      <c r="E111" s="21">
+        <v>5</v>
+      </c>
+      <c r="F111" s="22">
+        <v>13</v>
+      </c>
+      <c r="G111" s="11">
+        <v>3</v>
+      </c>
+      <c r="H111" s="21">
+        <v>11</v>
+      </c>
+      <c r="I111" s="22">
+        <v>17</v>
+      </c>
+      <c r="J111" s="11">
+        <v>9</v>
+      </c>
+      <c r="K111" s="21">
+        <v>1</v>
+      </c>
+      <c r="L111" s="11"/>
+      <c r="M111" s="2"/>
+    </row>
+    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B112" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" s="24">
+        <v>8</v>
+      </c>
+      <c r="D112" s="25">
+        <v>5</v>
+      </c>
+      <c r="E112" s="26">
+        <v>7</v>
+      </c>
+      <c r="F112" s="24">
+        <v>8</v>
+      </c>
+      <c r="G112" s="25">
+        <v>7</v>
+      </c>
+      <c r="H112" s="26">
+        <v>5</v>
+      </c>
+      <c r="I112" s="24">
+        <v>6</v>
+      </c>
+      <c r="J112" s="25">
+        <v>7</v>
+      </c>
+      <c r="K112" s="26">
+        <v>8</v>
+      </c>
+      <c r="L112" s="11">
+        <v>61</v>
+      </c>
+      <c r="M112" s="27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B113" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" s="22">
+        <v>2</v>
+      </c>
+      <c r="D113" s="11">
+        <v>2</v>
+      </c>
+      <c r="E113" s="21">
+        <v>2</v>
+      </c>
+      <c r="F113" s="22">
+        <v>2</v>
+      </c>
+      <c r="G113" s="11">
+        <v>2</v>
+      </c>
+      <c r="H113" s="21">
+        <v>2</v>
+      </c>
+      <c r="I113" s="22">
+        <v>2</v>
+      </c>
+      <c r="J113" s="11">
+        <v>2</v>
+      </c>
+      <c r="K113" s="21">
+        <v>2</v>
+      </c>
+      <c r="L113" s="27"/>
+      <c r="M113" s="2"/>
+    </row>
+    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B114" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114" s="22">
+        <v>6</v>
+      </c>
+      <c r="D114" s="11">
+        <v>3</v>
+      </c>
+      <c r="E114" s="21">
+        <v>5</v>
+      </c>
+      <c r="F114" s="22">
+        <v>6</v>
+      </c>
+      <c r="G114" s="11">
+        <v>5</v>
+      </c>
+      <c r="H114" s="21">
+        <v>3</v>
+      </c>
+      <c r="I114" s="22">
+        <v>4</v>
+      </c>
+      <c r="J114" s="11">
+        <v>5</v>
+      </c>
+      <c r="K114" s="21">
+        <v>6</v>
+      </c>
+      <c r="L114" s="28">
+        <v>43</v>
+      </c>
+      <c r="M114" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="30">
+        <v>0</v>
+      </c>
+      <c r="D115" s="31">
+        <v>1</v>
+      </c>
+      <c r="E115" s="32">
+        <v>1</v>
+      </c>
+      <c r="F115" s="30">
+        <v>1</v>
+      </c>
+      <c r="G115" s="31">
+        <v>1</v>
+      </c>
+      <c r="H115" s="32">
+        <v>1</v>
+      </c>
+      <c r="I115" s="30">
+        <v>0</v>
+      </c>
+      <c r="J115" s="31">
+        <v>1</v>
+      </c>
+      <c r="K115" s="32">
+        <v>0</v>
+      </c>
+      <c r="L115" s="11"/>
+      <c r="M115" s="2"/>
+    </row>
+    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B116" s="2"/>
+      <c r="C116" s="11"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
+      <c r="F116" s="11"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="11"/>
+      <c r="I116" s="11"/>
+      <c r="J116" s="11"/>
+      <c r="K116" s="11"/>
+      <c r="L116" s="11"/>
+      <c r="M116" s="2"/>
+    </row>
+    <row r="117" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B117" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="11">
+        <v>36</v>
+      </c>
+      <c r="E117" s="11"/>
+      <c r="F117" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H117" s="11"/>
+      <c r="I117" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J117" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K117" s="11"/>
+      <c r="L117" s="11"/>
+      <c r="M117" s="2"/>
+    </row>
+    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B118" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" s="17">
+        <v>1</v>
+      </c>
+      <c r="D118" s="18">
+        <v>2</v>
+      </c>
+      <c r="E118" s="19">
+        <v>3</v>
+      </c>
+      <c r="F118" s="17">
+        <v>4</v>
+      </c>
+      <c r="G118" s="18">
+        <v>5</v>
+      </c>
+      <c r="H118" s="19">
+        <v>6</v>
+      </c>
+      <c r="I118" s="17">
+        <v>7</v>
+      </c>
+      <c r="J118" s="18">
+        <v>8</v>
+      </c>
+      <c r="K118" s="19">
+        <v>9</v>
+      </c>
+      <c r="L118" s="11"/>
+      <c r="M118" s="27"/>
+    </row>
+    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B119" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="11">
+        <v>4</v>
+      </c>
+      <c r="D119" s="11">
+        <v>3</v>
+      </c>
+      <c r="E119" s="21">
+        <v>4</v>
+      </c>
+      <c r="F119" s="22">
+        <v>5</v>
+      </c>
+      <c r="G119" s="11">
+        <v>4</v>
+      </c>
+      <c r="H119" s="21">
+        <v>4</v>
+      </c>
+      <c r="I119" s="22">
+        <v>3</v>
+      </c>
+      <c r="J119" s="11">
+        <v>5</v>
+      </c>
+      <c r="K119" s="21">
+        <v>4</v>
+      </c>
+      <c r="L119" s="11">
+        <v>36</v>
+      </c>
+      <c r="M119" s="2"/>
+    </row>
+    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B120" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" s="11">
+        <v>17</v>
+      </c>
+      <c r="D120" s="11">
+        <v>9</v>
+      </c>
+      <c r="E120" s="21">
+        <v>5</v>
+      </c>
+      <c r="F120" s="22">
+        <v>7</v>
+      </c>
+      <c r="G120" s="11">
+        <v>3</v>
+      </c>
+      <c r="H120" s="21">
+        <v>15</v>
+      </c>
+      <c r="I120" s="22">
+        <v>11</v>
+      </c>
+      <c r="J120" s="11">
+        <v>13</v>
+      </c>
+      <c r="K120" s="21">
+        <v>1</v>
+      </c>
+      <c r="L120" s="11"/>
+      <c r="M120" s="2"/>
+    </row>
+    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B121" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" s="24">
+        <v>8</v>
+      </c>
+      <c r="D121" s="25">
+        <v>6</v>
+      </c>
+      <c r="E121" s="26">
+        <v>8</v>
+      </c>
+      <c r="F121" s="24">
+        <v>10</v>
+      </c>
+      <c r="G121" s="25">
+        <v>8</v>
+      </c>
+      <c r="H121" s="26">
+        <v>6</v>
+      </c>
+      <c r="I121" s="24">
+        <v>6</v>
+      </c>
+      <c r="J121" s="25">
+        <v>10</v>
+      </c>
+      <c r="K121" s="26">
+        <v>8</v>
+      </c>
+      <c r="L121" s="11">
+        <v>70</v>
+      </c>
+      <c r="M121" s="27">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B122" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C122" s="22">
+        <v>2</v>
+      </c>
+      <c r="D122" s="11">
+        <v>2</v>
+      </c>
+      <c r="E122" s="21">
+        <v>2</v>
+      </c>
+      <c r="F122" s="22">
+        <v>2</v>
+      </c>
+      <c r="G122" s="11">
+        <v>2</v>
+      </c>
+      <c r="H122" s="21">
+        <v>2</v>
+      </c>
+      <c r="I122" s="22">
+        <v>2</v>
+      </c>
+      <c r="J122" s="11">
+        <v>2</v>
+      </c>
+      <c r="K122" s="21">
+        <v>2</v>
+      </c>
+      <c r="L122" s="27"/>
+      <c r="M122" s="2"/>
+    </row>
+    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B123" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C123" s="22">
+        <v>6</v>
+      </c>
+      <c r="D123" s="11">
+        <v>4</v>
+      </c>
+      <c r="E123" s="21">
+        <v>6</v>
+      </c>
+      <c r="F123" s="22">
+        <v>8</v>
+      </c>
+      <c r="G123" s="11">
+        <v>6</v>
+      </c>
+      <c r="H123" s="21">
+        <v>4</v>
+      </c>
+      <c r="I123" s="22">
+        <v>4</v>
+      </c>
+      <c r="J123" s="11">
+        <v>8</v>
+      </c>
+      <c r="K123" s="21">
+        <v>6</v>
+      </c>
+      <c r="L123" s="28">
+        <v>52</v>
+      </c>
+      <c r="M123" s="27">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" s="30">
+        <v>0</v>
+      </c>
+      <c r="D124" s="31">
+        <v>0</v>
+      </c>
+      <c r="E124" s="32">
+        <v>0</v>
+      </c>
+      <c r="F124" s="30">
+        <v>0</v>
+      </c>
+      <c r="G124" s="31">
+        <v>0</v>
+      </c>
+      <c r="H124" s="32">
+        <v>0</v>
+      </c>
+      <c r="I124" s="30">
+        <v>0</v>
+      </c>
+      <c r="J124" s="31">
+        <v>0</v>
+      </c>
+      <c r="K124" s="32">
+        <v>0</v>
+      </c>
+      <c r="L124" s="11"/>
+      <c r="M124" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="30">
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="L52:M52"/>
     <mergeCell ref="B53:B54"/>
     <mergeCell ref="J53:K55"/>
     <mergeCell ref="L53:M55"/>
     <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C90:K90 C99:K99">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C115:K115 C124:K124">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -8194,18 +9685,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8214,7 +9705,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8223,18 +9714,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8243,7 +9734,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8252,18 +9743,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8272,7 +9763,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8281,7 +9772,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B43AC6E7-5556-427D-8E2A-B0EBF402ECAF}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6BAA437-66F2-4DE3-A76A-AB323EB73F36}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -534,7 +534,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -986,15 +996,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA99"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:27" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:27" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1062,7 @@
       </c>
       <c r="AA2" s="34"/>
     </row>
-    <row r="3" spans="2:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="36" t="s">
         <v>8</v>
       </c>
@@ -1114,7 +1124,7 @@
       </c>
       <c r="AA3" s="39"/>
     </row>
-    <row r="4" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="37"/>
       <c r="C4" s="7" t="s">
         <v>7</v>
@@ -1164,7 +1174,7 @@
       <c r="Z4" s="44"/>
       <c r="AA4" s="41"/>
     </row>
-    <row r="5" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="36" t="s">
         <v>21</v>
       </c>
@@ -1218,7 +1228,7 @@
       <c r="Z5" s="45"/>
       <c r="AA5" s="42"/>
     </row>
-    <row r="6" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="37"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
@@ -1268,7 +1278,7 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -1294,7 +1304,7 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="2"/>
     </row>
-    <row r="8" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
         <v>8</v>
       </c>
@@ -1348,7 +1358,7 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
@@ -1414,7 +1424,7 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
@@ -1484,7 +1494,7 @@
       </c>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
@@ -1550,7 +1560,7 @@
       <c r="Z11" s="11"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" s="23" t="s">
         <v>17</v>
       </c>
@@ -1624,7 +1634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
@@ -1690,7 +1700,7 @@
       <c r="Z13" s="27"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
         <v>19</v>
       </c>
@@ -1764,7 +1774,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="15" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>20</v>
       </c>
@@ -1830,7 +1840,7 @@
       <c r="Z15" s="11"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -1856,7 +1866,7 @@
       <c r="Z16" s="11"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="12" t="s">
         <v>21</v>
       </c>
@@ -1910,7 +1920,7 @@
       <c r="Z17" s="11"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
@@ -1976,7 +1986,7 @@
       <c r="Z18" s="11"/>
       <c r="AA18" s="27"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B19" s="20" t="s">
         <v>15</v>
       </c>
@@ -2046,7 +2056,7 @@
       </c>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
         <v>16</v>
       </c>
@@ -2112,7 +2122,7 @@
       <c r="Z20" s="11"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
@@ -2186,7 +2196,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B22" s="20" t="s">
         <v>18</v>
       </c>
@@ -2252,7 +2262,7 @@
       <c r="Z22" s="27"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B23" s="20" t="s">
         <v>19</v>
       </c>
@@ -2326,7 +2336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="29" t="s">
         <v>20</v>
       </c>
@@ -2392,8 +2402,8 @@
       <c r="Z24" s="11"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="26" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:27" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:27" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
@@ -2451,7 +2461,7 @@
       </c>
       <c r="AA27" s="34"/>
     </row>
-    <row r="28" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="36" t="s">
         <v>22</v>
       </c>
@@ -2513,7 +2523,7 @@
       </c>
       <c r="AA28" s="39"/>
     </row>
-    <row r="29" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="37"/>
       <c r="C29" s="7" t="s">
         <v>7</v>
@@ -2563,7 +2573,7 @@
       <c r="Z29" s="44"/>
       <c r="AA29" s="41"/>
     </row>
-    <row r="30" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="36" t="s">
         <v>23</v>
       </c>
@@ -2617,7 +2627,7 @@
       <c r="Z30" s="45"/>
       <c r="AA30" s="42"/>
     </row>
-    <row r="31" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="37"/>
       <c r="C31" s="7" t="s">
         <v>7</v>
@@ -2667,7 +2677,7 @@
       <c r="Z31" s="11"/>
       <c r="AA31" s="11"/>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -2693,7 +2703,7 @@
       <c r="Z32" s="11"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
         <v>22</v>
       </c>
@@ -2747,7 +2757,7 @@
       <c r="Z33" s="11"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" s="16" t="s">
         <v>14</v>
       </c>
@@ -2813,7 +2823,7 @@
       <c r="Z34" s="11"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" s="20" t="s">
         <v>15</v>
       </c>
@@ -2883,7 +2893,7 @@
       </c>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
         <v>16</v>
       </c>
@@ -2949,7 +2959,7 @@
       <c r="Z36" s="11"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B37" s="23" t="s">
         <v>17</v>
       </c>
@@ -3023,7 +3033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
         <v>18</v>
       </c>
@@ -3089,7 +3099,7 @@
       <c r="Z38" s="27"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
         <v>19</v>
       </c>
@@ -3163,7 +3173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="29" t="s">
         <v>20</v>
       </c>
@@ -3229,7 +3239,7 @@
       <c r="Z40" s="11"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -3255,7 +3265,7 @@
       <c r="Z41" s="11"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="2:27" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:27" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="12" t="s">
         <v>23</v>
       </c>
@@ -3309,7 +3319,7 @@
       <c r="Z42" s="11"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
         <v>14</v>
       </c>
@@ -3375,7 +3385,7 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="27"/>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" s="20" t="s">
         <v>15</v>
       </c>
@@ -3445,7 +3455,7 @@
       </c>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="20" t="s">
         <v>16</v>
       </c>
@@ -3511,7 +3521,7 @@
       <c r="Z45" s="11"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="23" t="s">
         <v>17</v>
       </c>
@@ -3585,7 +3595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="20" t="s">
         <v>18</v>
       </c>
@@ -3651,7 +3661,7 @@
       <c r="Z47" s="27"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
         <v>19</v>
       </c>
@@ -3725,7 +3735,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="49" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="29" t="s">
         <v>20</v>
       </c>
@@ -3791,8 +3801,8 @@
       <c r="Z49" s="11"/>
       <c r="AA49" s="2"/>
     </row>
-    <row r="51" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="2:27" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:27" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>24</v>
       </c>
@@ -3850,7 +3860,7 @@
       </c>
       <c r="AA52" s="34"/>
     </row>
-    <row r="53" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>25</v>
       </c>
@@ -3912,7 +3922,7 @@
       </c>
       <c r="AA53" s="39"/>
     </row>
-    <row r="54" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="37"/>
       <c r="C54" s="7" t="s">
         <v>7</v>
@@ -3962,7 +3972,7 @@
       <c r="Z54" s="44"/>
       <c r="AA54" s="41"/>
     </row>
-    <row r="55" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="36" t="s">
         <v>26</v>
       </c>
@@ -4016,7 +4026,7 @@
       <c r="Z55" s="45"/>
       <c r="AA55" s="42"/>
     </row>
-    <row r="56" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="37"/>
       <c r="C56" s="7" t="s">
         <v>7</v>
@@ -4066,7 +4076,7 @@
       <c r="Z56" s="11"/>
       <c r="AA56" s="11"/>
     </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
@@ -4092,7 +4102,7 @@
       <c r="Z57" s="11"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="12" t="s">
         <v>25</v>
       </c>
@@ -4146,7 +4156,7 @@
       <c r="Z58" s="11"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B59" s="16" t="s">
         <v>14</v>
       </c>
@@ -4212,7 +4222,7 @@
       <c r="Z59" s="11"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
         <v>15</v>
       </c>
@@ -4282,7 +4292,7 @@
       </c>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
         <v>16</v>
       </c>
@@ -4348,7 +4358,7 @@
       <c r="Z61" s="11"/>
       <c r="AA61" s="2"/>
     </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B62" s="23" t="s">
         <v>17</v>
       </c>
@@ -4422,7 +4432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
         <v>18</v>
       </c>
@@ -4488,7 +4498,7 @@
       <c r="Z63" s="27"/>
       <c r="AA63" s="2"/>
     </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B64" s="20" t="s">
         <v>19</v>
       </c>
@@ -4562,7 +4572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="29" t="s">
         <v>20</v>
       </c>
@@ -4628,7 +4638,7 @@
       <c r="Z65" s="11"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -4654,7 +4664,7 @@
       <c r="Z66" s="11"/>
       <c r="AA66" s="2"/>
     </row>
-    <row r="67" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="12" t="s">
         <v>26</v>
       </c>
@@ -4708,7 +4718,7 @@
       <c r="Z67" s="11"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B68" s="16" t="s">
         <v>14</v>
       </c>
@@ -4774,7 +4784,7 @@
       <c r="Z68" s="11"/>
       <c r="AA68" s="27"/>
     </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B69" s="20" t="s">
         <v>15</v>
       </c>
@@ -4844,7 +4854,7 @@
       </c>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
         <v>16</v>
       </c>
@@ -4910,7 +4920,7 @@
       <c r="Z70" s="11"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B71" s="23" t="s">
         <v>17</v>
       </c>
@@ -4984,7 +4994,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B72" s="20" t="s">
         <v>18</v>
       </c>
@@ -5050,7 +5060,7 @@
       <c r="Z72" s="27"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
         <v>19</v>
       </c>
@@ -5124,7 +5134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="29" t="s">
         <v>20</v>
       </c>
@@ -5190,8 +5200,8 @@
       <c r="Z74" s="11"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="76" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="2:27" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:27" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
         <v>0</v>
       </c>
@@ -5221,7 +5231,7 @@
       </c>
       <c r="M77" s="34"/>
     </row>
-    <row r="78" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="36" t="s">
         <v>35</v>
       </c>
@@ -5253,7 +5263,7 @@
       </c>
       <c r="M78" s="39"/>
     </row>
-    <row r="79" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="37"/>
       <c r="C79" s="7" t="s">
         <v>7</v>
@@ -5279,7 +5289,7 @@
       <c r="L79" s="44"/>
       <c r="M79" s="41"/>
     </row>
-    <row r="80" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="36" t="s">
         <v>36</v>
       </c>
@@ -5307,7 +5317,7 @@
       <c r="L80" s="45"/>
       <c r="M80" s="42"/>
     </row>
-    <row r="81" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="37"/>
       <c r="C81" s="7" t="s">
         <v>7</v>
@@ -5333,7 +5343,7 @@
       <c r="L81" s="11"/>
       <c r="M81" s="11"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
@@ -5347,7 +5357,7 @@
       <c r="L82" s="11"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="12" t="s">
         <v>35</v>
       </c>
@@ -5375,7 +5385,7 @@
       <c r="L83" s="11"/>
       <c r="M83" s="2"/>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B84" s="16" t="s">
         <v>14</v>
       </c>
@@ -5409,7 +5419,7 @@
       <c r="L84" s="11"/>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B85" s="20" t="s">
         <v>15</v>
       </c>
@@ -5445,7 +5455,7 @@
       </c>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B86" s="20" t="s">
         <v>16</v>
       </c>
@@ -5479,7 +5489,7 @@
       <c r="L86" s="11"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B87" s="23" t="s">
         <v>17</v>
       </c>
@@ -5517,7 +5527,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B88" s="20" t="s">
         <v>18</v>
       </c>
@@ -5551,7 +5561,7 @@
       <c r="L88" s="27"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
         <v>19</v>
       </c>
@@ -5589,7 +5599,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="29" t="s">
         <v>20</v>
       </c>
@@ -5623,7 +5633,7 @@
       <c r="L90" s="11"/>
       <c r="M90" s="2"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
@@ -5637,7 +5647,7 @@
       <c r="L91" s="11"/>
       <c r="M91" s="2"/>
     </row>
-    <row r="92" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="12" t="s">
         <v>36</v>
       </c>
@@ -5665,7 +5675,7 @@
       <c r="L92" s="11"/>
       <c r="M92" s="2"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B93" s="16" t="s">
         <v>14</v>
       </c>
@@ -5699,7 +5709,7 @@
       <c r="L93" s="11"/>
       <c r="M93" s="27"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B94" s="20" t="s">
         <v>15</v>
       </c>
@@ -5735,7 +5745,7 @@
       </c>
       <c r="M94" s="2"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B95" s="20" t="s">
         <v>16</v>
       </c>
@@ -5769,7 +5779,7 @@
       <c r="L95" s="11"/>
       <c r="M95" s="2"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B96" s="23" t="s">
         <v>17</v>
       </c>
@@ -5807,7 +5817,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B97" s="20" t="s">
         <v>18</v>
       </c>
@@ -5841,7 +5851,7 @@
       <c r="L97" s="27"/>
       <c r="M97" s="2"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B98" s="20" t="s">
         <v>19</v>
       </c>
@@ -5879,7 +5889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="29" t="s">
         <v>20</v>
       </c>
@@ -5915,81 +5925,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="X27:Y27"/>
     <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="P28:P29"/>
     <mergeCell ref="X28:Y30"/>
     <mergeCell ref="Z28:AA30"/>
     <mergeCell ref="P30:P31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5999,14 +6009,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:M124"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:M149"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -6036,7 +6046,7 @@
       </c>
       <c r="M2" s="34"/>
     </row>
-    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="36" t="s">
         <v>21</v>
       </c>
@@ -6068,7 +6078,7 @@
       </c>
       <c r="M3" s="39"/>
     </row>
-    <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="37"/>
       <c r="C4" s="7" t="s">
         <v>7</v>
@@ -6094,7 +6104,7 @@
       <c r="L4" s="44"/>
       <c r="M4" s="41"/>
     </row>
-    <row r="5" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="36" t="s">
         <v>23</v>
       </c>
@@ -6122,7 +6132,7 @@
       <c r="L5" s="45"/>
       <c r="M5" s="42"/>
     </row>
-    <row r="6" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="37"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
@@ -6148,7 +6158,7 @@
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -6162,7 +6172,7 @@
       <c r="L7" s="11"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
         <v>21</v>
       </c>
@@ -6190,7 +6200,7 @@
       <c r="L8" s="11"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
@@ -6224,7 +6234,7 @@
       <c r="L9" s="11"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
@@ -6260,7 +6270,7 @@
       </c>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
@@ -6294,7 +6304,7 @@
       <c r="L11" s="11"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="23" t="s">
         <v>17</v>
       </c>
@@ -6332,7 +6342,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
@@ -6366,7 +6376,7 @@
       <c r="L13" s="27"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
         <v>19</v>
       </c>
@@ -6404,7 +6414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>20</v>
       </c>
@@ -6438,7 +6448,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -6452,7 +6462,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="12" t="s">
         <v>23</v>
       </c>
@@ -6480,7 +6490,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
@@ -6514,7 +6524,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="27"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19" s="20" t="s">
         <v>15</v>
       </c>
@@ -6550,7 +6560,7 @@
       </c>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
         <v>16</v>
       </c>
@@ -6584,7 +6594,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
@@ -6622,7 +6632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" s="20" t="s">
         <v>18</v>
       </c>
@@ -6656,7 +6666,7 @@
       <c r="L22" s="27"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" s="20" t="s">
         <v>19</v>
       </c>
@@ -6694,7 +6704,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="29" t="s">
         <v>20</v>
       </c>
@@ -6728,8 +6738,8 @@
       <c r="L24" s="11"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="26" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
@@ -6759,7 +6769,7 @@
       </c>
       <c r="M27" s="34"/>
     </row>
-    <row r="28" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="36" t="s">
         <v>8</v>
       </c>
@@ -6791,7 +6801,7 @@
       </c>
       <c r="M28" s="39"/>
     </row>
-    <row r="29" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="37"/>
       <c r="C29" s="7" t="s">
         <v>7</v>
@@ -6817,7 +6827,7 @@
       <c r="L29" s="44"/>
       <c r="M29" s="41"/>
     </row>
-    <row r="30" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="36" t="s">
         <v>22</v>
       </c>
@@ -6845,7 +6855,7 @@
       <c r="L30" s="45"/>
       <c r="M30" s="42"/>
     </row>
-    <row r="31" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="37"/>
       <c r="C31" s="7" t="s">
         <v>7</v>
@@ -6871,7 +6881,7 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -6885,7 +6895,7 @@
       <c r="L32" s="11"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
         <v>8</v>
       </c>
@@ -6913,7 +6923,7 @@
       <c r="L33" s="11"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="16" t="s">
         <v>14</v>
       </c>
@@ -6947,7 +6957,7 @@
       <c r="L34" s="11"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="20" t="s">
         <v>15</v>
       </c>
@@ -6983,7 +6993,7 @@
       </c>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
         <v>16</v>
       </c>
@@ -7017,7 +7027,7 @@
       <c r="L36" s="11"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="23" t="s">
         <v>17</v>
       </c>
@@ -7055,7 +7065,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
         <v>18</v>
       </c>
@@ -7089,7 +7099,7 @@
       <c r="L38" s="27"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
         <v>19</v>
       </c>
@@ -7127,7 +7137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="29" t="s">
         <v>20</v>
       </c>
@@ -7161,7 +7171,7 @@
       <c r="L40" s="11"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -7175,7 +7185,7 @@
       <c r="L41" s="11"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="12" t="s">
         <v>22</v>
       </c>
@@ -7203,7 +7213,7 @@
       <c r="L42" s="11"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
         <v>14</v>
       </c>
@@ -7237,7 +7247,7 @@
       <c r="L43" s="11"/>
       <c r="M43" s="27"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="20" t="s">
         <v>15</v>
       </c>
@@ -7273,7 +7283,7 @@
       </c>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="20" t="s">
         <v>16</v>
       </c>
@@ -7307,7 +7317,7 @@
       <c r="L45" s="11"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="23" t="s">
         <v>17</v>
       </c>
@@ -7345,7 +7355,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="20" t="s">
         <v>18</v>
       </c>
@@ -7379,7 +7389,7 @@
       <c r="L47" s="27"/>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
         <v>19</v>
       </c>
@@ -7417,7 +7427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="29" t="s">
         <v>20</v>
       </c>
@@ -7451,8 +7461,8 @@
       <c r="L49" s="11"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="51" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>24</v>
       </c>
@@ -7482,7 +7492,7 @@
       </c>
       <c r="M52" s="34"/>
     </row>
-    <row r="53" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>31</v>
       </c>
@@ -7514,7 +7524,7 @@
       </c>
       <c r="M53" s="39"/>
     </row>
-    <row r="54" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="37"/>
       <c r="C54" s="7" t="s">
         <v>7</v>
@@ -7540,7 +7550,7 @@
       <c r="L54" s="44"/>
       <c r="M54" s="41"/>
     </row>
-    <row r="55" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="36" t="s">
         <v>26</v>
       </c>
@@ -7568,7 +7578,7 @@
       <c r="L55" s="45"/>
       <c r="M55" s="42"/>
     </row>
-    <row r="56" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="37"/>
       <c r="C56" s="7" t="s">
         <v>7</v>
@@ -7594,7 +7604,7 @@
       <c r="L56" s="11"/>
       <c r="M56" s="11"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
@@ -7608,7 +7618,7 @@
       <c r="L57" s="11"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="12" t="s">
         <v>31</v>
       </c>
@@ -7636,7 +7646,7 @@
       <c r="L58" s="11"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59" s="16" t="s">
         <v>14</v>
       </c>
@@ -7670,7 +7680,7 @@
       <c r="L59" s="11"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
         <v>15</v>
       </c>
@@ -7706,7 +7716,7 @@
       </c>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
         <v>16</v>
       </c>
@@ -7740,7 +7750,7 @@
       <c r="L61" s="11"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62" s="23" t="s">
         <v>17</v>
       </c>
@@ -7778,7 +7788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
         <v>18</v>
       </c>
@@ -7812,7 +7822,7 @@
       <c r="L63" s="27"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B64" s="20" t="s">
         <v>19</v>
       </c>
@@ -7850,7 +7860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="29" t="s">
         <v>20</v>
       </c>
@@ -7884,7 +7894,7 @@
       <c r="L65" s="11"/>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -7898,7 +7908,7 @@
       <c r="L66" s="11"/>
       <c r="M66" s="2"/>
     </row>
-    <row r="67" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="12" t="s">
         <v>26</v>
       </c>
@@ -7926,7 +7936,7 @@
       <c r="L67" s="11"/>
       <c r="M67" s="2"/>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B68" s="16" t="s">
         <v>14</v>
       </c>
@@ -7960,7 +7970,7 @@
       <c r="L68" s="11"/>
       <c r="M68" s="27"/>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B69" s="20" t="s">
         <v>15</v>
       </c>
@@ -7996,7 +8006,7 @@
       </c>
       <c r="M69" s="2"/>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
         <v>16</v>
       </c>
@@ -8030,7 +8040,7 @@
       <c r="L70" s="11"/>
       <c r="M70" s="2"/>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B71" s="23" t="s">
         <v>17</v>
       </c>
@@ -8068,7 +8078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B72" s="20" t="s">
         <v>18</v>
       </c>
@@ -8102,7 +8112,7 @@
       <c r="L72" s="27"/>
       <c r="M72" s="2"/>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
         <v>19</v>
       </c>
@@ -8140,7 +8150,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="29" t="s">
         <v>20</v>
       </c>
@@ -8174,8 +8184,8 @@
       <c r="L74" s="11"/>
       <c r="M74" s="2"/>
     </row>
-    <row r="76" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
         <v>0</v>
       </c>
@@ -8205,7 +8215,7 @@
       </c>
       <c r="M77" s="34"/>
     </row>
-    <row r="78" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="36" t="s">
         <v>32</v>
       </c>
@@ -8237,7 +8247,7 @@
       </c>
       <c r="M78" s="39"/>
     </row>
-    <row r="79" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="37"/>
       <c r="C79" s="7" t="s">
         <v>7</v>
@@ -8263,7 +8273,7 @@
       <c r="L79" s="44"/>
       <c r="M79" s="41"/>
     </row>
-    <row r="80" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="36" t="s">
         <v>27</v>
       </c>
@@ -8291,7 +8301,7 @@
       <c r="L80" s="45"/>
       <c r="M80" s="42"/>
     </row>
-    <row r="81" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="37"/>
       <c r="C81" s="7" t="s">
         <v>7</v>
@@ -8317,7 +8327,7 @@
       <c r="L81" s="11"/>
       <c r="M81" s="11"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
@@ -8331,7 +8341,7 @@
       <c r="L82" s="11"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="12" t="s">
         <v>32</v>
       </c>
@@ -8359,7 +8369,7 @@
       <c r="L83" s="11"/>
       <c r="M83" s="2"/>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B84" s="16" t="s">
         <v>14</v>
       </c>
@@ -8393,7 +8403,7 @@
       <c r="L84" s="11"/>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B85" s="20" t="s">
         <v>15</v>
       </c>
@@ -8429,7 +8439,7 @@
       </c>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B86" s="20" t="s">
         <v>16</v>
       </c>
@@ -8463,7 +8473,7 @@
       <c r="L86" s="11"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B87" s="23" t="s">
         <v>17</v>
       </c>
@@ -8501,7 +8511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B88" s="20" t="s">
         <v>18</v>
       </c>
@@ -8535,7 +8545,7 @@
       <c r="L88" s="27"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
         <v>19</v>
       </c>
@@ -8573,7 +8583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="29" t="s">
         <v>20</v>
       </c>
@@ -8607,7 +8617,7 @@
       <c r="L90" s="11"/>
       <c r="M90" s="2"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
@@ -8621,7 +8631,7 @@
       <c r="L91" s="11"/>
       <c r="M91" s="2"/>
     </row>
-    <row r="92" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="12" t="s">
         <v>27</v>
       </c>
@@ -8649,7 +8659,7 @@
       <c r="L92" s="11"/>
       <c r="M92" s="2"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B93" s="16" t="s">
         <v>14</v>
       </c>
@@ -8683,7 +8693,7 @@
       <c r="L93" s="11"/>
       <c r="M93" s="27"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B94" s="20" t="s">
         <v>15</v>
       </c>
@@ -8719,7 +8729,7 @@
       </c>
       <c r="M94" s="2"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B95" s="20" t="s">
         <v>16</v>
       </c>
@@ -8753,7 +8763,7 @@
       <c r="L95" s="11"/>
       <c r="M95" s="2"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B96" s="23" t="s">
         <v>17</v>
       </c>
@@ -8791,7 +8801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B97" s="20" t="s">
         <v>18</v>
       </c>
@@ -8825,7 +8835,7 @@
       <c r="L97" s="27"/>
       <c r="M97" s="2"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B98" s="20" t="s">
         <v>19</v>
       </c>
@@ -8863,7 +8873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="29" t="s">
         <v>20</v>
       </c>
@@ -8897,8 +8907,8 @@
       <c r="L99" s="11"/>
       <c r="M99" s="2"/>
     </row>
-    <row r="101" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="102" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
         <v>0</v>
       </c>
@@ -8928,7 +8938,7 @@
       </c>
       <c r="M102" s="34"/>
     </row>
-    <row r="103" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="36" t="s">
         <v>38</v>
       </c>
@@ -8960,7 +8970,7 @@
       </c>
       <c r="M103" s="39"/>
     </row>
-    <row r="104" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="37"/>
       <c r="C104" s="7" t="s">
         <v>7</v>
@@ -8986,7 +8996,7 @@
       <c r="L104" s="44"/>
       <c r="M104" s="41"/>
     </row>
-    <row r="105" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="36" t="s">
         <v>35</v>
       </c>
@@ -9014,7 +9024,7 @@
       <c r="L105" s="45"/>
       <c r="M105" s="42"/>
     </row>
-    <row r="106" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="37"/>
       <c r="C106" s="7" t="s">
         <v>7</v>
@@ -9040,7 +9050,7 @@
       <c r="L106" s="11"/>
       <c r="M106" s="11"/>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B107" s="2"/>
       <c r="C107" s="11"/>
       <c r="D107" s="11"/>
@@ -9054,7 +9064,7 @@
       <c r="L107" s="11"/>
       <c r="M107" s="2"/>
     </row>
-    <row r="108" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="12" t="s">
         <v>38</v>
       </c>
@@ -9082,7 +9092,7 @@
       <c r="L108" s="11"/>
       <c r="M108" s="2"/>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B109" s="16" t="s">
         <v>14</v>
       </c>
@@ -9116,7 +9126,7 @@
       <c r="L109" s="11"/>
       <c r="M109" s="2"/>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B110" s="20" t="s">
         <v>15</v>
       </c>
@@ -9152,7 +9162,7 @@
       </c>
       <c r="M110" s="2"/>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B111" s="20" t="s">
         <v>16</v>
       </c>
@@ -9186,7 +9196,7 @@
       <c r="L111" s="11"/>
       <c r="M111" s="2"/>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B112" s="23" t="s">
         <v>17</v>
       </c>
@@ -9224,7 +9234,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B113" s="20" t="s">
         <v>18</v>
       </c>
@@ -9258,7 +9268,7 @@
       <c r="L113" s="27"/>
       <c r="M113" s="2"/>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B114" s="20" t="s">
         <v>19</v>
       </c>
@@ -9296,7 +9306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B115" s="29" t="s">
         <v>20</v>
       </c>
@@ -9330,7 +9340,7 @@
       <c r="L115" s="11"/>
       <c r="M115" s="2"/>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B116" s="2"/>
       <c r="C116" s="11"/>
       <c r="D116" s="11"/>
@@ -9344,7 +9354,7 @@
       <c r="L116" s="11"/>
       <c r="M116" s="2"/>
     </row>
-    <row r="117" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B117" s="12" t="s">
         <v>35</v>
       </c>
@@ -9372,7 +9382,7 @@
       <c r="L117" s="11"/>
       <c r="M117" s="2"/>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B118" s="16" t="s">
         <v>14</v>
       </c>
@@ -9406,7 +9416,7 @@
       <c r="L118" s="11"/>
       <c r="M118" s="27"/>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B119" s="20" t="s">
         <v>15</v>
       </c>
@@ -9442,7 +9452,7 @@
       </c>
       <c r="M119" s="2"/>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B120" s="20" t="s">
         <v>16</v>
       </c>
@@ -9476,7 +9486,7 @@
       <c r="L120" s="11"/>
       <c r="M120" s="2"/>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B121" s="23" t="s">
         <v>17</v>
       </c>
@@ -9514,7 +9524,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B122" s="20" t="s">
         <v>18</v>
       </c>
@@ -9548,7 +9558,7 @@
       <c r="L122" s="27"/>
       <c r="M122" s="2"/>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B123" s="20" t="s">
         <v>19</v>
       </c>
@@ -9586,7 +9596,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="124" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="29" t="s">
         <v>20</v>
       </c>
@@ -9620,60 +9630,794 @@
       <c r="L124" s="11"/>
       <c r="M124" s="2"/>
     </row>
+    <row r="126" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="127" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B127" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I127" s="4"/>
+      <c r="J127" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="K127" s="34"/>
+      <c r="L127" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M127" s="34"/>
+    </row>
+    <row r="128" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" s="6">
+        <v>2</v>
+      </c>
+      <c r="E128" s="6">
+        <v>3</v>
+      </c>
+      <c r="F128" s="6">
+        <v>3</v>
+      </c>
+      <c r="G128" s="6">
+        <v>8</v>
+      </c>
+      <c r="H128" s="6">
+        <v>36</v>
+      </c>
+      <c r="I128" s="2"/>
+      <c r="J128" s="38">
+        <v>8</v>
+      </c>
+      <c r="K128" s="39"/>
+      <c r="L128" s="43">
+        <v>0</v>
+      </c>
+      <c r="M128" s="39"/>
+    </row>
+    <row r="129" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B129" s="37"/>
+      <c r="C129" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="8">
+        <v>2</v>
+      </c>
+      <c r="E129" s="8">
+        <v>2</v>
+      </c>
+      <c r="F129" s="8">
+        <v>2</v>
+      </c>
+      <c r="G129" s="8">
+        <v>1</v>
+      </c>
+      <c r="H129" s="8">
+        <v>1</v>
+      </c>
+      <c r="I129" s="2"/>
+      <c r="J129" s="40"/>
+      <c r="K129" s="41"/>
+      <c r="L129" s="44"/>
+      <c r="M129" s="41"/>
+    </row>
+    <row r="130" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B130" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" s="10">
+        <v>0</v>
+      </c>
+      <c r="E130" s="10">
+        <v>0</v>
+      </c>
+      <c r="F130" s="10">
+        <v>0</v>
+      </c>
+      <c r="G130" s="10">
+        <v>0</v>
+      </c>
+      <c r="H130" s="10">
+        <v>54</v>
+      </c>
+      <c r="I130" s="2"/>
+      <c r="J130" s="37"/>
+      <c r="K130" s="42"/>
+      <c r="L130" s="45"/>
+      <c r="M130" s="42"/>
+    </row>
+    <row r="131" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="37"/>
+      <c r="C131" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" s="8">
+        <v>0</v>
+      </c>
+      <c r="E131" s="8">
+        <v>0</v>
+      </c>
+      <c r="F131" s="8">
+        <v>0</v>
+      </c>
+      <c r="G131" s="8">
+        <v>0</v>
+      </c>
+      <c r="H131" s="8">
+        <v>0</v>
+      </c>
+      <c r="I131" s="2"/>
+      <c r="J131" s="11"/>
+      <c r="K131" s="11"/>
+      <c r="L131" s="11"/>
+      <c r="M131" s="11"/>
+    </row>
+    <row r="132" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B132" s="2"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="11"/>
+      <c r="H132" s="11"/>
+      <c r="I132" s="11"/>
+      <c r="J132" s="11"/>
+      <c r="K132" s="11"/>
+      <c r="L132" s="11"/>
+      <c r="M132" s="2"/>
+    </row>
+    <row r="133" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B133" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C133" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="11">
+        <v>30</v>
+      </c>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G133" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H133" s="11"/>
+      <c r="I133" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J133" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K133" s="11"/>
+      <c r="L133" s="11"/>
+      <c r="M133" s="2"/>
+    </row>
+    <row r="134" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B134" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134" s="17">
+        <v>1</v>
+      </c>
+      <c r="D134" s="18">
+        <v>2</v>
+      </c>
+      <c r="E134" s="19">
+        <v>3</v>
+      </c>
+      <c r="F134" s="17">
+        <v>4</v>
+      </c>
+      <c r="G134" s="18">
+        <v>5</v>
+      </c>
+      <c r="H134" s="19">
+        <v>6</v>
+      </c>
+      <c r="I134" s="17">
+        <v>7</v>
+      </c>
+      <c r="J134" s="18">
+        <v>8</v>
+      </c>
+      <c r="K134" s="19">
+        <v>9</v>
+      </c>
+      <c r="L134" s="11"/>
+      <c r="M134" s="2"/>
+    </row>
+    <row r="135" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B135" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135" s="11">
+        <v>4</v>
+      </c>
+      <c r="D135" s="11">
+        <v>3</v>
+      </c>
+      <c r="E135" s="21">
+        <v>4</v>
+      </c>
+      <c r="F135" s="22">
+        <v>5</v>
+      </c>
+      <c r="G135" s="11">
+        <v>4</v>
+      </c>
+      <c r="H135" s="21">
+        <v>4</v>
+      </c>
+      <c r="I135" s="22">
+        <v>3</v>
+      </c>
+      <c r="J135" s="11">
+        <v>5</v>
+      </c>
+      <c r="K135" s="21">
+        <v>4</v>
+      </c>
+      <c r="L135" s="11">
+        <v>36</v>
+      </c>
+      <c r="M135" s="2"/>
+    </row>
+    <row r="136" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B136" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" s="11">
+        <v>7</v>
+      </c>
+      <c r="D136" s="11">
+        <v>15</v>
+      </c>
+      <c r="E136" s="21">
+        <v>5</v>
+      </c>
+      <c r="F136" s="22">
+        <v>13</v>
+      </c>
+      <c r="G136" s="11">
+        <v>3</v>
+      </c>
+      <c r="H136" s="21">
+        <v>11</v>
+      </c>
+      <c r="I136" s="22">
+        <v>17</v>
+      </c>
+      <c r="J136" s="11">
+        <v>9</v>
+      </c>
+      <c r="K136" s="21">
+        <v>1</v>
+      </c>
+      <c r="L136" s="11"/>
+      <c r="M136" s="2"/>
+    </row>
+    <row r="137" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B137" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" s="24">
+        <v>6</v>
+      </c>
+      <c r="D137" s="25">
+        <v>5</v>
+      </c>
+      <c r="E137" s="26">
+        <v>6</v>
+      </c>
+      <c r="F137" s="24">
+        <v>6</v>
+      </c>
+      <c r="G137" s="25">
+        <v>6</v>
+      </c>
+      <c r="H137" s="26">
+        <v>6</v>
+      </c>
+      <c r="I137" s="24">
+        <v>4</v>
+      </c>
+      <c r="J137" s="25">
+        <v>6</v>
+      </c>
+      <c r="K137" s="26">
+        <v>6</v>
+      </c>
+      <c r="L137" s="11">
+        <v>51</v>
+      </c>
+      <c r="M137" s="27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B138" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C138" s="22">
+        <v>2</v>
+      </c>
+      <c r="D138" s="11">
+        <v>1</v>
+      </c>
+      <c r="E138" s="21">
+        <v>2</v>
+      </c>
+      <c r="F138" s="22">
+        <v>1</v>
+      </c>
+      <c r="G138" s="11">
+        <v>2</v>
+      </c>
+      <c r="H138" s="21">
+        <v>2</v>
+      </c>
+      <c r="I138" s="22">
+        <v>1</v>
+      </c>
+      <c r="J138" s="11">
+        <v>2</v>
+      </c>
+      <c r="K138" s="21">
+        <v>2</v>
+      </c>
+      <c r="L138" s="27"/>
+      <c r="M138" s="2"/>
+    </row>
+    <row r="139" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B139" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C139" s="22">
+        <v>4</v>
+      </c>
+      <c r="D139" s="11">
+        <v>4</v>
+      </c>
+      <c r="E139" s="21">
+        <v>4</v>
+      </c>
+      <c r="F139" s="22">
+        <v>5</v>
+      </c>
+      <c r="G139" s="11">
+        <v>4</v>
+      </c>
+      <c r="H139" s="21">
+        <v>4</v>
+      </c>
+      <c r="I139" s="22">
+        <v>3</v>
+      </c>
+      <c r="J139" s="11">
+        <v>4</v>
+      </c>
+      <c r="K139" s="21">
+        <v>4</v>
+      </c>
+      <c r="L139" s="28">
+        <v>36</v>
+      </c>
+      <c r="M139" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B140" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C140" s="30">
+        <v>1</v>
+      </c>
+      <c r="D140" s="31">
+        <v>0</v>
+      </c>
+      <c r="E140" s="32">
+        <v>1</v>
+      </c>
+      <c r="F140" s="30">
+        <v>1</v>
+      </c>
+      <c r="G140" s="31">
+        <v>1</v>
+      </c>
+      <c r="H140" s="32">
+        <v>1</v>
+      </c>
+      <c r="I140" s="30">
+        <v>1</v>
+      </c>
+      <c r="J140" s="31">
+        <v>1</v>
+      </c>
+      <c r="K140" s="32">
+        <v>1</v>
+      </c>
+      <c r="L140" s="11"/>
+      <c r="M140" s="2"/>
+    </row>
+    <row r="141" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B141" s="2"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
+      <c r="F141" s="11"/>
+      <c r="G141" s="11"/>
+      <c r="H141" s="11"/>
+      <c r="I141" s="11"/>
+      <c r="J141" s="11"/>
+      <c r="K141" s="11"/>
+      <c r="L141" s="11"/>
+      <c r="M141" s="2"/>
+    </row>
+    <row r="142" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B142" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="11">
+        <v>36</v>
+      </c>
+      <c r="E142" s="11"/>
+      <c r="F142" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G142" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H142" s="11"/>
+      <c r="I142" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J142" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K142" s="11"/>
+      <c r="L142" s="11"/>
+      <c r="M142" s="2"/>
+    </row>
+    <row r="143" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B143" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143" s="17">
+        <v>1</v>
+      </c>
+      <c r="D143" s="18">
+        <v>2</v>
+      </c>
+      <c r="E143" s="19">
+        <v>3</v>
+      </c>
+      <c r="F143" s="17">
+        <v>4</v>
+      </c>
+      <c r="G143" s="18">
+        <v>5</v>
+      </c>
+      <c r="H143" s="19">
+        <v>6</v>
+      </c>
+      <c r="I143" s="17">
+        <v>7</v>
+      </c>
+      <c r="J143" s="18">
+        <v>8</v>
+      </c>
+      <c r="K143" s="19">
+        <v>9</v>
+      </c>
+      <c r="L143" s="11"/>
+      <c r="M143" s="27"/>
+    </row>
+    <row r="144" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B144" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="11">
+        <v>4</v>
+      </c>
+      <c r="D144" s="11">
+        <v>3</v>
+      </c>
+      <c r="E144" s="21">
+        <v>4</v>
+      </c>
+      <c r="F144" s="22">
+        <v>5</v>
+      </c>
+      <c r="G144" s="11">
+        <v>4</v>
+      </c>
+      <c r="H144" s="21">
+        <v>4</v>
+      </c>
+      <c r="I144" s="22">
+        <v>3</v>
+      </c>
+      <c r="J144" s="11">
+        <v>5</v>
+      </c>
+      <c r="K144" s="21">
+        <v>4</v>
+      </c>
+      <c r="L144" s="11">
+        <v>36</v>
+      </c>
+      <c r="M144" s="2"/>
+    </row>
+    <row r="145" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B145" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="11">
+        <v>7</v>
+      </c>
+      <c r="D145" s="11">
+        <v>15</v>
+      </c>
+      <c r="E145" s="21">
+        <v>5</v>
+      </c>
+      <c r="F145" s="22">
+        <v>13</v>
+      </c>
+      <c r="G145" s="11">
+        <v>3</v>
+      </c>
+      <c r="H145" s="21">
+        <v>11</v>
+      </c>
+      <c r="I145" s="22">
+        <v>17</v>
+      </c>
+      <c r="J145" s="11">
+        <v>9</v>
+      </c>
+      <c r="K145" s="21">
+        <v>1</v>
+      </c>
+      <c r="L145" s="11"/>
+      <c r="M145" s="2"/>
+    </row>
+    <row r="146" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B146" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" s="24">
+        <v>8</v>
+      </c>
+      <c r="D146" s="25">
+        <v>6</v>
+      </c>
+      <c r="E146" s="26">
+        <v>8</v>
+      </c>
+      <c r="F146" s="24">
+        <v>10</v>
+      </c>
+      <c r="G146" s="25">
+        <v>8</v>
+      </c>
+      <c r="H146" s="26">
+        <v>8</v>
+      </c>
+      <c r="I146" s="24">
+        <v>6</v>
+      </c>
+      <c r="J146" s="25">
+        <v>10</v>
+      </c>
+      <c r="K146" s="26">
+        <v>8</v>
+      </c>
+      <c r="L146" s="11">
+        <v>72</v>
+      </c>
+      <c r="M146" s="27">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="147" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B147" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C147" s="22">
+        <v>2</v>
+      </c>
+      <c r="D147" s="11">
+        <v>2</v>
+      </c>
+      <c r="E147" s="21">
+        <v>2</v>
+      </c>
+      <c r="F147" s="22">
+        <v>2</v>
+      </c>
+      <c r="G147" s="11">
+        <v>2</v>
+      </c>
+      <c r="H147" s="21">
+        <v>2</v>
+      </c>
+      <c r="I147" s="22">
+        <v>2</v>
+      </c>
+      <c r="J147" s="11">
+        <v>2</v>
+      </c>
+      <c r="K147" s="21">
+        <v>2</v>
+      </c>
+      <c r="L147" s="27"/>
+      <c r="M147" s="2"/>
+    </row>
+    <row r="148" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B148" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C148" s="22">
+        <v>6</v>
+      </c>
+      <c r="D148" s="11">
+        <v>4</v>
+      </c>
+      <c r="E148" s="21">
+        <v>6</v>
+      </c>
+      <c r="F148" s="22">
+        <v>8</v>
+      </c>
+      <c r="G148" s="11">
+        <v>6</v>
+      </c>
+      <c r="H148" s="21">
+        <v>6</v>
+      </c>
+      <c r="I148" s="22">
+        <v>4</v>
+      </c>
+      <c r="J148" s="11">
+        <v>8</v>
+      </c>
+      <c r="K148" s="21">
+        <v>6</v>
+      </c>
+      <c r="L148" s="28">
+        <v>54</v>
+      </c>
+      <c r="M148" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B149" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C149" s="30">
+        <v>0</v>
+      </c>
+      <c r="D149" s="31">
+        <v>0</v>
+      </c>
+      <c r="E149" s="32">
+        <v>0</v>
+      </c>
+      <c r="F149" s="30">
+        <v>0</v>
+      </c>
+      <c r="G149" s="31">
+        <v>0</v>
+      </c>
+      <c r="H149" s="32">
+        <v>0</v>
+      </c>
+      <c r="I149" s="30">
+        <v>0</v>
+      </c>
+      <c r="J149" s="31">
+        <v>0</v>
+      </c>
+      <c r="K149" s="32">
+        <v>0</v>
+      </c>
+      <c r="L149" s="11"/>
+      <c r="M149" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="36">
+    <mergeCell ref="J127:K127"/>
+    <mergeCell ref="L127:M127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="J128:K130"/>
+    <mergeCell ref="L128:M130"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
     <mergeCell ref="J102:K102"/>
     <mergeCell ref="L102:M102"/>
     <mergeCell ref="B103:B104"/>
     <mergeCell ref="J103:K105"/>
     <mergeCell ref="L103:M105"/>
     <mergeCell ref="B105:B106"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:K40 C49:K49">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C40:K40 C49:K49">
+  <conditionalFormatting sqref="C65:K65 C74:K74">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C65:K65 C74:K74">
+  <conditionalFormatting sqref="C90:K90 C99:K99">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+  <conditionalFormatting sqref="C115:K115 C124:K124">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C115:K115 C124:K124">
+  <conditionalFormatting sqref="C140:K140 C149:K149">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -9685,18 +10429,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9705,7 +10449,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9714,18 +10458,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9734,7 +10478,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9743,18 +10487,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9763,7 +10507,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9772,7 +10516,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6BAA437-66F2-4DE3-A76A-AB323EB73F36}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71AC6EC3-EE10-45AB-95AD-04F94110E001}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -534,7 +534,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -5925,81 +5935,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="P28:P29"/>
+    <mergeCell ref="X28:Y30"/>
+    <mergeCell ref="Z28:AA30"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="J77:K77"/>
     <mergeCell ref="L77:M77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="J78:K80"/>
     <mergeCell ref="L78:M80"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="P28:P29"/>
-    <mergeCell ref="X28:Y30"/>
-    <mergeCell ref="Z28:AA30"/>
-    <mergeCell ref="P30:P31"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6009,7 +6019,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:M149"/>
+  <dimension ref="B1:M174"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -10353,71 +10363,805 @@
       <c r="L149" s="11"/>
       <c r="M149" s="2"/>
     </row>
+    <row r="151" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="152" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B152" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I152" s="4"/>
+      <c r="J152" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K152" s="34"/>
+      <c r="L152" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M152" s="34"/>
+    </row>
+    <row r="153" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B153" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" s="6">
+        <v>2</v>
+      </c>
+      <c r="E153" s="6">
+        <v>2</v>
+      </c>
+      <c r="F153" s="6">
+        <v>1</v>
+      </c>
+      <c r="G153" s="6">
+        <v>5</v>
+      </c>
+      <c r="H153" s="6">
+        <v>43</v>
+      </c>
+      <c r="I153" s="2"/>
+      <c r="J153" s="38">
+        <v>6</v>
+      </c>
+      <c r="K153" s="39"/>
+      <c r="L153" s="43">
+        <v>2</v>
+      </c>
+      <c r="M153" s="39"/>
+    </row>
+    <row r="154" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B154" s="37"/>
+      <c r="C154" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" s="8">
+        <v>2</v>
+      </c>
+      <c r="E154" s="8">
+        <v>2</v>
+      </c>
+      <c r="F154" s="8">
+        <v>0</v>
+      </c>
+      <c r="G154" s="8">
+        <v>1</v>
+      </c>
+      <c r="H154" s="8">
+        <v>1</v>
+      </c>
+      <c r="I154" s="2"/>
+      <c r="J154" s="40"/>
+      <c r="K154" s="41"/>
+      <c r="L154" s="44"/>
+      <c r="M154" s="41"/>
+    </row>
+    <row r="155" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B155" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D155" s="10">
+        <v>0</v>
+      </c>
+      <c r="E155" s="10">
+        <v>0</v>
+      </c>
+      <c r="F155" s="10">
+        <v>2</v>
+      </c>
+      <c r="G155" s="10">
+        <v>2</v>
+      </c>
+      <c r="H155" s="10">
+        <v>49</v>
+      </c>
+      <c r="I155" s="2"/>
+      <c r="J155" s="37"/>
+      <c r="K155" s="42"/>
+      <c r="L155" s="45"/>
+      <c r="M155" s="42"/>
+    </row>
+    <row r="156" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B156" s="37"/>
+      <c r="C156" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="8">
+        <v>0</v>
+      </c>
+      <c r="E156" s="8">
+        <v>0</v>
+      </c>
+      <c r="F156" s="8">
+        <v>2</v>
+      </c>
+      <c r="G156" s="8">
+        <v>0</v>
+      </c>
+      <c r="H156" s="8">
+        <v>0</v>
+      </c>
+      <c r="I156" s="2"/>
+      <c r="J156" s="11"/>
+      <c r="K156" s="11"/>
+      <c r="L156" s="11"/>
+      <c r="M156" s="11"/>
+    </row>
+    <row r="157" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B157" s="2"/>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="11"/>
+      <c r="G157" s="11"/>
+      <c r="H157" s="11"/>
+      <c r="I157" s="11"/>
+      <c r="J157" s="11"/>
+      <c r="K157" s="11"/>
+      <c r="L157" s="11"/>
+      <c r="M157" s="2"/>
+    </row>
+    <row r="158" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B158" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="11">
+        <v>22</v>
+      </c>
+      <c r="E158" s="11"/>
+      <c r="F158" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G158" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H158" s="11"/>
+      <c r="I158" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J158" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K158" s="11"/>
+      <c r="L158" s="11"/>
+      <c r="M158" s="2"/>
+    </row>
+    <row r="159" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B159" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C159" s="17">
+        <v>1</v>
+      </c>
+      <c r="D159" s="18">
+        <v>2</v>
+      </c>
+      <c r="E159" s="19">
+        <v>3</v>
+      </c>
+      <c r="F159" s="17">
+        <v>4</v>
+      </c>
+      <c r="G159" s="18">
+        <v>5</v>
+      </c>
+      <c r="H159" s="19">
+        <v>6</v>
+      </c>
+      <c r="I159" s="17">
+        <v>7</v>
+      </c>
+      <c r="J159" s="18">
+        <v>8</v>
+      </c>
+      <c r="K159" s="19">
+        <v>9</v>
+      </c>
+      <c r="L159" s="11"/>
+      <c r="M159" s="2"/>
+    </row>
+    <row r="160" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B160" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C160" s="11">
+        <v>4</v>
+      </c>
+      <c r="D160" s="11">
+        <v>5</v>
+      </c>
+      <c r="E160" s="21">
+        <v>4</v>
+      </c>
+      <c r="F160" s="22">
+        <v>4</v>
+      </c>
+      <c r="G160" s="11">
+        <v>3</v>
+      </c>
+      <c r="H160" s="21">
+        <v>4</v>
+      </c>
+      <c r="I160" s="22">
+        <v>3</v>
+      </c>
+      <c r="J160" s="11">
+        <v>4</v>
+      </c>
+      <c r="K160" s="21">
+        <v>5</v>
+      </c>
+      <c r="L160" s="11">
+        <v>36</v>
+      </c>
+      <c r="M160" s="2"/>
+    </row>
+    <row r="161" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B161" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" s="11">
+        <v>4</v>
+      </c>
+      <c r="D161" s="11">
+        <v>12</v>
+      </c>
+      <c r="E161" s="21">
+        <v>14</v>
+      </c>
+      <c r="F161" s="22">
+        <v>6</v>
+      </c>
+      <c r="G161" s="11">
+        <v>16</v>
+      </c>
+      <c r="H161" s="21">
+        <v>8</v>
+      </c>
+      <c r="I161" s="22">
+        <v>18</v>
+      </c>
+      <c r="J161" s="11">
+        <v>2</v>
+      </c>
+      <c r="K161" s="21">
+        <v>10</v>
+      </c>
+      <c r="L161" s="11"/>
+      <c r="M161" s="2"/>
+    </row>
+    <row r="162" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B162" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" s="24">
+        <v>6</v>
+      </c>
+      <c r="D162" s="25">
+        <v>9</v>
+      </c>
+      <c r="E162" s="26">
+        <v>5</v>
+      </c>
+      <c r="F162" s="24">
+        <v>5</v>
+      </c>
+      <c r="G162" s="25">
+        <v>5</v>
+      </c>
+      <c r="H162" s="26">
+        <v>4</v>
+      </c>
+      <c r="I162" s="24">
+        <v>4</v>
+      </c>
+      <c r="J162" s="25">
+        <v>8</v>
+      </c>
+      <c r="K162" s="26">
+        <v>8</v>
+      </c>
+      <c r="L162" s="11">
+        <v>54</v>
+      </c>
+      <c r="M162" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="163" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B163" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C163" s="22">
+        <v>2</v>
+      </c>
+      <c r="D163" s="11">
+        <v>1</v>
+      </c>
+      <c r="E163" s="21">
+        <v>1</v>
+      </c>
+      <c r="F163" s="22">
+        <v>1</v>
+      </c>
+      <c r="G163" s="11">
+        <v>1</v>
+      </c>
+      <c r="H163" s="21">
+        <v>1</v>
+      </c>
+      <c r="I163" s="22">
+        <v>1</v>
+      </c>
+      <c r="J163" s="11">
+        <v>2</v>
+      </c>
+      <c r="K163" s="21">
+        <v>1</v>
+      </c>
+      <c r="L163" s="27"/>
+      <c r="M163" s="2"/>
+    </row>
+    <row r="164" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B164" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164" s="22">
+        <v>4</v>
+      </c>
+      <c r="D164" s="11">
+        <v>8</v>
+      </c>
+      <c r="E164" s="21">
+        <v>4</v>
+      </c>
+      <c r="F164" s="22">
+        <v>4</v>
+      </c>
+      <c r="G164" s="11">
+        <v>4</v>
+      </c>
+      <c r="H164" s="21">
+        <v>3</v>
+      </c>
+      <c r="I164" s="22">
+        <v>3</v>
+      </c>
+      <c r="J164" s="11">
+        <v>6</v>
+      </c>
+      <c r="K164" s="21">
+        <v>7</v>
+      </c>
+      <c r="L164" s="28">
+        <v>43</v>
+      </c>
+      <c r="M164" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B165" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C165" s="30">
+        <v>1</v>
+      </c>
+      <c r="D165" s="31">
+        <v>0</v>
+      </c>
+      <c r="E165" s="32">
+        <v>1</v>
+      </c>
+      <c r="F165" s="30">
+        <v>1</v>
+      </c>
+      <c r="G165" s="31">
+        <v>0</v>
+      </c>
+      <c r="H165" s="32">
+        <v>1</v>
+      </c>
+      <c r="I165" s="30">
+        <v>1</v>
+      </c>
+      <c r="J165" s="31">
+        <v>0</v>
+      </c>
+      <c r="K165" s="32">
+        <v>0</v>
+      </c>
+      <c r="L165" s="11"/>
+      <c r="M165" s="2"/>
+    </row>
+    <row r="166" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B166" s="2"/>
+      <c r="C166" s="11"/>
+      <c r="D166" s="11"/>
+      <c r="E166" s="11"/>
+      <c r="F166" s="11"/>
+      <c r="G166" s="11"/>
+      <c r="H166" s="11"/>
+      <c r="I166" s="11"/>
+      <c r="J166" s="11"/>
+      <c r="K166" s="11"/>
+      <c r="L166" s="11"/>
+      <c r="M166" s="2"/>
+    </row>
+    <row r="167" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B167" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C167" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="11">
+        <v>27</v>
+      </c>
+      <c r="E167" s="11"/>
+      <c r="F167" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H167" s="11"/>
+      <c r="I167" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J167" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="K167" s="11"/>
+      <c r="L167" s="11"/>
+      <c r="M167" s="2"/>
+    </row>
+    <row r="168" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B168" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="17">
+        <v>1</v>
+      </c>
+      <c r="D168" s="18">
+        <v>2</v>
+      </c>
+      <c r="E168" s="19">
+        <v>3</v>
+      </c>
+      <c r="F168" s="17">
+        <v>4</v>
+      </c>
+      <c r="G168" s="18">
+        <v>5</v>
+      </c>
+      <c r="H168" s="19">
+        <v>6</v>
+      </c>
+      <c r="I168" s="17">
+        <v>7</v>
+      </c>
+      <c r="J168" s="18">
+        <v>8</v>
+      </c>
+      <c r="K168" s="19">
+        <v>9</v>
+      </c>
+      <c r="L168" s="11"/>
+      <c r="M168" s="27"/>
+    </row>
+    <row r="169" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B169" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169" s="11">
+        <v>4</v>
+      </c>
+      <c r="D169" s="11">
+        <v>5</v>
+      </c>
+      <c r="E169" s="21">
+        <v>4</v>
+      </c>
+      <c r="F169" s="22">
+        <v>4</v>
+      </c>
+      <c r="G169" s="11">
+        <v>3</v>
+      </c>
+      <c r="H169" s="21">
+        <v>4</v>
+      </c>
+      <c r="I169" s="22">
+        <v>3</v>
+      </c>
+      <c r="J169" s="11">
+        <v>4</v>
+      </c>
+      <c r="K169" s="21">
+        <v>5</v>
+      </c>
+      <c r="L169" s="11">
+        <v>36</v>
+      </c>
+      <c r="M169" s="2"/>
+    </row>
+    <row r="170" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B170" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" s="11">
+        <v>4</v>
+      </c>
+      <c r="D170" s="11">
+        <v>12</v>
+      </c>
+      <c r="E170" s="21">
+        <v>14</v>
+      </c>
+      <c r="F170" s="22">
+        <v>6</v>
+      </c>
+      <c r="G170" s="11">
+        <v>16</v>
+      </c>
+      <c r="H170" s="21">
+        <v>8</v>
+      </c>
+      <c r="I170" s="22">
+        <v>18</v>
+      </c>
+      <c r="J170" s="11">
+        <v>2</v>
+      </c>
+      <c r="K170" s="21">
+        <v>10</v>
+      </c>
+      <c r="L170" s="11"/>
+      <c r="M170" s="2"/>
+    </row>
+    <row r="171" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B171" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C171" s="24">
+        <v>8</v>
+      </c>
+      <c r="D171" s="25">
+        <v>9</v>
+      </c>
+      <c r="E171" s="26">
+        <v>8</v>
+      </c>
+      <c r="F171" s="24">
+        <v>7</v>
+      </c>
+      <c r="G171" s="25">
+        <v>5</v>
+      </c>
+      <c r="H171" s="26">
+        <v>7</v>
+      </c>
+      <c r="I171" s="24">
+        <v>5</v>
+      </c>
+      <c r="J171" s="25">
+        <v>7</v>
+      </c>
+      <c r="K171" s="26">
+        <v>6</v>
+      </c>
+      <c r="L171" s="11">
+        <v>62</v>
+      </c>
+      <c r="M171" s="27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="172" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B172" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C172" s="22">
+        <v>2</v>
+      </c>
+      <c r="D172" s="11">
+        <v>1</v>
+      </c>
+      <c r="E172" s="21">
+        <v>1</v>
+      </c>
+      <c r="F172" s="22">
+        <v>2</v>
+      </c>
+      <c r="G172" s="11">
+        <v>1</v>
+      </c>
+      <c r="H172" s="21">
+        <v>2</v>
+      </c>
+      <c r="I172" s="22">
+        <v>1</v>
+      </c>
+      <c r="J172" s="11">
+        <v>2</v>
+      </c>
+      <c r="K172" s="21">
+        <v>1</v>
+      </c>
+      <c r="L172" s="27"/>
+      <c r="M172" s="2"/>
+    </row>
+    <row r="173" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B173" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C173" s="22">
+        <v>6</v>
+      </c>
+      <c r="D173" s="11">
+        <v>8</v>
+      </c>
+      <c r="E173" s="21">
+        <v>7</v>
+      </c>
+      <c r="F173" s="22">
+        <v>5</v>
+      </c>
+      <c r="G173" s="11">
+        <v>4</v>
+      </c>
+      <c r="H173" s="21">
+        <v>5</v>
+      </c>
+      <c r="I173" s="22">
+        <v>4</v>
+      </c>
+      <c r="J173" s="11">
+        <v>5</v>
+      </c>
+      <c r="K173" s="21">
+        <v>5</v>
+      </c>
+      <c r="L173" s="28">
+        <v>49</v>
+      </c>
+      <c r="M173" s="27">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B174" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C174" s="30">
+        <v>0</v>
+      </c>
+      <c r="D174" s="31">
+        <v>0</v>
+      </c>
+      <c r="E174" s="32">
+        <v>0</v>
+      </c>
+      <c r="F174" s="30">
+        <v>0</v>
+      </c>
+      <c r="G174" s="31">
+        <v>0</v>
+      </c>
+      <c r="H174" s="32">
+        <v>0</v>
+      </c>
+      <c r="I174" s="30">
+        <v>0</v>
+      </c>
+      <c r="J174" s="31">
+        <v>1</v>
+      </c>
+      <c r="K174" s="32">
+        <v>1</v>
+      </c>
+      <c r="L174" s="11"/>
+      <c r="M174" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="42">
+    <mergeCell ref="J152:K152"/>
+    <mergeCell ref="L152:M152"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="J153:K155"/>
+    <mergeCell ref="L153:M155"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
     <mergeCell ref="J127:K127"/>
     <mergeCell ref="L127:M127"/>
     <mergeCell ref="B128:B129"/>
     <mergeCell ref="J128:K130"/>
     <mergeCell ref="L128:M130"/>
     <mergeCell ref="B130:B131"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="J103:K105"/>
-    <mergeCell ref="L103:M105"/>
-    <mergeCell ref="B105:B106"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:K40 C49:K49">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C40:K40 C49:K49">
+  <conditionalFormatting sqref="C65:K65 C74:K74">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C65:K65 C74:K74">
+  <conditionalFormatting sqref="C90:K90 C99:K99">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="C115:K115 C124:K124">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C115:K115 C124:K124">
+  <conditionalFormatting sqref="C140:K140 C149:K149">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C140:K140 C149:K149">
+  <conditionalFormatting sqref="C165:K165 C174:K174">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71AC6EC3-EE10-45AB-95AD-04F94110E001}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BC003A-49E2-4A46-8A30-822257BD3F90}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -534,7 +534,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -5935,81 +5955,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="X27:Y27"/>
     <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="P28:P29"/>
     <mergeCell ref="X28:Y30"/>
     <mergeCell ref="Z28:AA30"/>
     <mergeCell ref="P30:P31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="12" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11088,81 +11108,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J127:K127"/>
+    <mergeCell ref="L127:M127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="J128:K130"/>
+    <mergeCell ref="L128:M130"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
     <mergeCell ref="J152:K152"/>
     <mergeCell ref="L152:M152"/>
     <mergeCell ref="B153:B154"/>
     <mergeCell ref="J153:K155"/>
     <mergeCell ref="L153:M155"/>
     <mergeCell ref="B155:B156"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="J103:K105"/>
-    <mergeCell ref="L103:M105"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J127:K127"/>
-    <mergeCell ref="L127:M127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="J128:K130"/>
-    <mergeCell ref="L128:M130"/>
-    <mergeCell ref="B130:B131"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115:K115 C124:K124">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C140:K140 C149:K149">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C165:K165 C174:K174">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11172,20 +11192,1484 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A24"/>
+  <dimension ref="B1:M50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="34"/>
+      <c r="L3" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="34"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6">
+        <v>2</v>
+      </c>
+      <c r="G4" s="6">
+        <v>7</v>
+      </c>
+      <c r="H4" s="6">
+        <v>37</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="38">
+        <v>8</v>
+      </c>
+      <c r="K4" s="39"/>
+      <c r="L4" s="43">
+        <v>0</v>
+      </c>
+      <c r="M4" s="39"/>
+    </row>
+    <row r="5" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="37"/>
+      <c r="C5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="8">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8">
+        <v>2</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="41"/>
+    </row>
+    <row r="6" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10">
+        <v>54</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="42"/>
+    </row>
+    <row r="7" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="37"/>
+      <c r="C7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="11">
+        <v>28</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18">
+        <v>2</v>
+      </c>
+      <c r="E10" s="19">
+        <v>3</v>
+      </c>
+      <c r="F10" s="17">
+        <v>4</v>
+      </c>
+      <c r="G10" s="18">
+        <v>5</v>
+      </c>
+      <c r="H10" s="19">
+        <v>6</v>
+      </c>
+      <c r="I10" s="17">
+        <v>7</v>
+      </c>
+      <c r="J10" s="18">
+        <v>8</v>
+      </c>
+      <c r="K10" s="19">
+        <v>9</v>
+      </c>
+      <c r="L10" s="11"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="11">
+        <v>4</v>
+      </c>
+      <c r="D11" s="11">
+        <v>5</v>
+      </c>
+      <c r="E11" s="21">
+        <v>3</v>
+      </c>
+      <c r="F11" s="22">
+        <v>4</v>
+      </c>
+      <c r="G11" s="11">
+        <v>4</v>
+      </c>
+      <c r="H11" s="21">
+        <v>3</v>
+      </c>
+      <c r="I11" s="22">
+        <v>5</v>
+      </c>
+      <c r="J11" s="11">
+        <v>4</v>
+      </c>
+      <c r="K11" s="21">
+        <v>4</v>
+      </c>
+      <c r="L11" s="11">
+        <v>36</v>
+      </c>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="11">
+        <v>7</v>
+      </c>
+      <c r="D12" s="11">
+        <v>17</v>
+      </c>
+      <c r="E12" s="21">
+        <v>15</v>
+      </c>
+      <c r="F12" s="22">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11">
+        <v>11</v>
+      </c>
+      <c r="H12" s="21">
+        <v>9</v>
+      </c>
+      <c r="I12" s="22">
+        <v>13</v>
+      </c>
+      <c r="J12" s="11">
+        <v>5</v>
+      </c>
+      <c r="K12" s="21">
+        <v>3</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="24">
+        <v>5</v>
+      </c>
+      <c r="D13" s="25">
+        <v>5</v>
+      </c>
+      <c r="E13" s="26">
+        <v>6</v>
+      </c>
+      <c r="F13" s="24">
+        <v>7</v>
+      </c>
+      <c r="G13" s="25">
+        <v>5</v>
+      </c>
+      <c r="H13" s="26">
+        <v>4</v>
+      </c>
+      <c r="I13" s="24">
+        <v>5</v>
+      </c>
+      <c r="J13" s="25">
+        <v>8</v>
+      </c>
+      <c r="K13" s="26">
+        <v>6</v>
+      </c>
+      <c r="L13" s="11">
+        <v>51</v>
+      </c>
+      <c r="M13" s="27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="22">
+        <v>2</v>
+      </c>
+      <c r="D14" s="11">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21">
+        <v>1</v>
+      </c>
+      <c r="F14" s="22">
+        <v>2</v>
+      </c>
+      <c r="G14" s="11">
+        <v>1</v>
+      </c>
+      <c r="H14" s="21">
+        <v>2</v>
+      </c>
+      <c r="I14" s="22">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11">
+        <v>2</v>
+      </c>
+      <c r="K14" s="21">
+        <v>2</v>
+      </c>
+      <c r="L14" s="27"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="22">
+        <v>3</v>
+      </c>
+      <c r="D15" s="11">
+        <v>4</v>
+      </c>
+      <c r="E15" s="21">
+        <v>5</v>
+      </c>
+      <c r="F15" s="22">
+        <v>5</v>
+      </c>
+      <c r="G15" s="11">
+        <v>4</v>
+      </c>
+      <c r="H15" s="21">
+        <v>2</v>
+      </c>
+      <c r="I15" s="22">
+        <v>4</v>
+      </c>
+      <c r="J15" s="11">
+        <v>6</v>
+      </c>
+      <c r="K15" s="21">
+        <v>4</v>
+      </c>
+      <c r="L15" s="28">
+        <v>37</v>
+      </c>
+      <c r="M15" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="30">
+        <v>1</v>
+      </c>
+      <c r="D16" s="31">
+        <v>1</v>
+      </c>
+      <c r="E16" s="32">
+        <v>0</v>
+      </c>
+      <c r="F16" s="30">
+        <v>1</v>
+      </c>
+      <c r="G16" s="31">
+        <v>1</v>
+      </c>
+      <c r="H16" s="32">
+        <v>1</v>
+      </c>
+      <c r="I16" s="30">
+        <v>1</v>
+      </c>
+      <c r="J16" s="31">
+        <v>0</v>
+      </c>
+      <c r="K16" s="32">
+        <v>1</v>
+      </c>
+      <c r="L16" s="11"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="11">
+        <v>36</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="17">
+        <v>1</v>
+      </c>
+      <c r="D19" s="18">
+        <v>2</v>
+      </c>
+      <c r="E19" s="19">
+        <v>3</v>
+      </c>
+      <c r="F19" s="17">
+        <v>4</v>
+      </c>
+      <c r="G19" s="18">
+        <v>5</v>
+      </c>
+      <c r="H19" s="19">
+        <v>6</v>
+      </c>
+      <c r="I19" s="17">
+        <v>7</v>
+      </c>
+      <c r="J19" s="18">
+        <v>8</v>
+      </c>
+      <c r="K19" s="19">
+        <v>9</v>
+      </c>
+      <c r="L19" s="11"/>
+      <c r="M19" s="27"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="11">
+        <v>4</v>
+      </c>
+      <c r="D20" s="11">
+        <v>5</v>
+      </c>
+      <c r="E20" s="21">
+        <v>3</v>
+      </c>
+      <c r="F20" s="22">
+        <v>4</v>
+      </c>
+      <c r="G20" s="11">
+        <v>4</v>
+      </c>
+      <c r="H20" s="21">
+        <v>3</v>
+      </c>
+      <c r="I20" s="22">
+        <v>5</v>
+      </c>
+      <c r="J20" s="11">
+        <v>4</v>
+      </c>
+      <c r="K20" s="21">
+        <v>4</v>
+      </c>
+      <c r="L20" s="11">
+        <v>36</v>
+      </c>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="11">
+        <v>7</v>
+      </c>
+      <c r="D21" s="11">
+        <v>17</v>
+      </c>
+      <c r="E21" s="21">
+        <v>15</v>
+      </c>
+      <c r="F21" s="22">
+        <v>1</v>
+      </c>
+      <c r="G21" s="11">
+        <v>11</v>
+      </c>
+      <c r="H21" s="21">
+        <v>9</v>
+      </c>
+      <c r="I21" s="22">
+        <v>13</v>
+      </c>
+      <c r="J21" s="11">
+        <v>5</v>
+      </c>
+      <c r="K21" s="21">
+        <v>3</v>
+      </c>
+      <c r="L21" s="11"/>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="24">
+        <v>8</v>
+      </c>
+      <c r="D22" s="25">
+        <v>10</v>
+      </c>
+      <c r="E22" s="26">
+        <v>6</v>
+      </c>
+      <c r="F22" s="24">
+        <v>8</v>
+      </c>
+      <c r="G22" s="25">
+        <v>8</v>
+      </c>
+      <c r="H22" s="26">
+        <v>6</v>
+      </c>
+      <c r="I22" s="24">
+        <v>10</v>
+      </c>
+      <c r="J22" s="25">
+        <v>8</v>
+      </c>
+      <c r="K22" s="26">
+        <v>8</v>
+      </c>
+      <c r="L22" s="11">
+        <v>72</v>
+      </c>
+      <c r="M22" s="27">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="22">
+        <v>2</v>
+      </c>
+      <c r="D23" s="11">
+        <v>2</v>
+      </c>
+      <c r="E23" s="21">
+        <v>2</v>
+      </c>
+      <c r="F23" s="22">
+        <v>2</v>
+      </c>
+      <c r="G23" s="11">
+        <v>2</v>
+      </c>
+      <c r="H23" s="21">
+        <v>2</v>
+      </c>
+      <c r="I23" s="22">
+        <v>2</v>
+      </c>
+      <c r="J23" s="11">
+        <v>2</v>
+      </c>
+      <c r="K23" s="21">
+        <v>2</v>
+      </c>
+      <c r="L23" s="27"/>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="22">
+        <v>6</v>
+      </c>
+      <c r="D24" s="11">
+        <v>8</v>
+      </c>
+      <c r="E24" s="21">
+        <v>4</v>
+      </c>
+      <c r="F24" s="22">
+        <v>6</v>
+      </c>
+      <c r="G24" s="11">
+        <v>6</v>
+      </c>
+      <c r="H24" s="21">
+        <v>4</v>
+      </c>
+      <c r="I24" s="22">
+        <v>8</v>
+      </c>
+      <c r="J24" s="11">
+        <v>6</v>
+      </c>
+      <c r="K24" s="21">
+        <v>6</v>
+      </c>
+      <c r="L24" s="28">
+        <v>54</v>
+      </c>
+      <c r="M24" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="30">
+        <v>0</v>
+      </c>
+      <c r="D25" s="31">
+        <v>0</v>
+      </c>
+      <c r="E25" s="32">
+        <v>1</v>
+      </c>
+      <c r="F25" s="30">
+        <v>0</v>
+      </c>
+      <c r="G25" s="31">
+        <v>0</v>
+      </c>
+      <c r="H25" s="32">
+        <v>0</v>
+      </c>
+      <c r="I25" s="30">
+        <v>0</v>
+      </c>
+      <c r="J25" s="31">
+        <v>0</v>
+      </c>
+      <c r="K25" s="32">
+        <v>0</v>
+      </c>
+      <c r="L25" s="11"/>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="27" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="34"/>
+      <c r="L28" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="34"/>
+    </row>
+    <row r="29" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="6">
+        <v>2</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6">
+        <v>2</v>
+      </c>
+      <c r="G29" s="6">
+        <v>5</v>
+      </c>
+      <c r="H29" s="6">
+        <v>39</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="38">
+        <v>7</v>
+      </c>
+      <c r="K29" s="39"/>
+      <c r="L29" s="43">
+        <v>1</v>
+      </c>
+      <c r="M29" s="39"/>
+    </row>
+    <row r="30" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="37"/>
+      <c r="C30" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="8">
+        <v>2</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8">
+        <v>2</v>
+      </c>
+      <c r="G30" s="8">
+        <v>1</v>
+      </c>
+      <c r="H30" s="8">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="41"/>
+    </row>
+    <row r="31" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="10">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10">
+        <v>0</v>
+      </c>
+      <c r="G31" s="10">
+        <v>1</v>
+      </c>
+      <c r="H31" s="10">
+        <v>54</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="42"/>
+    </row>
+    <row r="32" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="37"/>
+      <c r="C32" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="8">
+        <v>0</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1</v>
+      </c>
+      <c r="F32" s="8">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B33" s="2"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="11">
+        <v>27</v>
+      </c>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="17">
+        <v>1</v>
+      </c>
+      <c r="D35" s="18">
+        <v>2</v>
+      </c>
+      <c r="E35" s="19">
+        <v>3</v>
+      </c>
+      <c r="F35" s="17">
+        <v>4</v>
+      </c>
+      <c r="G35" s="18">
+        <v>5</v>
+      </c>
+      <c r="H35" s="19">
+        <v>6</v>
+      </c>
+      <c r="I35" s="17">
+        <v>7</v>
+      </c>
+      <c r="J35" s="18">
+        <v>8</v>
+      </c>
+      <c r="K35" s="19">
+        <v>9</v>
+      </c>
+      <c r="L35" s="11"/>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B36" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="11">
+        <v>4</v>
+      </c>
+      <c r="D36" s="11">
+        <v>5</v>
+      </c>
+      <c r="E36" s="21">
+        <v>3</v>
+      </c>
+      <c r="F36" s="22">
+        <v>4</v>
+      </c>
+      <c r="G36" s="11">
+        <v>4</v>
+      </c>
+      <c r="H36" s="21">
+        <v>3</v>
+      </c>
+      <c r="I36" s="22">
+        <v>5</v>
+      </c>
+      <c r="J36" s="11">
+        <v>4</v>
+      </c>
+      <c r="K36" s="21">
+        <v>4</v>
+      </c>
+      <c r="L36" s="11">
+        <v>36</v>
+      </c>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B37" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="11">
+        <v>7</v>
+      </c>
+      <c r="D37" s="11">
+        <v>17</v>
+      </c>
+      <c r="E37" s="21">
+        <v>15</v>
+      </c>
+      <c r="F37" s="22">
+        <v>1</v>
+      </c>
+      <c r="G37" s="11">
+        <v>11</v>
+      </c>
+      <c r="H37" s="21">
+        <v>9</v>
+      </c>
+      <c r="I37" s="22">
+        <v>13</v>
+      </c>
+      <c r="J37" s="11">
+        <v>5</v>
+      </c>
+      <c r="K37" s="21">
+        <v>3</v>
+      </c>
+      <c r="L37" s="11"/>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="24">
+        <v>4</v>
+      </c>
+      <c r="D38" s="25">
+        <v>7</v>
+      </c>
+      <c r="E38" s="26">
+        <v>5</v>
+      </c>
+      <c r="F38" s="24">
+        <v>4</v>
+      </c>
+      <c r="G38" s="25">
+        <v>8</v>
+      </c>
+      <c r="H38" s="26">
+        <v>6</v>
+      </c>
+      <c r="I38" s="24">
+        <v>7</v>
+      </c>
+      <c r="J38" s="25">
+        <v>4</v>
+      </c>
+      <c r="K38" s="26">
+        <v>8</v>
+      </c>
+      <c r="L38" s="11">
+        <v>53</v>
+      </c>
+      <c r="M38" s="27">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="22">
+        <v>2</v>
+      </c>
+      <c r="D39" s="11">
+        <v>1</v>
+      </c>
+      <c r="E39" s="21">
+        <v>1</v>
+      </c>
+      <c r="F39" s="22">
+        <v>2</v>
+      </c>
+      <c r="G39" s="11">
+        <v>1</v>
+      </c>
+      <c r="H39" s="21">
+        <v>2</v>
+      </c>
+      <c r="I39" s="22">
+        <v>1</v>
+      </c>
+      <c r="J39" s="11">
+        <v>2</v>
+      </c>
+      <c r="K39" s="21">
+        <v>2</v>
+      </c>
+      <c r="L39" s="27"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B40" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="22">
+        <v>2</v>
+      </c>
+      <c r="D40" s="11">
+        <v>6</v>
+      </c>
+      <c r="E40" s="21">
+        <v>4</v>
+      </c>
+      <c r="F40" s="22">
+        <v>2</v>
+      </c>
+      <c r="G40" s="11">
+        <v>7</v>
+      </c>
+      <c r="H40" s="21">
+        <v>4</v>
+      </c>
+      <c r="I40" s="22">
+        <v>6</v>
+      </c>
+      <c r="J40" s="11">
+        <v>2</v>
+      </c>
+      <c r="K40" s="21">
+        <v>6</v>
+      </c>
+      <c r="L40" s="28">
+        <v>39</v>
+      </c>
+      <c r="M40" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="30">
+        <v>1</v>
+      </c>
+      <c r="D41" s="31">
+        <v>1</v>
+      </c>
+      <c r="E41" s="32">
+        <v>0</v>
+      </c>
+      <c r="F41" s="30">
+        <v>1</v>
+      </c>
+      <c r="G41" s="31">
+        <v>0</v>
+      </c>
+      <c r="H41" s="32">
+        <v>0</v>
+      </c>
+      <c r="I41" s="30">
+        <v>1</v>
+      </c>
+      <c r="J41" s="31">
+        <v>1</v>
+      </c>
+      <c r="K41" s="32">
+        <v>0</v>
+      </c>
+      <c r="L41" s="11"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B42" s="2"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="11">
+        <v>36</v>
+      </c>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B44" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="17">
+        <v>1</v>
+      </c>
+      <c r="D44" s="18">
+        <v>2</v>
+      </c>
+      <c r="E44" s="19">
+        <v>3</v>
+      </c>
+      <c r="F44" s="17">
+        <v>4</v>
+      </c>
+      <c r="G44" s="18">
+        <v>5</v>
+      </c>
+      <c r="H44" s="19">
+        <v>6</v>
+      </c>
+      <c r="I44" s="17">
+        <v>7</v>
+      </c>
+      <c r="J44" s="18">
+        <v>8</v>
+      </c>
+      <c r="K44" s="19">
+        <v>9</v>
+      </c>
+      <c r="L44" s="11"/>
+      <c r="M44" s="27"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B45" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="11">
+        <v>4</v>
+      </c>
+      <c r="D45" s="11">
+        <v>5</v>
+      </c>
+      <c r="E45" s="21">
+        <v>3</v>
+      </c>
+      <c r="F45" s="22">
+        <v>4</v>
+      </c>
+      <c r="G45" s="11">
+        <v>4</v>
+      </c>
+      <c r="H45" s="21">
+        <v>3</v>
+      </c>
+      <c r="I45" s="22">
+        <v>5</v>
+      </c>
+      <c r="J45" s="11">
+        <v>4</v>
+      </c>
+      <c r="K45" s="21">
+        <v>4</v>
+      </c>
+      <c r="L45" s="11">
+        <v>36</v>
+      </c>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B46" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="11">
+        <v>7</v>
+      </c>
+      <c r="D46" s="11">
+        <v>17</v>
+      </c>
+      <c r="E46" s="21">
+        <v>15</v>
+      </c>
+      <c r="F46" s="22">
+        <v>1</v>
+      </c>
+      <c r="G46" s="11">
+        <v>11</v>
+      </c>
+      <c r="H46" s="21">
+        <v>9</v>
+      </c>
+      <c r="I46" s="22">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11">
+        <v>5</v>
+      </c>
+      <c r="K46" s="21">
+        <v>3</v>
+      </c>
+      <c r="L46" s="11"/>
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B47" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="24">
+        <v>8</v>
+      </c>
+      <c r="D47" s="25">
+        <v>10</v>
+      </c>
+      <c r="E47" s="26">
+        <v>6</v>
+      </c>
+      <c r="F47" s="24">
+        <v>8</v>
+      </c>
+      <c r="G47" s="25">
+        <v>8</v>
+      </c>
+      <c r="H47" s="26">
+        <v>6</v>
+      </c>
+      <c r="I47" s="24">
+        <v>10</v>
+      </c>
+      <c r="J47" s="25">
+        <v>8</v>
+      </c>
+      <c r="K47" s="26">
+        <v>8</v>
+      </c>
+      <c r="L47" s="11">
+        <v>72</v>
+      </c>
+      <c r="M47" s="27">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B48" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="22">
+        <v>2</v>
+      </c>
+      <c r="D48" s="11">
+        <v>2</v>
+      </c>
+      <c r="E48" s="21">
+        <v>2</v>
+      </c>
+      <c r="F48" s="22">
+        <v>2</v>
+      </c>
+      <c r="G48" s="11">
+        <v>2</v>
+      </c>
+      <c r="H48" s="21">
+        <v>2</v>
+      </c>
+      <c r="I48" s="22">
+        <v>2</v>
+      </c>
+      <c r="J48" s="11">
+        <v>2</v>
+      </c>
+      <c r="K48" s="21">
+        <v>2</v>
+      </c>
+      <c r="L48" s="27"/>
+      <c r="M48" s="2"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B49" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="22">
+        <v>6</v>
+      </c>
+      <c r="D49" s="11">
+        <v>8</v>
+      </c>
+      <c r="E49" s="21">
+        <v>4</v>
+      </c>
+      <c r="F49" s="22">
+        <v>6</v>
+      </c>
+      <c r="G49" s="11">
+        <v>6</v>
+      </c>
+      <c r="H49" s="21">
+        <v>4</v>
+      </c>
+      <c r="I49" s="22">
+        <v>8</v>
+      </c>
+      <c r="J49" s="11">
+        <v>6</v>
+      </c>
+      <c r="K49" s="21">
+        <v>6</v>
+      </c>
+      <c r="L49" s="28">
+        <v>54</v>
+      </c>
+      <c r="M49" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="30">
+        <v>0</v>
+      </c>
+      <c r="D50" s="31">
+        <v>0</v>
+      </c>
+      <c r="E50" s="32">
+        <v>0</v>
+      </c>
+      <c r="F50" s="30">
+        <v>0</v>
+      </c>
+      <c r="G50" s="31">
+        <v>1</v>
+      </c>
+      <c r="H50" s="32">
+        <v>0</v>
+      </c>
+      <c r="I50" s="30">
+        <v>0</v>
+      </c>
+      <c r="J50" s="31">
+        <v>0</v>
+      </c>
+      <c r="K50" s="32">
+        <v>0</v>
+      </c>
+      <c r="L50" s="11"/>
+      <c r="M50" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="J29:K31"/>
+    <mergeCell ref="L29:M31"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J4:K6"/>
+    <mergeCell ref="L4:M6"/>
+    <mergeCell ref="B6:B7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:K16 C25:K25">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41:K41 C50:K50">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BC003A-49E2-4A46-8A30-822257BD3F90}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583A2400-7B08-414E-B87F-185488502672}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27840" yWindow="-855" windowWidth="23010" windowHeight="13680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -534,7 +534,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -5955,81 +5965,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="P28:P29"/>
+    <mergeCell ref="X28:Y30"/>
+    <mergeCell ref="Z28:AA30"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="J77:K77"/>
     <mergeCell ref="L77:M77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="J78:K80"/>
     <mergeCell ref="L78:M80"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="P28:P29"/>
-    <mergeCell ref="X28:Y30"/>
-    <mergeCell ref="Z28:AA30"/>
-    <mergeCell ref="P30:P31"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="15" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11108,81 +11118,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J152:K152"/>
+    <mergeCell ref="L152:M152"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="J153:K155"/>
+    <mergeCell ref="L153:M155"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
     <mergeCell ref="J127:K127"/>
     <mergeCell ref="L127:M127"/>
     <mergeCell ref="B128:B129"/>
     <mergeCell ref="J128:K130"/>
     <mergeCell ref="L128:M130"/>
     <mergeCell ref="B130:B131"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="J103:K105"/>
-    <mergeCell ref="L103:M105"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="J152:K152"/>
-    <mergeCell ref="L152:M152"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="J153:K155"/>
-    <mergeCell ref="L153:M155"/>
-    <mergeCell ref="B155:B156"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115:K115 C124:K124">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C140:K140 C149:K149">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C165:K165 C174:K174">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11192,7 +11202,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:M50"/>
+  <dimension ref="B1:M75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -12645,27 +12655,761 @@
       <c r="L50" s="11"/>
       <c r="M50" s="2"/>
     </row>
+    <row r="52" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53" s="34"/>
+      <c r="L53" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="M53" s="34"/>
+    </row>
+    <row r="54" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6">
+        <v>2</v>
+      </c>
+      <c r="F54" s="6">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6">
+        <v>3</v>
+      </c>
+      <c r="H54" s="6">
+        <v>42</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="38">
+        <v>4.5</v>
+      </c>
+      <c r="K54" s="39"/>
+      <c r="L54" s="43">
+        <v>3.5</v>
+      </c>
+      <c r="M54" s="39"/>
+    </row>
+    <row r="55" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="37"/>
+      <c r="C55" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="8">
+        <v>1</v>
+      </c>
+      <c r="E55" s="8">
+        <v>2</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H55" s="8">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="41"/>
+      <c r="L55" s="44"/>
+      <c r="M55" s="41"/>
+    </row>
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="10">
+        <v>1</v>
+      </c>
+      <c r="E56" s="10">
+        <v>1</v>
+      </c>
+      <c r="F56" s="10">
+        <v>1</v>
+      </c>
+      <c r="G56" s="10">
+        <v>3</v>
+      </c>
+      <c r="H56" s="10">
+        <v>43</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="37"/>
+      <c r="K56" s="42"/>
+      <c r="L56" s="45"/>
+      <c r="M56" s="42"/>
+    </row>
+    <row r="57" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="37"/>
+      <c r="C57" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="8">
+        <v>1</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8">
+        <v>2</v>
+      </c>
+      <c r="G57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="8">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B58" s="2"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="11">
+        <v>30</v>
+      </c>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B60" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="17">
+        <v>1</v>
+      </c>
+      <c r="D60" s="18">
+        <v>2</v>
+      </c>
+      <c r="E60" s="19">
+        <v>3</v>
+      </c>
+      <c r="F60" s="17">
+        <v>4</v>
+      </c>
+      <c r="G60" s="18">
+        <v>5</v>
+      </c>
+      <c r="H60" s="19">
+        <v>6</v>
+      </c>
+      <c r="I60" s="17">
+        <v>7</v>
+      </c>
+      <c r="J60" s="18">
+        <v>8</v>
+      </c>
+      <c r="K60" s="19">
+        <v>9</v>
+      </c>
+      <c r="L60" s="11"/>
+      <c r="M60" s="2"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="11">
+        <v>4</v>
+      </c>
+      <c r="D61" s="11">
+        <v>3</v>
+      </c>
+      <c r="E61" s="21">
+        <v>5</v>
+      </c>
+      <c r="F61" s="22">
+        <v>4</v>
+      </c>
+      <c r="G61" s="11">
+        <v>4</v>
+      </c>
+      <c r="H61" s="21">
+        <v>4</v>
+      </c>
+      <c r="I61" s="22">
+        <v>4</v>
+      </c>
+      <c r="J61" s="11">
+        <v>3</v>
+      </c>
+      <c r="K61" s="21">
+        <v>5</v>
+      </c>
+      <c r="L61" s="11">
+        <v>36</v>
+      </c>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="11">
+        <v>14</v>
+      </c>
+      <c r="D62" s="11">
+        <v>8</v>
+      </c>
+      <c r="E62" s="21">
+        <v>6</v>
+      </c>
+      <c r="F62" s="22">
+        <v>4</v>
+      </c>
+      <c r="G62" s="11">
+        <v>16</v>
+      </c>
+      <c r="H62" s="21">
+        <v>2</v>
+      </c>
+      <c r="I62" s="22">
+        <v>10</v>
+      </c>
+      <c r="J62" s="11">
+        <v>12</v>
+      </c>
+      <c r="K62" s="21">
+        <v>18</v>
+      </c>
+      <c r="L62" s="11"/>
+      <c r="M62" s="2"/>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B63" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="24">
+        <v>5</v>
+      </c>
+      <c r="D63" s="25">
+        <v>4</v>
+      </c>
+      <c r="E63" s="26">
+        <v>10</v>
+      </c>
+      <c r="F63" s="24">
+        <v>4</v>
+      </c>
+      <c r="G63" s="25">
+        <v>8</v>
+      </c>
+      <c r="H63" s="26">
+        <v>7</v>
+      </c>
+      <c r="I63" s="24">
+        <v>8</v>
+      </c>
+      <c r="J63" s="25">
+        <v>6</v>
+      </c>
+      <c r="K63" s="26">
+        <v>5</v>
+      </c>
+      <c r="L63" s="11">
+        <v>57</v>
+      </c>
+      <c r="M63" s="27">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B64" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="22">
+        <v>1</v>
+      </c>
+      <c r="D64" s="11">
+        <v>2</v>
+      </c>
+      <c r="E64" s="21">
+        <v>2</v>
+      </c>
+      <c r="F64" s="22">
+        <v>2</v>
+      </c>
+      <c r="G64" s="11">
+        <v>1</v>
+      </c>
+      <c r="H64" s="21">
+        <v>2</v>
+      </c>
+      <c r="I64" s="22">
+        <v>2</v>
+      </c>
+      <c r="J64" s="11">
+        <v>2</v>
+      </c>
+      <c r="K64" s="21">
+        <v>1</v>
+      </c>
+      <c r="L64" s="27"/>
+      <c r="M64" s="2"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B65" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="22">
+        <v>4</v>
+      </c>
+      <c r="D65" s="11">
+        <v>2</v>
+      </c>
+      <c r="E65" s="21">
+        <v>8</v>
+      </c>
+      <c r="F65" s="22">
+        <v>2</v>
+      </c>
+      <c r="G65" s="11">
+        <v>7</v>
+      </c>
+      <c r="H65" s="21">
+        <v>5</v>
+      </c>
+      <c r="I65" s="22">
+        <v>6</v>
+      </c>
+      <c r="J65" s="11">
+        <v>4</v>
+      </c>
+      <c r="K65" s="21">
+        <v>4</v>
+      </c>
+      <c r="L65" s="28">
+        <v>42</v>
+      </c>
+      <c r="M65" s="27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="30">
+        <v>0</v>
+      </c>
+      <c r="D66" s="31">
+        <v>1</v>
+      </c>
+      <c r="E66" s="32">
+        <v>0</v>
+      </c>
+      <c r="F66" s="30">
+        <v>1</v>
+      </c>
+      <c r="G66" s="31">
+        <v>0</v>
+      </c>
+      <c r="H66" s="32">
+        <v>1</v>
+      </c>
+      <c r="I66" s="30">
+        <v>0</v>
+      </c>
+      <c r="J66" s="31">
+        <v>0</v>
+      </c>
+      <c r="K66" s="32">
+        <v>0</v>
+      </c>
+      <c r="L66" s="11"/>
+      <c r="M66" s="2"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B67" s="2"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="2"/>
+    </row>
+    <row r="68" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="11">
+        <v>36</v>
+      </c>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="2"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B69" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="17">
+        <v>1</v>
+      </c>
+      <c r="D69" s="18">
+        <v>2</v>
+      </c>
+      <c r="E69" s="19">
+        <v>3</v>
+      </c>
+      <c r="F69" s="17">
+        <v>4</v>
+      </c>
+      <c r="G69" s="18">
+        <v>5</v>
+      </c>
+      <c r="H69" s="19">
+        <v>6</v>
+      </c>
+      <c r="I69" s="17">
+        <v>7</v>
+      </c>
+      <c r="J69" s="18">
+        <v>8</v>
+      </c>
+      <c r="K69" s="19">
+        <v>9</v>
+      </c>
+      <c r="L69" s="11"/>
+      <c r="M69" s="27"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B70" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="11">
+        <v>4</v>
+      </c>
+      <c r="D70" s="11">
+        <v>3</v>
+      </c>
+      <c r="E70" s="21">
+        <v>5</v>
+      </c>
+      <c r="F70" s="22">
+        <v>4</v>
+      </c>
+      <c r="G70" s="11">
+        <v>4</v>
+      </c>
+      <c r="H70" s="21">
+        <v>4</v>
+      </c>
+      <c r="I70" s="22">
+        <v>4</v>
+      </c>
+      <c r="J70" s="11">
+        <v>3</v>
+      </c>
+      <c r="K70" s="21">
+        <v>5</v>
+      </c>
+      <c r="L70" s="11">
+        <v>36</v>
+      </c>
+      <c r="M70" s="2"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B71" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="11">
+        <v>14</v>
+      </c>
+      <c r="D71" s="11">
+        <v>8</v>
+      </c>
+      <c r="E71" s="21">
+        <v>6</v>
+      </c>
+      <c r="F71" s="22">
+        <v>4</v>
+      </c>
+      <c r="G71" s="11">
+        <v>16</v>
+      </c>
+      <c r="H71" s="21">
+        <v>2</v>
+      </c>
+      <c r="I71" s="22">
+        <v>10</v>
+      </c>
+      <c r="J71" s="11">
+        <v>12</v>
+      </c>
+      <c r="K71" s="21">
+        <v>18</v>
+      </c>
+      <c r="L71" s="11"/>
+      <c r="M71" s="2"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B72" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" s="24">
+        <v>5</v>
+      </c>
+      <c r="D72" s="25">
+        <v>6</v>
+      </c>
+      <c r="E72" s="26">
+        <v>10</v>
+      </c>
+      <c r="F72" s="24">
+        <v>7</v>
+      </c>
+      <c r="G72" s="25">
+        <v>6</v>
+      </c>
+      <c r="H72" s="26">
+        <v>8</v>
+      </c>
+      <c r="I72" s="24">
+        <v>8</v>
+      </c>
+      <c r="J72" s="25">
+        <v>6</v>
+      </c>
+      <c r="K72" s="26">
+        <v>5</v>
+      </c>
+      <c r="L72" s="11">
+        <v>61</v>
+      </c>
+      <c r="M72" s="27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B73" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="22">
+        <v>2</v>
+      </c>
+      <c r="D73" s="11">
+        <v>2</v>
+      </c>
+      <c r="E73" s="21">
+        <v>2</v>
+      </c>
+      <c r="F73" s="22">
+        <v>2</v>
+      </c>
+      <c r="G73" s="11">
+        <v>2</v>
+      </c>
+      <c r="H73" s="21">
+        <v>2</v>
+      </c>
+      <c r="I73" s="22">
+        <v>2</v>
+      </c>
+      <c r="J73" s="11">
+        <v>2</v>
+      </c>
+      <c r="K73" s="21">
+        <v>2</v>
+      </c>
+      <c r="L73" s="27"/>
+      <c r="M73" s="2"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B74" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="22">
+        <v>3</v>
+      </c>
+      <c r="D74" s="11">
+        <v>4</v>
+      </c>
+      <c r="E74" s="21">
+        <v>8</v>
+      </c>
+      <c r="F74" s="22">
+        <v>5</v>
+      </c>
+      <c r="G74" s="11">
+        <v>4</v>
+      </c>
+      <c r="H74" s="21">
+        <v>6</v>
+      </c>
+      <c r="I74" s="22">
+        <v>6</v>
+      </c>
+      <c r="J74" s="11">
+        <v>4</v>
+      </c>
+      <c r="K74" s="21">
+        <v>3</v>
+      </c>
+      <c r="L74" s="28">
+        <v>43</v>
+      </c>
+      <c r="M74" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="30">
+        <v>1</v>
+      </c>
+      <c r="D75" s="31">
+        <v>0</v>
+      </c>
+      <c r="E75" s="32">
+        <v>0</v>
+      </c>
+      <c r="F75" s="30">
+        <v>0</v>
+      </c>
+      <c r="G75" s="31">
+        <v>1</v>
+      </c>
+      <c r="H75" s="32">
+        <v>0</v>
+      </c>
+      <c r="I75" s="30">
+        <v>0</v>
+      </c>
+      <c r="J75" s="31">
+        <v>0</v>
+      </c>
+      <c r="K75" s="32">
+        <v>1</v>
+      </c>
+      <c r="L75" s="11"/>
+      <c r="M75" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="J54:K56"/>
+    <mergeCell ref="L54:M56"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J4:K6"/>
+    <mergeCell ref="L4:M6"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="L28:M28"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="J29:K31"/>
     <mergeCell ref="L29:M31"/>
     <mergeCell ref="B31:B32"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J4:K6"/>
-    <mergeCell ref="L4:M6"/>
-    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:K16 C25:K25">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41:K41 C50:K50">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:K41 C50:K50">
+  <conditionalFormatting sqref="C66:K66 C75:K75">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583A2400-7B08-414E-B87F-185488502672}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAC45106-2140-4761-815A-CA19098116FA}"/>
   <bookViews>
-    <workbookView xWindow="-27840" yWindow="-855" windowWidth="23010" windowHeight="13680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -534,7 +534,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -5965,81 +5975,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="X27:Y27"/>
     <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="P28:P29"/>
     <mergeCell ref="X28:Y30"/>
     <mergeCell ref="Z28:AA30"/>
     <mergeCell ref="P30:P31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="16" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11118,81 +11128,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J127:K127"/>
+    <mergeCell ref="L127:M127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="J128:K130"/>
+    <mergeCell ref="L128:M130"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
     <mergeCell ref="J152:K152"/>
     <mergeCell ref="L152:M152"/>
     <mergeCell ref="B153:B154"/>
     <mergeCell ref="J153:K155"/>
     <mergeCell ref="L153:M155"/>
     <mergeCell ref="B155:B156"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="J103:K105"/>
-    <mergeCell ref="L103:M105"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J127:K127"/>
-    <mergeCell ref="L127:M127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="J128:K130"/>
-    <mergeCell ref="L128:M130"/>
-    <mergeCell ref="B130:B131"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115:K115 C124:K124">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C140:K140 C149:K149">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C165:K165 C174:K174">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11202,7 +11212,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:M75"/>
+  <dimension ref="B1:M100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -13378,38 +13388,772 @@
       <c r="L75" s="11"/>
       <c r="M75" s="2"/>
     </row>
+    <row r="77" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I78" s="4"/>
+      <c r="J78" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="K78" s="34"/>
+      <c r="L78" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M78" s="34"/>
+    </row>
+    <row r="79" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="6">
+        <v>1</v>
+      </c>
+      <c r="E79" s="6">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6">
+        <v>0</v>
+      </c>
+      <c r="G79" s="6">
+        <v>2</v>
+      </c>
+      <c r="H79" s="6">
+        <v>52</v>
+      </c>
+      <c r="I79" s="2"/>
+      <c r="J79" s="38">
+        <v>7</v>
+      </c>
+      <c r="K79" s="39"/>
+      <c r="L79" s="43">
+        <v>1</v>
+      </c>
+      <c r="M79" s="39"/>
+    </row>
+    <row r="80" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="37"/>
+      <c r="C80" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="8">
+        <v>2</v>
+      </c>
+      <c r="E80" s="8">
+        <v>2</v>
+      </c>
+      <c r="F80" s="8">
+        <v>1</v>
+      </c>
+      <c r="G80" s="8">
+        <v>1</v>
+      </c>
+      <c r="H80" s="8">
+        <v>1</v>
+      </c>
+      <c r="I80" s="2"/>
+      <c r="J80" s="40"/>
+      <c r="K80" s="41"/>
+      <c r="L80" s="44"/>
+      <c r="M80" s="41"/>
+    </row>
+    <row r="81" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="10">
+        <v>0</v>
+      </c>
+      <c r="E81" s="10">
+        <v>0</v>
+      </c>
+      <c r="F81" s="10">
+        <v>0</v>
+      </c>
+      <c r="G81" s="10">
+        <v>0</v>
+      </c>
+      <c r="H81" s="10">
+        <v>54</v>
+      </c>
+      <c r="I81" s="2"/>
+      <c r="J81" s="37"/>
+      <c r="K81" s="42"/>
+      <c r="L81" s="45"/>
+      <c r="M81" s="42"/>
+    </row>
+    <row r="82" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="37"/>
+      <c r="C82" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="8">
+        <v>0</v>
+      </c>
+      <c r="E82" s="8">
+        <v>0</v>
+      </c>
+      <c r="F82" s="8">
+        <v>1</v>
+      </c>
+      <c r="G82" s="8">
+        <v>0</v>
+      </c>
+      <c r="H82" s="8">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="11"/>
+    </row>
+    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B83" s="2"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="2"/>
+    </row>
+    <row r="84" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="11">
+        <v>36</v>
+      </c>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K84" s="11"/>
+      <c r="L84" s="11"/>
+      <c r="M84" s="2"/>
+    </row>
+    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B85" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="17">
+        <v>1</v>
+      </c>
+      <c r="D85" s="18">
+        <v>2</v>
+      </c>
+      <c r="E85" s="19">
+        <v>3</v>
+      </c>
+      <c r="F85" s="17">
+        <v>4</v>
+      </c>
+      <c r="G85" s="18">
+        <v>5</v>
+      </c>
+      <c r="H85" s="19">
+        <v>6</v>
+      </c>
+      <c r="I85" s="17">
+        <v>7</v>
+      </c>
+      <c r="J85" s="18">
+        <v>8</v>
+      </c>
+      <c r="K85" s="19">
+        <v>9</v>
+      </c>
+      <c r="L85" s="11"/>
+      <c r="M85" s="2"/>
+    </row>
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B86" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="11">
+        <v>4</v>
+      </c>
+      <c r="D86" s="11">
+        <v>3</v>
+      </c>
+      <c r="E86" s="21">
+        <v>4</v>
+      </c>
+      <c r="F86" s="22">
+        <v>5</v>
+      </c>
+      <c r="G86" s="11">
+        <v>4</v>
+      </c>
+      <c r="H86" s="21">
+        <v>4</v>
+      </c>
+      <c r="I86" s="22">
+        <v>3</v>
+      </c>
+      <c r="J86" s="11">
+        <v>5</v>
+      </c>
+      <c r="K86" s="21">
+        <v>4</v>
+      </c>
+      <c r="L86" s="11">
+        <v>36</v>
+      </c>
+      <c r="M86" s="2"/>
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B87" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="11">
+        <v>7</v>
+      </c>
+      <c r="D87" s="11">
+        <v>15</v>
+      </c>
+      <c r="E87" s="21">
+        <v>5</v>
+      </c>
+      <c r="F87" s="22">
+        <v>13</v>
+      </c>
+      <c r="G87" s="11">
+        <v>3</v>
+      </c>
+      <c r="H87" s="21">
+        <v>11</v>
+      </c>
+      <c r="I87" s="22">
+        <v>17</v>
+      </c>
+      <c r="J87" s="11">
+        <v>9</v>
+      </c>
+      <c r="K87" s="21">
+        <v>1</v>
+      </c>
+      <c r="L87" s="11"/>
+      <c r="M87" s="2"/>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B88" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" s="24">
+        <v>8</v>
+      </c>
+      <c r="D88" s="25">
+        <v>5</v>
+      </c>
+      <c r="E88" s="26">
+        <v>8</v>
+      </c>
+      <c r="F88" s="24">
+        <v>10</v>
+      </c>
+      <c r="G88" s="25">
+        <v>8</v>
+      </c>
+      <c r="H88" s="26">
+        <v>7</v>
+      </c>
+      <c r="I88" s="24">
+        <v>6</v>
+      </c>
+      <c r="J88" s="25">
+        <v>10</v>
+      </c>
+      <c r="K88" s="26">
+        <v>8</v>
+      </c>
+      <c r="L88" s="11">
+        <v>70</v>
+      </c>
+      <c r="M88" s="27">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B89" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="22">
+        <v>2</v>
+      </c>
+      <c r="D89" s="11">
+        <v>2</v>
+      </c>
+      <c r="E89" s="21">
+        <v>2</v>
+      </c>
+      <c r="F89" s="22">
+        <v>2</v>
+      </c>
+      <c r="G89" s="11">
+        <v>2</v>
+      </c>
+      <c r="H89" s="21">
+        <v>2</v>
+      </c>
+      <c r="I89" s="22">
+        <v>2</v>
+      </c>
+      <c r="J89" s="11">
+        <v>2</v>
+      </c>
+      <c r="K89" s="21">
+        <v>2</v>
+      </c>
+      <c r="L89" s="27"/>
+      <c r="M89" s="2"/>
+    </row>
+    <row r="90" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B90" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" s="22">
+        <v>6</v>
+      </c>
+      <c r="D90" s="11">
+        <v>3</v>
+      </c>
+      <c r="E90" s="21">
+        <v>6</v>
+      </c>
+      <c r="F90" s="22">
+        <v>8</v>
+      </c>
+      <c r="G90" s="11">
+        <v>6</v>
+      </c>
+      <c r="H90" s="21">
+        <v>5</v>
+      </c>
+      <c r="I90" s="22">
+        <v>4</v>
+      </c>
+      <c r="J90" s="11">
+        <v>8</v>
+      </c>
+      <c r="K90" s="21">
+        <v>6</v>
+      </c>
+      <c r="L90" s="28">
+        <v>52</v>
+      </c>
+      <c r="M90" s="27">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" s="30">
+        <v>0</v>
+      </c>
+      <c r="D91" s="31">
+        <v>1</v>
+      </c>
+      <c r="E91" s="32">
+        <v>0</v>
+      </c>
+      <c r="F91" s="30">
+        <v>0</v>
+      </c>
+      <c r="G91" s="31">
+        <v>0</v>
+      </c>
+      <c r="H91" s="32">
+        <v>1</v>
+      </c>
+      <c r="I91" s="30">
+        <v>0</v>
+      </c>
+      <c r="J91" s="31">
+        <v>0</v>
+      </c>
+      <c r="K91" s="32">
+        <v>0</v>
+      </c>
+      <c r="L91" s="11"/>
+      <c r="M91" s="2"/>
+    </row>
+    <row r="92" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B92" s="2"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11"/>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="2"/>
+    </row>
+    <row r="93" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="11">
+        <v>36</v>
+      </c>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K93" s="11"/>
+      <c r="L93" s="11"/>
+      <c r="M93" s="2"/>
+    </row>
+    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B94" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" s="17">
+        <v>1</v>
+      </c>
+      <c r="D94" s="18">
+        <v>2</v>
+      </c>
+      <c r="E94" s="19">
+        <v>3</v>
+      </c>
+      <c r="F94" s="17">
+        <v>4</v>
+      </c>
+      <c r="G94" s="18">
+        <v>5</v>
+      </c>
+      <c r="H94" s="19">
+        <v>6</v>
+      </c>
+      <c r="I94" s="17">
+        <v>7</v>
+      </c>
+      <c r="J94" s="18">
+        <v>8</v>
+      </c>
+      <c r="K94" s="19">
+        <v>9</v>
+      </c>
+      <c r="L94" s="11"/>
+      <c r="M94" s="27"/>
+    </row>
+    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B95" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="11">
+        <v>4</v>
+      </c>
+      <c r="D95" s="11">
+        <v>3</v>
+      </c>
+      <c r="E95" s="21">
+        <v>4</v>
+      </c>
+      <c r="F95" s="22">
+        <v>5</v>
+      </c>
+      <c r="G95" s="11">
+        <v>4</v>
+      </c>
+      <c r="H95" s="21">
+        <v>4</v>
+      </c>
+      <c r="I95" s="22">
+        <v>3</v>
+      </c>
+      <c r="J95" s="11">
+        <v>5</v>
+      </c>
+      <c r="K95" s="21">
+        <v>4</v>
+      </c>
+      <c r="L95" s="11">
+        <v>36</v>
+      </c>
+      <c r="M95" s="2"/>
+    </row>
+    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B96" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" s="11">
+        <v>17</v>
+      </c>
+      <c r="D96" s="11">
+        <v>9</v>
+      </c>
+      <c r="E96" s="21">
+        <v>5</v>
+      </c>
+      <c r="F96" s="22">
+        <v>7</v>
+      </c>
+      <c r="G96" s="11">
+        <v>3</v>
+      </c>
+      <c r="H96" s="21">
+        <v>15</v>
+      </c>
+      <c r="I96" s="22">
+        <v>11</v>
+      </c>
+      <c r="J96" s="11">
+        <v>13</v>
+      </c>
+      <c r="K96" s="21">
+        <v>1</v>
+      </c>
+      <c r="L96" s="11"/>
+      <c r="M96" s="2"/>
+    </row>
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B97" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="24">
+        <v>8</v>
+      </c>
+      <c r="D97" s="25">
+        <v>6</v>
+      </c>
+      <c r="E97" s="26">
+        <v>8</v>
+      </c>
+      <c r="F97" s="24">
+        <v>10</v>
+      </c>
+      <c r="G97" s="25">
+        <v>8</v>
+      </c>
+      <c r="H97" s="26">
+        <v>8</v>
+      </c>
+      <c r="I97" s="24">
+        <v>6</v>
+      </c>
+      <c r="J97" s="25">
+        <v>10</v>
+      </c>
+      <c r="K97" s="26">
+        <v>8</v>
+      </c>
+      <c r="L97" s="11">
+        <v>72</v>
+      </c>
+      <c r="M97" s="27">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B98" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="22">
+        <v>2</v>
+      </c>
+      <c r="D98" s="11">
+        <v>2</v>
+      </c>
+      <c r="E98" s="21">
+        <v>2</v>
+      </c>
+      <c r="F98" s="22">
+        <v>2</v>
+      </c>
+      <c r="G98" s="11">
+        <v>2</v>
+      </c>
+      <c r="H98" s="21">
+        <v>2</v>
+      </c>
+      <c r="I98" s="22">
+        <v>2</v>
+      </c>
+      <c r="J98" s="11">
+        <v>2</v>
+      </c>
+      <c r="K98" s="21">
+        <v>2</v>
+      </c>
+      <c r="L98" s="27"/>
+      <c r="M98" s="2"/>
+    </row>
+    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B99" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="22">
+        <v>6</v>
+      </c>
+      <c r="D99" s="11">
+        <v>4</v>
+      </c>
+      <c r="E99" s="21">
+        <v>6</v>
+      </c>
+      <c r="F99" s="22">
+        <v>8</v>
+      </c>
+      <c r="G99" s="11">
+        <v>6</v>
+      </c>
+      <c r="H99" s="21">
+        <v>6</v>
+      </c>
+      <c r="I99" s="22">
+        <v>4</v>
+      </c>
+      <c r="J99" s="11">
+        <v>8</v>
+      </c>
+      <c r="K99" s="21">
+        <v>6</v>
+      </c>
+      <c r="L99" s="28">
+        <v>54</v>
+      </c>
+      <c r="M99" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="30">
+        <v>0</v>
+      </c>
+      <c r="D100" s="31">
+        <v>0</v>
+      </c>
+      <c r="E100" s="32">
+        <v>0</v>
+      </c>
+      <c r="F100" s="30">
+        <v>0</v>
+      </c>
+      <c r="G100" s="31">
+        <v>0</v>
+      </c>
+      <c r="H100" s="32">
+        <v>0</v>
+      </c>
+      <c r="I100" s="30">
+        <v>0</v>
+      </c>
+      <c r="J100" s="31">
+        <v>0</v>
+      </c>
+      <c r="K100" s="32">
+        <v>0</v>
+      </c>
+      <c r="L100" s="11"/>
+      <c r="M100" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="J79:K81"/>
+    <mergeCell ref="L79:M81"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="J29:K31"/>
+    <mergeCell ref="L29:M31"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J4:K6"/>
+    <mergeCell ref="L4:M6"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="J53:K53"/>
     <mergeCell ref="L53:M53"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="J54:K56"/>
     <mergeCell ref="L54:M56"/>
     <mergeCell ref="B56:B57"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J4:K6"/>
-    <mergeCell ref="L4:M6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="J29:K31"/>
-    <mergeCell ref="L29:M31"/>
-    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:K16 C25:K25">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41:K41 C50:K50">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:K41 C50:K50">
+  <conditionalFormatting sqref="C66:K66 C75:K75">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C66:K66 C75:K75">
+  <conditionalFormatting sqref="C91:K91 C100:K100">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAC45106-2140-4761-815A-CA19098116FA}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6660ADE0-7097-472D-B9EA-4E7D8CB603F2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -534,7 +534,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -5975,81 +5985,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="P28:P29"/>
+    <mergeCell ref="X28:Y30"/>
+    <mergeCell ref="Z28:AA30"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="J77:K77"/>
     <mergeCell ref="L77:M77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="J78:K80"/>
     <mergeCell ref="L78:M80"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="P28:P29"/>
-    <mergeCell ref="X28:Y30"/>
-    <mergeCell ref="Z28:AA30"/>
-    <mergeCell ref="P30:P31"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="17" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="16" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11128,81 +11138,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J152:K152"/>
+    <mergeCell ref="L152:M152"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="J153:K155"/>
+    <mergeCell ref="L153:M155"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
     <mergeCell ref="J127:K127"/>
     <mergeCell ref="L127:M127"/>
     <mergeCell ref="B128:B129"/>
     <mergeCell ref="J128:K130"/>
     <mergeCell ref="L128:M130"/>
     <mergeCell ref="B130:B131"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="J103:K105"/>
-    <mergeCell ref="L103:M105"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="J152:K152"/>
-    <mergeCell ref="L152:M152"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="J153:K155"/>
-    <mergeCell ref="L153:M155"/>
-    <mergeCell ref="B155:B156"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115:K115 C124:K124">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C140:K140 C149:K149">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C165:K165 C174:K174">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14113,48 +14123,48 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="J54:K56"/>
+    <mergeCell ref="L54:M56"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J4:K6"/>
+    <mergeCell ref="L4:M6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="J29:K31"/>
+    <mergeCell ref="L29:M31"/>
+    <mergeCell ref="B31:B32"/>
     <mergeCell ref="J78:K78"/>
     <mergeCell ref="L78:M78"/>
     <mergeCell ref="B79:B80"/>
     <mergeCell ref="J79:K81"/>
     <mergeCell ref="L79:M81"/>
     <mergeCell ref="B81:B82"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="J29:K31"/>
-    <mergeCell ref="L29:M31"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J4:K6"/>
-    <mergeCell ref="L4:M6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="J54:K56"/>
-    <mergeCell ref="L54:M56"/>
-    <mergeCell ref="B56:B57"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:K16 C25:K25">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41:K41 C50:K50">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:K66 C75:K75">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C91:K91 C100:K100">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14164,9 +14174,749 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="34"/>
+      <c r="L2" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="34"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>43</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="38">
+        <v>4</v>
+      </c>
+      <c r="K3" s="39"/>
+      <c r="L3" s="43">
+        <v>4</v>
+      </c>
+      <c r="M3" s="39"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="37"/>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="41"/>
+    </row>
+    <row r="5" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10">
+        <v>43</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="42"/>
+    </row>
+    <row r="6" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="37"/>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="2"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11">
+        <v>36</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+      <c r="D9" s="18">
+        <v>2</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3</v>
+      </c>
+      <c r="F9" s="17">
+        <v>4</v>
+      </c>
+      <c r="G9" s="18">
+        <v>5</v>
+      </c>
+      <c r="H9" s="19">
+        <v>6</v>
+      </c>
+      <c r="I9" s="17">
+        <v>7</v>
+      </c>
+      <c r="J9" s="18">
+        <v>8</v>
+      </c>
+      <c r="K9" s="19">
+        <v>9</v>
+      </c>
+      <c r="L9" s="11"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="11">
+        <v>4</v>
+      </c>
+      <c r="D10" s="11">
+        <v>5</v>
+      </c>
+      <c r="E10" s="21">
+        <v>3</v>
+      </c>
+      <c r="F10" s="22">
+        <v>4</v>
+      </c>
+      <c r="G10" s="11">
+        <v>4</v>
+      </c>
+      <c r="H10" s="21">
+        <v>3</v>
+      </c>
+      <c r="I10" s="22">
+        <v>5</v>
+      </c>
+      <c r="J10" s="11">
+        <v>4</v>
+      </c>
+      <c r="K10" s="21">
+        <v>4</v>
+      </c>
+      <c r="L10" s="11">
+        <v>36</v>
+      </c>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="11">
+        <v>7</v>
+      </c>
+      <c r="D11" s="11">
+        <v>17</v>
+      </c>
+      <c r="E11" s="21">
+        <v>15</v>
+      </c>
+      <c r="F11" s="22">
+        <v>1</v>
+      </c>
+      <c r="G11" s="11">
+        <v>11</v>
+      </c>
+      <c r="H11" s="21">
+        <v>9</v>
+      </c>
+      <c r="I11" s="22">
+        <v>13</v>
+      </c>
+      <c r="J11" s="11">
+        <v>5</v>
+      </c>
+      <c r="K11" s="21">
+        <v>3</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="24">
+        <v>7</v>
+      </c>
+      <c r="D12" s="25">
+        <v>10</v>
+      </c>
+      <c r="E12" s="26">
+        <v>6</v>
+      </c>
+      <c r="F12" s="24">
+        <v>8</v>
+      </c>
+      <c r="G12" s="25">
+        <v>5</v>
+      </c>
+      <c r="H12" s="26">
+        <v>6</v>
+      </c>
+      <c r="I12" s="24">
+        <v>6</v>
+      </c>
+      <c r="J12" s="25">
+        <v>6</v>
+      </c>
+      <c r="K12" s="26">
+        <v>7</v>
+      </c>
+      <c r="L12" s="11">
+        <v>61</v>
+      </c>
+      <c r="M12" s="27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="22">
+        <v>2</v>
+      </c>
+      <c r="D13" s="11">
+        <v>2</v>
+      </c>
+      <c r="E13" s="21">
+        <v>2</v>
+      </c>
+      <c r="F13" s="22">
+        <v>2</v>
+      </c>
+      <c r="G13" s="11">
+        <v>2</v>
+      </c>
+      <c r="H13" s="21">
+        <v>2</v>
+      </c>
+      <c r="I13" s="22">
+        <v>2</v>
+      </c>
+      <c r="J13" s="11">
+        <v>2</v>
+      </c>
+      <c r="K13" s="21">
+        <v>2</v>
+      </c>
+      <c r="L13" s="27"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="22">
+        <v>5</v>
+      </c>
+      <c r="D14" s="11">
+        <v>8</v>
+      </c>
+      <c r="E14" s="21">
+        <v>4</v>
+      </c>
+      <c r="F14" s="22">
+        <v>6</v>
+      </c>
+      <c r="G14" s="11">
+        <v>3</v>
+      </c>
+      <c r="H14" s="21">
+        <v>4</v>
+      </c>
+      <c r="I14" s="22">
+        <v>4</v>
+      </c>
+      <c r="J14" s="11">
+        <v>4</v>
+      </c>
+      <c r="K14" s="21">
+        <v>5</v>
+      </c>
+      <c r="L14" s="28">
+        <v>43</v>
+      </c>
+      <c r="M14" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="30">
+        <v>0</v>
+      </c>
+      <c r="D15" s="31">
+        <v>0</v>
+      </c>
+      <c r="E15" s="32">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30">
+        <v>0</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0</v>
+      </c>
+      <c r="H15" s="32">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30">
+        <v>0</v>
+      </c>
+      <c r="J15" s="31">
+        <v>0</v>
+      </c>
+      <c r="K15" s="32">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="11">
+        <v>36</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="17">
+        <v>1</v>
+      </c>
+      <c r="D18" s="18">
+        <v>2</v>
+      </c>
+      <c r="E18" s="19">
+        <v>3</v>
+      </c>
+      <c r="F18" s="17">
+        <v>4</v>
+      </c>
+      <c r="G18" s="18">
+        <v>5</v>
+      </c>
+      <c r="H18" s="19">
+        <v>6</v>
+      </c>
+      <c r="I18" s="17">
+        <v>7</v>
+      </c>
+      <c r="J18" s="18">
+        <v>8</v>
+      </c>
+      <c r="K18" s="19">
+        <v>9</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" s="27"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="11">
+        <v>4</v>
+      </c>
+      <c r="D19" s="11">
+        <v>5</v>
+      </c>
+      <c r="E19" s="21">
+        <v>3</v>
+      </c>
+      <c r="F19" s="22">
+        <v>4</v>
+      </c>
+      <c r="G19" s="11">
+        <v>4</v>
+      </c>
+      <c r="H19" s="21">
+        <v>3</v>
+      </c>
+      <c r="I19" s="22">
+        <v>5</v>
+      </c>
+      <c r="J19" s="11">
+        <v>4</v>
+      </c>
+      <c r="K19" s="21">
+        <v>4</v>
+      </c>
+      <c r="L19" s="11">
+        <v>36</v>
+      </c>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="11">
+        <v>7</v>
+      </c>
+      <c r="D20" s="11">
+        <v>17</v>
+      </c>
+      <c r="E20" s="21">
+        <v>15</v>
+      </c>
+      <c r="F20" s="22">
+        <v>1</v>
+      </c>
+      <c r="G20" s="11">
+        <v>11</v>
+      </c>
+      <c r="H20" s="21">
+        <v>9</v>
+      </c>
+      <c r="I20" s="22">
+        <v>13</v>
+      </c>
+      <c r="J20" s="11">
+        <v>5</v>
+      </c>
+      <c r="K20" s="21">
+        <v>3</v>
+      </c>
+      <c r="L20" s="11"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="24">
+        <v>7</v>
+      </c>
+      <c r="D21" s="25">
+        <v>10</v>
+      </c>
+      <c r="E21" s="26">
+        <v>6</v>
+      </c>
+      <c r="F21" s="24">
+        <v>8</v>
+      </c>
+      <c r="G21" s="25">
+        <v>5</v>
+      </c>
+      <c r="H21" s="26">
+        <v>6</v>
+      </c>
+      <c r="I21" s="24">
+        <v>6</v>
+      </c>
+      <c r="J21" s="25">
+        <v>6</v>
+      </c>
+      <c r="K21" s="26">
+        <v>7</v>
+      </c>
+      <c r="L21" s="11">
+        <v>61</v>
+      </c>
+      <c r="M21" s="27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="22">
+        <v>2</v>
+      </c>
+      <c r="D22" s="11">
+        <v>2</v>
+      </c>
+      <c r="E22" s="21">
+        <v>2</v>
+      </c>
+      <c r="F22" s="22">
+        <v>2</v>
+      </c>
+      <c r="G22" s="11">
+        <v>2</v>
+      </c>
+      <c r="H22" s="21">
+        <v>2</v>
+      </c>
+      <c r="I22" s="22">
+        <v>2</v>
+      </c>
+      <c r="J22" s="11">
+        <v>2</v>
+      </c>
+      <c r="K22" s="21">
+        <v>2</v>
+      </c>
+      <c r="L22" s="27"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="22">
+        <v>5</v>
+      </c>
+      <c r="D23" s="11">
+        <v>8</v>
+      </c>
+      <c r="E23" s="21">
+        <v>4</v>
+      </c>
+      <c r="F23" s="22">
+        <v>6</v>
+      </c>
+      <c r="G23" s="11">
+        <v>3</v>
+      </c>
+      <c r="H23" s="21">
+        <v>4</v>
+      </c>
+      <c r="I23" s="22">
+        <v>4</v>
+      </c>
+      <c r="J23" s="11">
+        <v>4</v>
+      </c>
+      <c r="K23" s="21">
+        <v>5</v>
+      </c>
+      <c r="L23" s="28">
+        <v>43</v>
+      </c>
+      <c r="M23" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="30">
+        <v>0</v>
+      </c>
+      <c r="D24" s="31">
+        <v>0</v>
+      </c>
+      <c r="E24" s="32">
+        <v>0</v>
+      </c>
+      <c r="F24" s="30">
+        <v>0</v>
+      </c>
+      <c r="G24" s="31">
+        <v>0</v>
+      </c>
+      <c r="H24" s="32">
+        <v>0</v>
+      </c>
+      <c r="I24" s="30">
+        <v>0</v>
+      </c>
+      <c r="J24" s="31">
+        <v>0</v>
+      </c>
+      <c r="K24" s="32">
+        <v>0</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C15:K15 C24:K24">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6660ADE0-7097-472D-B9EA-4E7D8CB603F2}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00D5892-EA1F-44EC-9501-6090E99495A3}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -534,7 +534,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -5985,81 +5995,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="X27:Y27"/>
     <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="P28:P29"/>
     <mergeCell ref="X28:Y30"/>
     <mergeCell ref="Z28:AA30"/>
     <mergeCell ref="P30:P31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11138,81 +11148,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J127:K127"/>
+    <mergeCell ref="L127:M127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="J128:K130"/>
+    <mergeCell ref="L128:M130"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
     <mergeCell ref="J152:K152"/>
     <mergeCell ref="L152:M152"/>
     <mergeCell ref="B153:B154"/>
     <mergeCell ref="J153:K155"/>
     <mergeCell ref="L153:M155"/>
     <mergeCell ref="B155:B156"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="J103:K105"/>
-    <mergeCell ref="L103:M105"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J127:K127"/>
-    <mergeCell ref="L127:M127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="J128:K130"/>
-    <mergeCell ref="L128:M130"/>
-    <mergeCell ref="B130:B131"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115:K115 C124:K124">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C140:K140 C149:K149">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C165:K165 C174:K174">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14123,48 +14133,48 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="J79:K81"/>
+    <mergeCell ref="L79:M81"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="J29:K31"/>
+    <mergeCell ref="L29:M31"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J4:K6"/>
+    <mergeCell ref="L4:M6"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="J53:K53"/>
     <mergeCell ref="L53:M53"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="J54:K56"/>
     <mergeCell ref="L54:M56"/>
     <mergeCell ref="B56:B57"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J4:K6"/>
-    <mergeCell ref="L4:M6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="J29:K31"/>
-    <mergeCell ref="L29:M31"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="L78:M78"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="J79:K81"/>
-    <mergeCell ref="L79:M81"/>
-    <mergeCell ref="B81:B82"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:K16 C25:K25">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41:K41 C50:K50">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:K66 C75:K75">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C91:K91 C100:K100">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14174,7 +14184,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:M24"/>
+  <dimension ref="B1:M49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -14903,8 +14913,737 @@
       <c r="L24" s="11"/>
       <c r="M24" s="2"/>
     </row>
+    <row r="26" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="34"/>
+      <c r="L27" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27" s="34"/>
+    </row>
+    <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6">
+        <v>3</v>
+      </c>
+      <c r="G28" s="6">
+        <v>6</v>
+      </c>
+      <c r="H28" s="6">
+        <v>42</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="38">
+        <v>7</v>
+      </c>
+      <c r="K28" s="39"/>
+      <c r="L28" s="43">
+        <v>1</v>
+      </c>
+      <c r="M28" s="39"/>
+    </row>
+    <row r="29" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="37"/>
+      <c r="C29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="8">
+        <v>2</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2</v>
+      </c>
+      <c r="G29" s="8">
+        <v>1</v>
+      </c>
+      <c r="H29" s="8">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="41"/>
+    </row>
+    <row r="30" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10">
+        <v>0</v>
+      </c>
+      <c r="G30" s="10">
+        <v>1</v>
+      </c>
+      <c r="H30" s="10">
+        <v>49</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="42"/>
+    </row>
+    <row r="31" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="37"/>
+      <c r="C31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="11">
+        <v>12</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B34" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="17">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18">
+        <v>2</v>
+      </c>
+      <c r="E34" s="19">
+        <v>3</v>
+      </c>
+      <c r="F34" s="17">
+        <v>4</v>
+      </c>
+      <c r="G34" s="18">
+        <v>5</v>
+      </c>
+      <c r="H34" s="19">
+        <v>6</v>
+      </c>
+      <c r="I34" s="17">
+        <v>7</v>
+      </c>
+      <c r="J34" s="18">
+        <v>8</v>
+      </c>
+      <c r="K34" s="19">
+        <v>9</v>
+      </c>
+      <c r="L34" s="11"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="11">
+        <v>4</v>
+      </c>
+      <c r="D35" s="11">
+        <v>5</v>
+      </c>
+      <c r="E35" s="21">
+        <v>3</v>
+      </c>
+      <c r="F35" s="22">
+        <v>4</v>
+      </c>
+      <c r="G35" s="11">
+        <v>4</v>
+      </c>
+      <c r="H35" s="21">
+        <v>3</v>
+      </c>
+      <c r="I35" s="22">
+        <v>5</v>
+      </c>
+      <c r="J35" s="11">
+        <v>4</v>
+      </c>
+      <c r="K35" s="21">
+        <v>4</v>
+      </c>
+      <c r="L35" s="11">
+        <v>36</v>
+      </c>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B36" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="11">
+        <v>7</v>
+      </c>
+      <c r="D36" s="11">
+        <v>17</v>
+      </c>
+      <c r="E36" s="21">
+        <v>15</v>
+      </c>
+      <c r="F36" s="22">
+        <v>1</v>
+      </c>
+      <c r="G36" s="11">
+        <v>11</v>
+      </c>
+      <c r="H36" s="21">
+        <v>9</v>
+      </c>
+      <c r="I36" s="22">
+        <v>13</v>
+      </c>
+      <c r="J36" s="11">
+        <v>5</v>
+      </c>
+      <c r="K36" s="21">
+        <v>3</v>
+      </c>
+      <c r="L36" s="11"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B37" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="24">
+        <v>5</v>
+      </c>
+      <c r="D37" s="25">
+        <v>6</v>
+      </c>
+      <c r="E37" s="26">
+        <v>3</v>
+      </c>
+      <c r="F37" s="24">
+        <v>6</v>
+      </c>
+      <c r="G37" s="25">
+        <v>6</v>
+      </c>
+      <c r="H37" s="26">
+        <v>6</v>
+      </c>
+      <c r="I37" s="24">
+        <v>6</v>
+      </c>
+      <c r="J37" s="25">
+        <v>6</v>
+      </c>
+      <c r="K37" s="26">
+        <v>4</v>
+      </c>
+      <c r="L37" s="11">
+        <v>48</v>
+      </c>
+      <c r="M37" s="27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="22">
+        <v>1</v>
+      </c>
+      <c r="D38" s="11">
+        <v>0</v>
+      </c>
+      <c r="E38" s="21">
+        <v>0</v>
+      </c>
+      <c r="F38" s="22">
+        <v>1</v>
+      </c>
+      <c r="G38" s="11">
+        <v>1</v>
+      </c>
+      <c r="H38" s="21">
+        <v>1</v>
+      </c>
+      <c r="I38" s="22">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11">
+        <v>1</v>
+      </c>
+      <c r="K38" s="21">
+        <v>1</v>
+      </c>
+      <c r="L38" s="27"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="22">
+        <v>4</v>
+      </c>
+      <c r="D39" s="11">
+        <v>6</v>
+      </c>
+      <c r="E39" s="21">
+        <v>3</v>
+      </c>
+      <c r="F39" s="22">
+        <v>5</v>
+      </c>
+      <c r="G39" s="11">
+        <v>5</v>
+      </c>
+      <c r="H39" s="21">
+        <v>5</v>
+      </c>
+      <c r="I39" s="22">
+        <v>6</v>
+      </c>
+      <c r="J39" s="11">
+        <v>5</v>
+      </c>
+      <c r="K39" s="21">
+        <v>3</v>
+      </c>
+      <c r="L39" s="28">
+        <v>42</v>
+      </c>
+      <c r="M39" s="27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="30">
+        <v>1</v>
+      </c>
+      <c r="D40" s="31">
+        <v>0</v>
+      </c>
+      <c r="E40" s="32">
+        <v>1</v>
+      </c>
+      <c r="F40" s="30">
+        <v>1</v>
+      </c>
+      <c r="G40" s="31">
+        <v>0</v>
+      </c>
+      <c r="H40" s="32">
+        <v>0</v>
+      </c>
+      <c r="I40" s="30">
+        <v>1</v>
+      </c>
+      <c r="J40" s="31">
+        <v>1</v>
+      </c>
+      <c r="K40" s="32">
+        <v>1</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B41" s="2"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="11">
+        <v>30</v>
+      </c>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="18">
+        <v>2</v>
+      </c>
+      <c r="E43" s="19">
+        <v>3</v>
+      </c>
+      <c r="F43" s="17">
+        <v>4</v>
+      </c>
+      <c r="G43" s="18">
+        <v>5</v>
+      </c>
+      <c r="H43" s="19">
+        <v>6</v>
+      </c>
+      <c r="I43" s="17">
+        <v>7</v>
+      </c>
+      <c r="J43" s="18">
+        <v>8</v>
+      </c>
+      <c r="K43" s="19">
+        <v>9</v>
+      </c>
+      <c r="L43" s="11"/>
+      <c r="M43" s="27"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B44" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="11">
+        <v>4</v>
+      </c>
+      <c r="D44" s="11">
+        <v>5</v>
+      </c>
+      <c r="E44" s="21">
+        <v>3</v>
+      </c>
+      <c r="F44" s="22">
+        <v>4</v>
+      </c>
+      <c r="G44" s="11">
+        <v>4</v>
+      </c>
+      <c r="H44" s="21">
+        <v>3</v>
+      </c>
+      <c r="I44" s="22">
+        <v>5</v>
+      </c>
+      <c r="J44" s="11">
+        <v>4</v>
+      </c>
+      <c r="K44" s="21">
+        <v>4</v>
+      </c>
+      <c r="L44" s="11">
+        <v>36</v>
+      </c>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B45" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="11">
+        <v>7</v>
+      </c>
+      <c r="D45" s="11">
+        <v>17</v>
+      </c>
+      <c r="E45" s="21">
+        <v>15</v>
+      </c>
+      <c r="F45" s="22">
+        <v>1</v>
+      </c>
+      <c r="G45" s="11">
+        <v>11</v>
+      </c>
+      <c r="H45" s="21">
+        <v>9</v>
+      </c>
+      <c r="I45" s="22">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11">
+        <v>5</v>
+      </c>
+      <c r="K45" s="21">
+        <v>3</v>
+      </c>
+      <c r="L45" s="11"/>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B46" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="24">
+        <v>8</v>
+      </c>
+      <c r="D46" s="25">
+        <v>7</v>
+      </c>
+      <c r="E46" s="26">
+        <v>5</v>
+      </c>
+      <c r="F46" s="24">
+        <v>8</v>
+      </c>
+      <c r="G46" s="25">
+        <v>7</v>
+      </c>
+      <c r="H46" s="26">
+        <v>6</v>
+      </c>
+      <c r="I46" s="24">
+        <v>8</v>
+      </c>
+      <c r="J46" s="25">
+        <v>8</v>
+      </c>
+      <c r="K46" s="26">
+        <v>7</v>
+      </c>
+      <c r="L46" s="11">
+        <v>64</v>
+      </c>
+      <c r="M46" s="27">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B47" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="22">
+        <v>2</v>
+      </c>
+      <c r="D47" s="11">
+        <v>1</v>
+      </c>
+      <c r="E47" s="21">
+        <v>1</v>
+      </c>
+      <c r="F47" s="22">
+        <v>2</v>
+      </c>
+      <c r="G47" s="11">
+        <v>2</v>
+      </c>
+      <c r="H47" s="21">
+        <v>2</v>
+      </c>
+      <c r="I47" s="22">
+        <v>1</v>
+      </c>
+      <c r="J47" s="11">
+        <v>2</v>
+      </c>
+      <c r="K47" s="21">
+        <v>2</v>
+      </c>
+      <c r="L47" s="27"/>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B48" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="22">
+        <v>6</v>
+      </c>
+      <c r="D48" s="11">
+        <v>6</v>
+      </c>
+      <c r="E48" s="21">
+        <v>4</v>
+      </c>
+      <c r="F48" s="22">
+        <v>6</v>
+      </c>
+      <c r="G48" s="11">
+        <v>5</v>
+      </c>
+      <c r="H48" s="21">
+        <v>4</v>
+      </c>
+      <c r="I48" s="22">
+        <v>7</v>
+      </c>
+      <c r="J48" s="11">
+        <v>6</v>
+      </c>
+      <c r="K48" s="21">
+        <v>5</v>
+      </c>
+      <c r="L48" s="28">
+        <v>49</v>
+      </c>
+      <c r="M48" s="27">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="30">
+        <v>0</v>
+      </c>
+      <c r="D49" s="31">
+        <v>0</v>
+      </c>
+      <c r="E49" s="32">
+        <v>0</v>
+      </c>
+      <c r="F49" s="30">
+        <v>0</v>
+      </c>
+      <c r="G49" s="31">
+        <v>0</v>
+      </c>
+      <c r="H49" s="32">
+        <v>1</v>
+      </c>
+      <c r="I49" s="30">
+        <v>0</v>
+      </c>
+      <c r="J49" s="31">
+        <v>0</v>
+      </c>
+      <c r="K49" s="32">
+        <v>0</v>
+      </c>
+      <c r="L49" s="11"/>
+      <c r="M49" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="B3:B4"/>
@@ -14913,6 +15652,11 @@
     <mergeCell ref="B5:B6"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:K40 C49:K49">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00D5892-EA1F-44EC-9501-6090E99495A3}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6EA0A8C-DE35-438E-96AA-ACC0285FA568}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="39">
   <si>
     <t>Skybrook</t>
   </si>
@@ -534,7 +534,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -5995,81 +6005,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="P28:P29"/>
+    <mergeCell ref="X28:Y30"/>
+    <mergeCell ref="Z28:AA30"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="J77:K77"/>
     <mergeCell ref="L77:M77"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="J78:K80"/>
     <mergeCell ref="L78:M80"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="P28:P29"/>
-    <mergeCell ref="X28:Y30"/>
-    <mergeCell ref="Z28:AA30"/>
-    <mergeCell ref="P30:P31"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="19" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:Y15 Q24:Y24">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q40:Y40 Q49:Y49">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q65:Y65 Q74:Y74">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11148,81 +11158,81 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J152:K152"/>
+    <mergeCell ref="L152:M152"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="J153:K155"/>
+    <mergeCell ref="L153:M155"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
     <mergeCell ref="J127:K127"/>
     <mergeCell ref="L127:M127"/>
     <mergeCell ref="B128:B129"/>
     <mergeCell ref="J128:K130"/>
     <mergeCell ref="L128:M130"/>
     <mergeCell ref="B130:B131"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="J103:K105"/>
-    <mergeCell ref="L103:M105"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="J152:K152"/>
-    <mergeCell ref="L152:M152"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="J153:K155"/>
-    <mergeCell ref="L153:M155"/>
-    <mergeCell ref="B155:B156"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115:K115 C124:K124">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C140:K140 C149:K149">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C165:K165 C174:K174">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14133,48 +14143,48 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="J54:K56"/>
+    <mergeCell ref="L54:M56"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J4:K6"/>
+    <mergeCell ref="L4:M6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="J29:K31"/>
+    <mergeCell ref="L29:M31"/>
+    <mergeCell ref="B31:B32"/>
     <mergeCell ref="J78:K78"/>
     <mergeCell ref="L78:M78"/>
     <mergeCell ref="B79:B80"/>
     <mergeCell ref="J79:K81"/>
     <mergeCell ref="L79:M81"/>
     <mergeCell ref="B81:B82"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="J29:K31"/>
-    <mergeCell ref="L29:M31"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J4:K6"/>
-    <mergeCell ref="L4:M6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="J54:K56"/>
-    <mergeCell ref="L54:M56"/>
-    <mergeCell ref="B56:B57"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:K16 C25:K25">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41:K41 C50:K50">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:K66 C75:K75">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C91:K91 C100:K100">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14184,7 +14194,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:M49"/>
+  <dimension ref="B1:M74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -15636,27 +15646,761 @@
       <c r="L49" s="11"/>
       <c r="M49" s="2"/>
     </row>
+    <row r="51" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" s="34"/>
+      <c r="L52" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="M52" s="34"/>
+    </row>
+    <row r="53" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6">
+        <v>3</v>
+      </c>
+      <c r="F53" s="6">
+        <v>3</v>
+      </c>
+      <c r="G53" s="6">
+        <v>8</v>
+      </c>
+      <c r="H53" s="6">
+        <v>41</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="38">
+        <v>8</v>
+      </c>
+      <c r="K53" s="39"/>
+      <c r="L53" s="43">
+        <v>0</v>
+      </c>
+      <c r="M53" s="39"/>
+    </row>
+    <row r="54" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="37"/>
+      <c r="C54" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="8">
+        <v>2</v>
+      </c>
+      <c r="E54" s="8">
+        <v>2</v>
+      </c>
+      <c r="F54" s="8">
+        <v>2</v>
+      </c>
+      <c r="G54" s="8">
+        <v>1</v>
+      </c>
+      <c r="H54" s="8">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="44"/>
+      <c r="M54" s="41"/>
+    </row>
+    <row r="55" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="10">
+        <v>0</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0</v>
+      </c>
+      <c r="F55" s="10">
+        <v>0</v>
+      </c>
+      <c r="G55" s="10">
+        <v>0</v>
+      </c>
+      <c r="H55" s="10">
+        <v>54</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="45"/>
+      <c r="M55" s="42"/>
+    </row>
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="37"/>
+      <c r="C56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="8">
+        <v>0</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0</v>
+      </c>
+      <c r="F56" s="8">
+        <v>0</v>
+      </c>
+      <c r="G56" s="8">
+        <v>0</v>
+      </c>
+      <c r="H56" s="8">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B57" s="2"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="11">
+        <v>20</v>
+      </c>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B59" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="17">
+        <v>1</v>
+      </c>
+      <c r="D59" s="18">
+        <v>2</v>
+      </c>
+      <c r="E59" s="19">
+        <v>3</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4</v>
+      </c>
+      <c r="G59" s="18">
+        <v>5</v>
+      </c>
+      <c r="H59" s="19">
+        <v>6</v>
+      </c>
+      <c r="I59" s="17">
+        <v>7</v>
+      </c>
+      <c r="J59" s="18">
+        <v>8</v>
+      </c>
+      <c r="K59" s="19">
+        <v>9</v>
+      </c>
+      <c r="L59" s="11"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="11">
+        <v>4</v>
+      </c>
+      <c r="D60" s="11">
+        <v>5</v>
+      </c>
+      <c r="E60" s="21">
+        <v>3</v>
+      </c>
+      <c r="F60" s="22">
+        <v>4</v>
+      </c>
+      <c r="G60" s="11">
+        <v>4</v>
+      </c>
+      <c r="H60" s="21">
+        <v>3</v>
+      </c>
+      <c r="I60" s="22">
+        <v>5</v>
+      </c>
+      <c r="J60" s="11">
+        <v>4</v>
+      </c>
+      <c r="K60" s="21">
+        <v>4</v>
+      </c>
+      <c r="L60" s="11">
+        <v>36</v>
+      </c>
+      <c r="M60" s="2"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="11">
+        <v>7</v>
+      </c>
+      <c r="D61" s="11">
+        <v>17</v>
+      </c>
+      <c r="E61" s="21">
+        <v>15</v>
+      </c>
+      <c r="F61" s="22">
+        <v>1</v>
+      </c>
+      <c r="G61" s="11">
+        <v>11</v>
+      </c>
+      <c r="H61" s="21">
+        <v>9</v>
+      </c>
+      <c r="I61" s="22">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11">
+        <v>5</v>
+      </c>
+      <c r="K61" s="21">
+        <v>3</v>
+      </c>
+      <c r="L61" s="11"/>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="24">
+        <v>5</v>
+      </c>
+      <c r="D62" s="25">
+        <v>9</v>
+      </c>
+      <c r="E62" s="26">
+        <v>4</v>
+      </c>
+      <c r="F62" s="24">
+        <v>4</v>
+      </c>
+      <c r="G62" s="25">
+        <v>6</v>
+      </c>
+      <c r="H62" s="26">
+        <v>3</v>
+      </c>
+      <c r="I62" s="24">
+        <v>8</v>
+      </c>
+      <c r="J62" s="25">
+        <v>6</v>
+      </c>
+      <c r="K62" s="26">
+        <v>6</v>
+      </c>
+      <c r="L62" s="11">
+        <v>51</v>
+      </c>
+      <c r="M62" s="27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B63" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="22">
+        <v>1</v>
+      </c>
+      <c r="D63" s="11">
+        <v>1</v>
+      </c>
+      <c r="E63" s="21">
+        <v>1</v>
+      </c>
+      <c r="F63" s="22">
+        <v>2</v>
+      </c>
+      <c r="G63" s="11">
+        <v>1</v>
+      </c>
+      <c r="H63" s="21">
+        <v>1</v>
+      </c>
+      <c r="I63" s="22">
+        <v>1</v>
+      </c>
+      <c r="J63" s="11">
+        <v>1</v>
+      </c>
+      <c r="K63" s="21">
+        <v>1</v>
+      </c>
+      <c r="L63" s="27"/>
+      <c r="M63" s="2"/>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B64" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="22">
+        <v>4</v>
+      </c>
+      <c r="D64" s="11">
+        <v>8</v>
+      </c>
+      <c r="E64" s="21">
+        <v>3</v>
+      </c>
+      <c r="F64" s="22">
+        <v>2</v>
+      </c>
+      <c r="G64" s="11">
+        <v>5</v>
+      </c>
+      <c r="H64" s="21">
+        <v>2</v>
+      </c>
+      <c r="I64" s="22">
+        <v>7</v>
+      </c>
+      <c r="J64" s="11">
+        <v>5</v>
+      </c>
+      <c r="K64" s="21">
+        <v>5</v>
+      </c>
+      <c r="L64" s="28">
+        <v>41</v>
+      </c>
+      <c r="M64" s="27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="30">
+        <v>1</v>
+      </c>
+      <c r="D65" s="31">
+        <v>0</v>
+      </c>
+      <c r="E65" s="32">
+        <v>1</v>
+      </c>
+      <c r="F65" s="30">
+        <v>1</v>
+      </c>
+      <c r="G65" s="31">
+        <v>1</v>
+      </c>
+      <c r="H65" s="32">
+        <v>1</v>
+      </c>
+      <c r="I65" s="30">
+        <v>1</v>
+      </c>
+      <c r="J65" s="31">
+        <v>1</v>
+      </c>
+      <c r="K65" s="32">
+        <v>1</v>
+      </c>
+      <c r="L65" s="11"/>
+      <c r="M65" s="2"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B66" s="2"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="2"/>
+    </row>
+    <row r="67" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="11">
+        <v>36</v>
+      </c>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="2"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B68" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="17">
+        <v>1</v>
+      </c>
+      <c r="D68" s="18">
+        <v>2</v>
+      </c>
+      <c r="E68" s="19">
+        <v>3</v>
+      </c>
+      <c r="F68" s="17">
+        <v>4</v>
+      </c>
+      <c r="G68" s="18">
+        <v>5</v>
+      </c>
+      <c r="H68" s="19">
+        <v>6</v>
+      </c>
+      <c r="I68" s="17">
+        <v>7</v>
+      </c>
+      <c r="J68" s="18">
+        <v>8</v>
+      </c>
+      <c r="K68" s="19">
+        <v>9</v>
+      </c>
+      <c r="L68" s="11"/>
+      <c r="M68" s="27"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B69" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="11">
+        <v>4</v>
+      </c>
+      <c r="D69" s="11">
+        <v>5</v>
+      </c>
+      <c r="E69" s="21">
+        <v>3</v>
+      </c>
+      <c r="F69" s="22">
+        <v>4</v>
+      </c>
+      <c r="G69" s="11">
+        <v>4</v>
+      </c>
+      <c r="H69" s="21">
+        <v>3</v>
+      </c>
+      <c r="I69" s="22">
+        <v>5</v>
+      </c>
+      <c r="J69" s="11">
+        <v>4</v>
+      </c>
+      <c r="K69" s="21">
+        <v>4</v>
+      </c>
+      <c r="L69" s="11">
+        <v>36</v>
+      </c>
+      <c r="M69" s="2"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B70" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="11">
+        <v>7</v>
+      </c>
+      <c r="D70" s="11">
+        <v>17</v>
+      </c>
+      <c r="E70" s="21">
+        <v>15</v>
+      </c>
+      <c r="F70" s="22">
+        <v>1</v>
+      </c>
+      <c r="G70" s="11">
+        <v>11</v>
+      </c>
+      <c r="H70" s="21">
+        <v>9</v>
+      </c>
+      <c r="I70" s="22">
+        <v>13</v>
+      </c>
+      <c r="J70" s="11">
+        <v>5</v>
+      </c>
+      <c r="K70" s="21">
+        <v>3</v>
+      </c>
+      <c r="L70" s="11"/>
+      <c r="M70" s="2"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="24">
+        <v>8</v>
+      </c>
+      <c r="D71" s="25">
+        <v>10</v>
+      </c>
+      <c r="E71" s="26">
+        <v>6</v>
+      </c>
+      <c r="F71" s="24">
+        <v>8</v>
+      </c>
+      <c r="G71" s="25">
+        <v>8</v>
+      </c>
+      <c r="H71" s="26">
+        <v>6</v>
+      </c>
+      <c r="I71" s="24">
+        <v>10</v>
+      </c>
+      <c r="J71" s="25">
+        <v>8</v>
+      </c>
+      <c r="K71" s="26">
+        <v>8</v>
+      </c>
+      <c r="L71" s="11">
+        <v>72</v>
+      </c>
+      <c r="M71" s="27">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B72" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="22">
+        <v>2</v>
+      </c>
+      <c r="D72" s="11">
+        <v>2</v>
+      </c>
+      <c r="E72" s="21">
+        <v>2</v>
+      </c>
+      <c r="F72" s="22">
+        <v>2</v>
+      </c>
+      <c r="G72" s="11">
+        <v>2</v>
+      </c>
+      <c r="H72" s="21">
+        <v>2</v>
+      </c>
+      <c r="I72" s="22">
+        <v>2</v>
+      </c>
+      <c r="J72" s="11">
+        <v>2</v>
+      </c>
+      <c r="K72" s="21">
+        <v>2</v>
+      </c>
+      <c r="L72" s="27"/>
+      <c r="M72" s="2"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B73" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="22">
+        <v>6</v>
+      </c>
+      <c r="D73" s="11">
+        <v>8</v>
+      </c>
+      <c r="E73" s="21">
+        <v>4</v>
+      </c>
+      <c r="F73" s="22">
+        <v>6</v>
+      </c>
+      <c r="G73" s="11">
+        <v>6</v>
+      </c>
+      <c r="H73" s="21">
+        <v>4</v>
+      </c>
+      <c r="I73" s="22">
+        <v>8</v>
+      </c>
+      <c r="J73" s="11">
+        <v>6</v>
+      </c>
+      <c r="K73" s="21">
+        <v>6</v>
+      </c>
+      <c r="L73" s="28">
+        <v>54</v>
+      </c>
+      <c r="M73" s="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="30">
+        <v>0</v>
+      </c>
+      <c r="D74" s="31">
+        <v>0</v>
+      </c>
+      <c r="E74" s="32">
+        <v>0</v>
+      </c>
+      <c r="F74" s="30">
+        <v>0</v>
+      </c>
+      <c r="G74" s="31">
+        <v>0</v>
+      </c>
+      <c r="H74" s="32">
+        <v>0</v>
+      </c>
+      <c r="I74" s="30">
+        <v>0</v>
+      </c>
+      <c r="J74" s="31">
+        <v>0</v>
+      </c>
+      <c r="K74" s="32">
+        <v>0</v>
+      </c>
+      <c r="L74" s="11"/>
+      <c r="M74" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="J28:K30"/>
     <mergeCell ref="L28:M30"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:K40 C49:K49">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C40:K40 C49:K49">
+  <conditionalFormatting sqref="C65:K65 C74:K74">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>

--- a/Scores/Scores.xlsx
+++ b/Scores/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/Scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{277BDAC4-620B-4D3D-AEF5-CE4B56F43027}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{A7A9DF33-59F8-4D98-BEDA-ABC849897098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AD21870-B2CE-4125-8711-8009DE762238}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1 Scores" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="41">
   <si>
     <t>Skybrook</t>
   </si>
@@ -6061,48 +6061,48 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X53:Y55"/>
+    <mergeCell ref="Z53:AA55"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="X3:Y5"/>
+    <mergeCell ref="Z3:AA5"/>
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="X27:Y27"/>
     <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="P28:P29"/>
     <mergeCell ref="X28:Y30"/>
     <mergeCell ref="Z28:AA30"/>
     <mergeCell ref="P30:P31"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="X3:Y5"/>
-    <mergeCell ref="Z3:AA5"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X53:Y55"/>
-    <mergeCell ref="Z53:AA55"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
     <cfRule type="cellIs" dxfId="25" priority="10" operator="greaterThan">
@@ -11214,48 +11214,48 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J127:K127"/>
+    <mergeCell ref="L127:M127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="J128:K130"/>
+    <mergeCell ref="L128:M130"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="J53:K55"/>
+    <mergeCell ref="L53:M55"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="J103:K105"/>
+    <mergeCell ref="L103:M105"/>
+    <mergeCell ref="B105:B106"/>
     <mergeCell ref="J152:K152"/>
     <mergeCell ref="L152:M152"/>
     <mergeCell ref="B153:B154"/>
     <mergeCell ref="J153:K155"/>
     <mergeCell ref="L153:M155"/>
     <mergeCell ref="B155:B156"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="J103:K105"/>
-    <mergeCell ref="L103:M105"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="J53:K55"/>
-    <mergeCell ref="L53:M55"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J127:K127"/>
-    <mergeCell ref="L127:M127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="J128:K130"/>
-    <mergeCell ref="L128:M130"/>
-    <mergeCell ref="B130:B131"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
     <cfRule type="cellIs" dxfId="18" priority="8" operator="greaterThan">
@@ -11298,7 +11298,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:M125"/>
+  <dimension ref="B1:M150"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -14920,60 +14920,794 @@
       <c r="L125" s="11"/>
       <c r="M125" s="2"/>
     </row>
+    <row r="127" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="128" spans="2:13" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I128" s="4"/>
+      <c r="J128" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="K128" s="34"/>
+      <c r="L128" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="M128" s="34"/>
+    </row>
+    <row r="129" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B129" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D129" s="6">
+        <v>0</v>
+      </c>
+      <c r="E129" s="6">
+        <v>0</v>
+      </c>
+      <c r="F129" s="6">
+        <v>1</v>
+      </c>
+      <c r="G129" s="6">
+        <v>1</v>
+      </c>
+      <c r="H129" s="6">
+        <v>47</v>
+      </c>
+      <c r="I129" s="2"/>
+      <c r="J129" s="38">
+        <v>0</v>
+      </c>
+      <c r="K129" s="39"/>
+      <c r="L129" s="43">
+        <v>8</v>
+      </c>
+      <c r="M129" s="39"/>
+    </row>
+    <row r="130" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B130" s="37"/>
+      <c r="C130" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="8">
+        <v>0</v>
+      </c>
+      <c r="E130" s="8">
+        <v>0</v>
+      </c>
+      <c r="F130" s="8">
+        <v>0</v>
+      </c>
+      <c r="G130" s="8">
+        <v>0</v>
+      </c>
+      <c r="H130" s="8">
+        <v>0</v>
+      </c>
+      <c r="I130" s="2"/>
+      <c r="J130" s="40"/>
+      <c r="K130" s="41"/>
+      <c r="L130" s="44"/>
+      <c r="M130" s="41"/>
+    </row>
+    <row r="131" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D131" s="10">
+        <v>3</v>
+      </c>
+      <c r="E131" s="10">
+        <v>3</v>
+      </c>
+      <c r="F131" s="10">
+        <v>2</v>
+      </c>
+      <c r="G131" s="10">
+        <v>8</v>
+      </c>
+      <c r="H131" s="10">
+        <v>34</v>
+      </c>
+      <c r="I131" s="2"/>
+      <c r="J131" s="37"/>
+      <c r="K131" s="42"/>
+      <c r="L131" s="45"/>
+      <c r="M131" s="42"/>
+    </row>
+    <row r="132" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B132" s="37"/>
+      <c r="C132" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="8">
+        <v>2</v>
+      </c>
+      <c r="E132" s="8">
+        <v>2</v>
+      </c>
+      <c r="F132" s="8">
+        <v>2</v>
+      </c>
+      <c r="G132" s="8">
+        <v>1</v>
+      </c>
+      <c r="H132" s="8">
+        <v>1</v>
+      </c>
+      <c r="I132" s="2"/>
+      <c r="J132" s="11"/>
+      <c r="K132" s="11"/>
+      <c r="L132" s="11"/>
+      <c r="M132" s="11"/>
+    </row>
+    <row r="133" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B133" s="2"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="11"/>
+      <c r="H133" s="11"/>
+      <c r="I133" s="11"/>
+      <c r="J133" s="11"/>
+      <c r="K133" s="11"/>
+      <c r="L133" s="11"/>
+      <c r="M133" s="2"/>
+    </row>
+    <row r="134" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B134" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="11">
+        <v>20</v>
+      </c>
+      <c r="E134" s="11"/>
+      <c r="F134" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H134" s="11"/>
+      <c r="I134" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J134" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K134" s="11"/>
+      <c r="L134" s="11"/>
+      <c r="M134" s="2"/>
+    </row>
+    <row r="135" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B135" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135" s="17">
+        <v>1</v>
+      </c>
+      <c r="D135" s="18">
+        <v>2</v>
+      </c>
+      <c r="E135" s="19">
+        <v>3</v>
+      </c>
+      <c r="F135" s="17">
+        <v>4</v>
+      </c>
+      <c r="G135" s="18">
+        <v>5</v>
+      </c>
+      <c r="H135" s="19">
+        <v>6</v>
+      </c>
+      <c r="I135" s="17">
+        <v>7</v>
+      </c>
+      <c r="J135" s="18">
+        <v>8</v>
+      </c>
+      <c r="K135" s="19">
+        <v>9</v>
+      </c>
+      <c r="L135" s="11"/>
+      <c r="M135" s="2"/>
+    </row>
+    <row r="136" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B136" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C136" s="11">
+        <v>5</v>
+      </c>
+      <c r="D136" s="11">
+        <v>4</v>
+      </c>
+      <c r="E136" s="21">
+        <v>3</v>
+      </c>
+      <c r="F136" s="22">
+        <v>5</v>
+      </c>
+      <c r="G136" s="11">
+        <v>4</v>
+      </c>
+      <c r="H136" s="21">
+        <v>3</v>
+      </c>
+      <c r="I136" s="22">
+        <v>4</v>
+      </c>
+      <c r="J136" s="11">
+        <v>3</v>
+      </c>
+      <c r="K136" s="21">
+        <v>4</v>
+      </c>
+      <c r="L136" s="11">
+        <v>35</v>
+      </c>
+      <c r="M136" s="2"/>
+    </row>
+    <row r="137" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B137" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" s="11">
+        <v>7</v>
+      </c>
+      <c r="D137" s="11">
+        <v>3</v>
+      </c>
+      <c r="E137" s="21">
+        <v>13</v>
+      </c>
+      <c r="F137" s="22">
+        <v>9</v>
+      </c>
+      <c r="G137" s="11">
+        <v>11</v>
+      </c>
+      <c r="H137" s="21">
+        <v>15</v>
+      </c>
+      <c r="I137" s="22">
+        <v>1</v>
+      </c>
+      <c r="J137" s="11">
+        <v>5</v>
+      </c>
+      <c r="K137" s="21">
+        <v>17</v>
+      </c>
+      <c r="L137" s="11"/>
+      <c r="M137" s="2"/>
+    </row>
+    <row r="138" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B138" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C138" s="24">
+        <v>7</v>
+      </c>
+      <c r="D138" s="25">
+        <v>7</v>
+      </c>
+      <c r="E138" s="26">
+        <v>5</v>
+      </c>
+      <c r="F138" s="24">
+        <v>7</v>
+      </c>
+      <c r="G138" s="25">
+        <v>6</v>
+      </c>
+      <c r="H138" s="26">
+        <v>6</v>
+      </c>
+      <c r="I138" s="24">
+        <v>8</v>
+      </c>
+      <c r="J138" s="25">
+        <v>3</v>
+      </c>
+      <c r="K138" s="26">
+        <v>8</v>
+      </c>
+      <c r="L138" s="11">
+        <v>57</v>
+      </c>
+      <c r="M138" s="27">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B139" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C139" s="22">
+        <v>1</v>
+      </c>
+      <c r="D139" s="11">
+        <v>1</v>
+      </c>
+      <c r="E139" s="21">
+        <v>1</v>
+      </c>
+      <c r="F139" s="22">
+        <v>1</v>
+      </c>
+      <c r="G139" s="11">
+        <v>1</v>
+      </c>
+      <c r="H139" s="21">
+        <v>1</v>
+      </c>
+      <c r="I139" s="22">
+        <v>2</v>
+      </c>
+      <c r="J139" s="11">
+        <v>1</v>
+      </c>
+      <c r="K139" s="21">
+        <v>1</v>
+      </c>
+      <c r="L139" s="27"/>
+      <c r="M139" s="2"/>
+    </row>
+    <row r="140" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B140" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C140" s="22">
+        <v>6</v>
+      </c>
+      <c r="D140" s="11">
+        <v>6</v>
+      </c>
+      <c r="E140" s="21">
+        <v>4</v>
+      </c>
+      <c r="F140" s="22">
+        <v>6</v>
+      </c>
+      <c r="G140" s="11">
+        <v>5</v>
+      </c>
+      <c r="H140" s="21">
+        <v>5</v>
+      </c>
+      <c r="I140" s="22">
+        <v>6</v>
+      </c>
+      <c r="J140" s="11">
+        <v>2</v>
+      </c>
+      <c r="K140" s="21">
+        <v>7</v>
+      </c>
+      <c r="L140" s="28">
+        <v>47</v>
+      </c>
+      <c r="M140" s="27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B141" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C141" s="30">
+        <v>0</v>
+      </c>
+      <c r="D141" s="31">
+        <v>0</v>
+      </c>
+      <c r="E141" s="32">
+        <v>0</v>
+      </c>
+      <c r="F141" s="30">
+        <v>0</v>
+      </c>
+      <c r="G141" s="31">
+        <v>0</v>
+      </c>
+      <c r="H141" s="32">
+        <v>0</v>
+      </c>
+      <c r="I141" s="30">
+        <v>0</v>
+      </c>
+      <c r="J141" s="31">
+        <v>1</v>
+      </c>
+      <c r="K141" s="32">
+        <v>0</v>
+      </c>
+      <c r="L141" s="11"/>
+      <c r="M141" s="2"/>
+    </row>
+    <row r="142" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B142" s="2"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="11"/>
+      <c r="H142" s="11"/>
+      <c r="I142" s="11"/>
+      <c r="J142" s="11"/>
+      <c r="K142" s="11"/>
+      <c r="L142" s="11"/>
+      <c r="M142" s="2"/>
+    </row>
+    <row r="143" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B143" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C143" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="11">
+        <v>12</v>
+      </c>
+      <c r="E143" s="11"/>
+      <c r="F143" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G143" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H143" s="11"/>
+      <c r="I143" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J143" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K143" s="11"/>
+      <c r="L143" s="11"/>
+      <c r="M143" s="2"/>
+    </row>
+    <row r="144" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B144" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C144" s="17">
+        <v>1</v>
+      </c>
+      <c r="D144" s="18">
+        <v>2</v>
+      </c>
+      <c r="E144" s="19">
+        <v>3</v>
+      </c>
+      <c r="F144" s="17">
+        <v>4</v>
+      </c>
+      <c r="G144" s="18">
+        <v>5</v>
+      </c>
+      <c r="H144" s="19">
+        <v>6</v>
+      </c>
+      <c r="I144" s="17">
+        <v>7</v>
+      </c>
+      <c r="J144" s="18">
+        <v>8</v>
+      </c>
+      <c r="K144" s="19">
+        <v>9</v>
+      </c>
+      <c r="L144" s="11"/>
+      <c r="M144" s="27"/>
+    </row>
+    <row r="145" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B145" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="11">
+        <v>5</v>
+      </c>
+      <c r="D145" s="11">
+        <v>4</v>
+      </c>
+      <c r="E145" s="21">
+        <v>3</v>
+      </c>
+      <c r="F145" s="22">
+        <v>5</v>
+      </c>
+      <c r="G145" s="11">
+        <v>4</v>
+      </c>
+      <c r="H145" s="21">
+        <v>3</v>
+      </c>
+      <c r="I145" s="22">
+        <v>4</v>
+      </c>
+      <c r="J145" s="11">
+        <v>3</v>
+      </c>
+      <c r="K145" s="21">
+        <v>4</v>
+      </c>
+      <c r="L145" s="11">
+        <v>35</v>
+      </c>
+      <c r="M145" s="2"/>
+    </row>
+    <row r="146" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B146" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" s="11">
+        <v>7</v>
+      </c>
+      <c r="D146" s="11">
+        <v>3</v>
+      </c>
+      <c r="E146" s="21">
+        <v>13</v>
+      </c>
+      <c r="F146" s="22">
+        <v>9</v>
+      </c>
+      <c r="G146" s="11">
+        <v>11</v>
+      </c>
+      <c r="H146" s="21">
+        <v>15</v>
+      </c>
+      <c r="I146" s="22">
+        <v>1</v>
+      </c>
+      <c r="J146" s="11">
+        <v>5</v>
+      </c>
+      <c r="K146" s="21">
+        <v>17</v>
+      </c>
+      <c r="L146" s="11"/>
+      <c r="M146" s="2"/>
+    </row>
+    <row r="147" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B147" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" s="24">
+        <v>6</v>
+      </c>
+      <c r="D147" s="25">
+        <v>5</v>
+      </c>
+      <c r="E147" s="26">
+        <v>2</v>
+      </c>
+      <c r="F147" s="24">
+        <v>5</v>
+      </c>
+      <c r="G147" s="25">
+        <v>5</v>
+      </c>
+      <c r="H147" s="26">
+        <v>3</v>
+      </c>
+      <c r="I147" s="24">
+        <v>6</v>
+      </c>
+      <c r="J147" s="25">
+        <v>4</v>
+      </c>
+      <c r="K147" s="26">
+        <v>4</v>
+      </c>
+      <c r="L147" s="11">
+        <v>40</v>
+      </c>
+      <c r="M147" s="27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B148" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C148" s="22">
+        <v>1</v>
+      </c>
+      <c r="D148" s="11">
+        <v>1</v>
+      </c>
+      <c r="E148" s="21">
+        <v>0</v>
+      </c>
+      <c r="F148" s="22">
+        <v>1</v>
+      </c>
+      <c r="G148" s="11">
+        <v>1</v>
+      </c>
+      <c r="H148" s="21">
+        <v>0</v>
+      </c>
+      <c r="I148" s="22">
+        <v>1</v>
+      </c>
+      <c r="J148" s="11">
+        <v>1</v>
+      </c>
+      <c r="K148" s="21">
+        <v>0</v>
+      </c>
+      <c r="L148" s="27"/>
+      <c r="M148" s="2"/>
+    </row>
+    <row r="149" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B149" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C149" s="22">
+        <v>5</v>
+      </c>
+      <c r="D149" s="11">
+        <v>4</v>
+      </c>
+      <c r="E149" s="21">
+        <v>2</v>
+      </c>
+      <c r="F149" s="22">
+        <v>4</v>
+      </c>
+      <c r="G149" s="11">
+        <v>4</v>
+      </c>
+      <c r="H149" s="21">
+        <v>3</v>
+      </c>
+      <c r="I149" s="22">
+        <v>5</v>
+      </c>
+      <c r="J149" s="11">
+        <v>3</v>
+      </c>
+      <c r="K149" s="21">
+        <v>4</v>
+      </c>
+      <c r="L149" s="28">
+        <v>34</v>
+      </c>
+      <c r="M149" s="27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="150" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B150" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" s="30">
+        <v>1</v>
+      </c>
+      <c r="D150" s="31">
+        <v>1</v>
+      </c>
+      <c r="E150" s="32">
+        <v>1</v>
+      </c>
+      <c r="F150" s="30">
+        <v>1</v>
+      </c>
+      <c r="G150" s="31">
+        <v>1</v>
+      </c>
+      <c r="H150" s="32">
+        <v>1</v>
+      </c>
+      <c r="I150" s="30">
+        <v>1</v>
+      </c>
+      <c r="J150" s="31">
+        <v>0</v>
+      </c>
+      <c r="K150" s="32">
+        <v>1</v>
+      </c>
+      <c r="L150" s="11"/>
+      <c r="M150" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="36">
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="L128:M128"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="J129:K131"/>
+    <mergeCell ref="L129:M131"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="J79:K81"/>
+    <mergeCell ref="L79:M81"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="J29:K31"/>
+    <mergeCell ref="L29:M31"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J4:K6"/>
+    <mergeCell ref="L4:M6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="J54:K56"/>
+    <mergeCell ref="L54:M56"/>
+    <mergeCell ref="B56:B57"/>
     <mergeCell ref="J103:K103"/>
     <mergeCell ref="L103:M103"/>
     <mergeCell ref="B104:B105"/>
     <mergeCell ref="J104:K106"/>
     <mergeCell ref="L104:M106"/>
     <mergeCell ref="B106:B107"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="J54:K56"/>
-    <mergeCell ref="L54:M56"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J4:K6"/>
-    <mergeCell ref="L4:M6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="J29:K31"/>
-    <mergeCell ref="L29:M31"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="L78:M78"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="J79:K81"/>
-    <mergeCell ref="L79:M81"/>
-    <mergeCell ref="B81:B82"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:K16 C25:K25">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41:K41 C50:K50">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:K66 C75:K75">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C91:K91 C100:K100">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C116:K116 C125:K125">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C141:K141 C150:K150">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -17884,48 +18618,48 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="J78:K80"/>
+    <mergeCell ref="L78:M80"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="J28:K30"/>
+    <mergeCell ref="L28:M30"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="L52:M52"/>
     <mergeCell ref="B53:B54"/>
     <mergeCell ref="J53:K55"/>
     <mergeCell ref="L53:M55"/>
     <mergeCell ref="B55:B56"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="J28:K30"/>
-    <mergeCell ref="L28:M30"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="J78:K80"/>
-    <mergeCell ref="L78:M80"/>
-    <mergeCell ref="B80:B81"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:K65 C74:K74">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90:K90 C99:K99">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19390,26 +20124,26 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="J28:K30"/>
     <mergeCell ref="L28:M30"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40:K40 C49:K49">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
